--- a/최종산출물/2. WBS/[2조] WBS(현대이지웰_최종프로젝트).xlsx
+++ b/최종산출물/2. WBS/[2조] WBS(현대이지웰_최종프로젝트).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="112">
   <si>
     <t>[K-Digital] 현대이지웰 과정 WBS양식 (예시 양식일 뿐, 다른 양식으로 사용하셔도 됩니다)</t>
   </si>
@@ -331,22 +331,22 @@
     <t>사용자 개인 접근성 설정 및 적용 처리</t>
   </si>
   <si>
-    <t>접근성 점검(키보드/포커스/라벨/대비) + 개선</t>
-  </si>
-  <si>
     <t>README/최종 ERD/API/데모 시나리오</t>
   </si>
   <si>
+    <t>UI/UX 통일화 작업</t>
+  </si>
+  <si>
     <t>프런트/백엔드 연동</t>
+  </si>
+  <si>
+    <t>서버 동기화</t>
   </si>
   <si>
     <t>예외처리/검증/에러</t>
   </si>
   <si>
     <t>전역 예외 / 검증 / 유효성 처리</t>
-  </si>
-  <si>
-    <t>예외 / 검증 / 에러 알림 UI</t>
   </si>
   <si>
     <t>공통 에러 응답/알림 처리</t>
@@ -642,7 +642,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -870,9 +870,6 @@
     </xf>
     <xf borderId="7" fillId="2" fontId="10" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="10" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -3867,25 +3864,31 @@
       <c r="B69" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="C69" s="30">
-        <v>0.0</v>
-      </c>
-      <c r="D69" s="26"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
+      <c r="C69" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="25">
+        <v>46134.0</v>
+      </c>
+      <c r="F69" s="25">
+        <v>46196.0</v>
+      </c>
       <c r="G69" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H69" s="71"/>
+        <v>25</v>
+      </c>
+      <c r="H69" s="27"/>
       <c r="I69" s="71"/>
       <c r="J69" s="71"/>
       <c r="K69" s="71"/>
       <c r="L69" s="71"/>
       <c r="M69" s="71"/>
       <c r="N69" s="71"/>
-      <c r="O69" s="28"/>
+      <c r="O69" s="71"/>
       <c r="P69" s="28"/>
-      <c r="Q69" s="71"/>
+      <c r="Q69" s="28"/>
       <c r="R69" s="71"/>
       <c r="S69" s="71"/>
       <c r="T69" s="71"/>
@@ -3900,33 +3903,33 @@
     </row>
     <row r="70" ht="17.25" customHeight="1">
       <c r="A70" s="37"/>
-      <c r="B70" s="69" t="s">
+      <c r="B70" s="56" t="s">
         <v>100</v>
       </c>
       <c r="C70" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="D70" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E70" s="25">
-        <v>46134.0</v>
-      </c>
-      <c r="F70" s="25">
-        <v>46196.0</v>
-      </c>
-      <c r="G70" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H70" s="27"/>
+        <v>1.0</v>
+      </c>
+      <c r="D70" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="49">
+        <v>46189.0</v>
+      </c>
+      <c r="F70" s="49">
+        <v>46190.0</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="71"/>
       <c r="I70" s="71"/>
-      <c r="J70" s="71"/>
-      <c r="K70" s="71"/>
-      <c r="L70" s="71"/>
-      <c r="M70" s="71"/>
-      <c r="N70" s="71"/>
-      <c r="O70" s="71"/>
-      <c r="P70" s="28"/>
+      <c r="J70" s="53"/>
+      <c r="K70" s="53"/>
+      <c r="L70" s="53"/>
+      <c r="M70" s="53"/>
+      <c r="N70" s="53"/>
+      <c r="O70" s="53"/>
+      <c r="P70" s="27"/>
       <c r="Q70" s="28"/>
       <c r="R70" s="71"/>
       <c r="S70" s="71"/>
@@ -3946,13 +3949,17 @@
         <v>101</v>
       </c>
       <c r="C71" s="23">
-        <v>0.95</v>
-      </c>
-      <c r="D71" s="26"/>
+        <v>1.0</v>
+      </c>
+      <c r="D71" s="39" t="s">
+        <v>17</v>
+      </c>
       <c r="E71" s="49">
         <v>46148.0</v>
       </c>
-      <c r="F71" s="25"/>
+      <c r="F71" s="49">
+        <v>46185.0</v>
+      </c>
       <c r="G71" s="26" t="s">
         <v>25</v>
       </c>
@@ -3980,22 +3987,32 @@
     </row>
     <row r="72" ht="17.25" customHeight="1">
       <c r="A72" s="37"/>
-      <c r="B72" s="32" t="s">
+      <c r="B72" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="33"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="36"/>
+      <c r="C72" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="D72" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="49">
+        <v>46191.0</v>
+      </c>
+      <c r="F72" s="49">
+        <v>46192.0</v>
+      </c>
+      <c r="G72" s="39" t="s">
+        <v>39</v>
+      </c>
       <c r="H72" s="71"/>
       <c r="I72" s="71"/>
-      <c r="J72" s="71"/>
-      <c r="K72" s="71"/>
-      <c r="L72" s="71"/>
-      <c r="M72" s="71"/>
-      <c r="N72" s="71"/>
-      <c r="O72" s="71"/>
+      <c r="J72" s="27"/>
+      <c r="K72" s="27"/>
+      <c r="L72" s="27"/>
+      <c r="M72" s="27"/>
+      <c r="N72" s="27"/>
+      <c r="O72" s="27"/>
       <c r="P72" s="28"/>
       <c r="Q72" s="28"/>
       <c r="R72" s="71"/>
@@ -4012,28 +4029,18 @@
     </row>
     <row r="73" ht="17.25" customHeight="1">
       <c r="A73" s="37"/>
-      <c r="B73" s="56" t="s">
+      <c r="B73" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="C73" s="75">
-        <v>1.0</v>
-      </c>
-      <c r="D73" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="49">
-        <v>46153.0</v>
-      </c>
-      <c r="F73" s="49">
-        <v>46154.0</v>
-      </c>
-      <c r="G73" s="39" t="s">
-        <v>27</v>
-      </c>
+      <c r="C73" s="33"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="36"/>
       <c r="H73" s="71"/>
       <c r="I73" s="71"/>
       <c r="J73" s="71"/>
-      <c r="K73" s="74"/>
+      <c r="K73" s="71"/>
       <c r="L73" s="71"/>
       <c r="M73" s="71"/>
       <c r="N73" s="71"/>
@@ -4046,30 +4053,36 @@
       <c r="U73" s="71"/>
       <c r="V73" s="71"/>
       <c r="W73" s="71"/>
-      <c r="X73" s="7"/>
-      <c r="Y73" s="7"/>
-      <c r="Z73" s="7"/>
-      <c r="AA73" s="7"/>
-      <c r="AB73" s="7"/>
+      <c r="X73" s="70"/>
+      <c r="Y73" s="70"/>
+      <c r="Z73" s="70"/>
+      <c r="AA73" s="70"/>
+      <c r="AB73" s="70"/>
     </row>
     <row r="74" ht="17.25" customHeight="1">
       <c r="A74" s="37"/>
-      <c r="B74" s="69" t="s">
+      <c r="B74" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C74" s="76"/>
-      <c r="D74" s="26" t="s">
+      <c r="C74" s="75">
+        <v>1.0</v>
+      </c>
+      <c r="D74" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
+      <c r="E74" s="49">
+        <v>46153.0</v>
+      </c>
+      <c r="F74" s="49">
+        <v>46154.0</v>
+      </c>
       <c r="G74" s="39" t="s">
         <v>27</v>
       </c>
       <c r="H74" s="71"/>
       <c r="I74" s="71"/>
       <c r="J74" s="71"/>
-      <c r="K74" s="71"/>
+      <c r="K74" s="74"/>
       <c r="L74" s="71"/>
       <c r="M74" s="71"/>
       <c r="N74" s="71"/>
@@ -4180,10 +4193,10 @@
       <c r="C77" s="30">
         <v>0.0</v>
       </c>
-      <c r="D77" s="77"/>
+      <c r="D77" s="76"/>
       <c r="E77" s="35"/>
       <c r="F77" s="35"/>
-      <c r="G77" s="77"/>
+      <c r="G77" s="76"/>
       <c r="H77" s="71"/>
       <c r="I77" s="71"/>
       <c r="J77" s="71"/>
@@ -4193,13 +4206,13 @@
       <c r="N77" s="71"/>
       <c r="O77" s="71"/>
       <c r="P77" s="71"/>
-      <c r="Q77" s="71"/>
+      <c r="Q77" s="74"/>
       <c r="R77" s="71"/>
       <c r="S77" s="71"/>
-      <c r="T77" s="78"/>
-      <c r="U77" s="78"/>
-      <c r="V77" s="78"/>
-      <c r="W77" s="78"/>
+      <c r="T77" s="77"/>
+      <c r="U77" s="77"/>
+      <c r="V77" s="77"/>
+      <c r="W77" s="77"/>
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
@@ -4208,17 +4221,17 @@
     </row>
     <row r="78" ht="17.25" customHeight="1">
       <c r="A78" s="37"/>
-      <c r="B78" s="79" t="s">
+      <c r="B78" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="30">
-        <v>0.0</v>
+      <c r="C78" s="23">
+        <v>1.0</v>
       </c>
       <c r="D78" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E78" s="25">
-        <v>46193.0</v>
+      <c r="E78" s="49">
+        <v>46191.0</v>
       </c>
       <c r="F78" s="25">
         <v>46196.0</v>
@@ -4226,22 +4239,22 @@
       <c r="G78" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="H78" s="80"/>
-      <c r="I78" s="80"/>
-      <c r="J78" s="80"/>
-      <c r="K78" s="80"/>
-      <c r="L78" s="80"/>
-      <c r="M78" s="80"/>
-      <c r="N78" s="80"/>
-      <c r="O78" s="80"/>
-      <c r="P78" s="80"/>
-      <c r="Q78" s="80"/>
-      <c r="R78" s="80"/>
-      <c r="S78" s="80"/>
-      <c r="T78" s="80"/>
-      <c r="U78" s="80"/>
-      <c r="V78" s="80"/>
-      <c r="W78" s="80"/>
+      <c r="H78" s="79"/>
+      <c r="I78" s="79"/>
+      <c r="J78" s="79"/>
+      <c r="K78" s="79"/>
+      <c r="L78" s="79"/>
+      <c r="M78" s="79"/>
+      <c r="N78" s="79"/>
+      <c r="O78" s="79"/>
+      <c r="P78" s="79"/>
+      <c r="Q78" s="79"/>
+      <c r="R78" s="79"/>
+      <c r="S78" s="79"/>
+      <c r="T78" s="79"/>
+      <c r="U78" s="79"/>
+      <c r="V78" s="79"/>
+      <c r="W78" s="79"/>
       <c r="X78" s="7"/>
       <c r="Y78" s="7"/>
       <c r="Z78" s="7"/>
@@ -4250,17 +4263,17 @@
     </row>
     <row r="79" ht="17.25" customHeight="1">
       <c r="A79" s="37"/>
-      <c r="B79" s="79" t="s">
+      <c r="B79" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="C79" s="30">
-        <v>0.0</v>
+      <c r="C79" s="23">
+        <v>1.0</v>
       </c>
       <c r="D79" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E79" s="25">
-        <v>46193.0</v>
+      <c r="E79" s="49">
+        <v>46191.0</v>
       </c>
       <c r="F79" s="25">
         <v>46196.0</v>
@@ -4268,22 +4281,22 @@
       <c r="G79" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H79" s="80"/>
-      <c r="I79" s="80"/>
-      <c r="J79" s="80"/>
-      <c r="K79" s="80"/>
-      <c r="L79" s="80"/>
-      <c r="M79" s="80"/>
-      <c r="N79" s="80"/>
-      <c r="O79" s="80"/>
-      <c r="P79" s="80"/>
-      <c r="Q79" s="80"/>
-      <c r="R79" s="80"/>
-      <c r="S79" s="80"/>
-      <c r="T79" s="80"/>
-      <c r="U79" s="80"/>
-      <c r="V79" s="80"/>
-      <c r="W79" s="80"/>
+      <c r="H79" s="79"/>
+      <c r="I79" s="79"/>
+      <c r="J79" s="79"/>
+      <c r="K79" s="79"/>
+      <c r="L79" s="79"/>
+      <c r="M79" s="79"/>
+      <c r="N79" s="79"/>
+      <c r="O79" s="79"/>
+      <c r="P79" s="79"/>
+      <c r="Q79" s="74"/>
+      <c r="R79" s="79"/>
+      <c r="S79" s="79"/>
+      <c r="T79" s="79"/>
+      <c r="U79" s="79"/>
+      <c r="V79" s="79"/>
+      <c r="W79" s="79"/>
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
@@ -4291,12 +4304,12 @@
       <c r="AB79" s="7"/>
     </row>
     <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="81"/>
-      <c r="B80" s="79" t="s">
+      <c r="A80" s="80"/>
+      <c r="B80" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="C80" s="30">
-        <v>0.0</v>
+      <c r="C80" s="23">
+        <v>1.0</v>
       </c>
       <c r="D80" s="26" t="s">
         <v>13</v>
@@ -4310,22 +4323,22 @@
       <c r="G80" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="H80" s="80"/>
-      <c r="I80" s="80"/>
-      <c r="J80" s="80"/>
-      <c r="K80" s="80"/>
-      <c r="L80" s="80"/>
-      <c r="M80" s="80"/>
-      <c r="N80" s="80"/>
-      <c r="O80" s="80"/>
-      <c r="P80" s="80"/>
-      <c r="Q80" s="80"/>
-      <c r="R80" s="80"/>
-      <c r="S80" s="80"/>
-      <c r="T80" s="80"/>
-      <c r="U80" s="80"/>
-      <c r="V80" s="80"/>
-      <c r="W80" s="80"/>
+      <c r="H80" s="79"/>
+      <c r="I80" s="79"/>
+      <c r="J80" s="79"/>
+      <c r="K80" s="79"/>
+      <c r="L80" s="79"/>
+      <c r="M80" s="79"/>
+      <c r="N80" s="79"/>
+      <c r="O80" s="79"/>
+      <c r="P80" s="79"/>
+      <c r="Q80" s="74"/>
+      <c r="R80" s="79"/>
+      <c r="S80" s="79"/>
+      <c r="T80" s="79"/>
+      <c r="U80" s="79"/>
+      <c r="V80" s="79"/>
+      <c r="W80" s="79"/>
       <c r="X80" s="7"/>
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
@@ -4335,7 +4348,7 @@
     <row r="81" ht="17.25" customHeight="1">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
-      <c r="C81" s="82"/>
+      <c r="C81" s="81"/>
       <c r="D81" s="7"/>
       <c r="E81" s="18"/>
       <c r="F81" s="18"/>
@@ -4365,7 +4378,7 @@
     <row r="82" ht="17.25" customHeight="1">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="82"/>
+      <c r="C82" s="81"/>
       <c r="D82" s="7"/>
       <c r="E82" s="18"/>
       <c r="F82" s="18"/>
@@ -4395,7 +4408,7 @@
     <row r="83" ht="17.25" customHeight="1">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="82"/>
+      <c r="C83" s="81"/>
       <c r="D83" s="7"/>
       <c r="E83" s="18"/>
       <c r="F83" s="18"/>
@@ -4425,7 +4438,7 @@
     <row r="84" ht="17.25" customHeight="1">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
-      <c r="C84" s="82"/>
+      <c r="C84" s="81"/>
       <c r="D84" s="7"/>
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
@@ -4455,7 +4468,7 @@
     <row r="85" ht="17.25" customHeight="1">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
-      <c r="C85" s="82"/>
+      <c r="C85" s="81"/>
       <c r="D85" s="7"/>
       <c r="E85" s="18"/>
       <c r="F85" s="18"/>
@@ -4485,7 +4498,7 @@
     <row r="86" ht="17.25" customHeight="1">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
-      <c r="C86" s="82"/>
+      <c r="C86" s="81"/>
       <c r="D86" s="7"/>
       <c r="E86" s="18"/>
       <c r="F86" s="18"/>
@@ -4515,7 +4528,7 @@
     <row r="87" ht="17.25" customHeight="1">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
-      <c r="C87" s="82"/>
+      <c r="C87" s="81"/>
       <c r="D87" s="7"/>
       <c r="E87" s="18"/>
       <c r="F87" s="18"/>
@@ -4545,7 +4558,7 @@
     <row r="88" ht="17.25" customHeight="1">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
-      <c r="C88" s="82"/>
+      <c r="C88" s="81"/>
       <c r="D88" s="7"/>
       <c r="E88" s="18"/>
       <c r="F88" s="18"/>
@@ -4575,7 +4588,7 @@
     <row r="89" ht="17.25" customHeight="1">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
-      <c r="C89" s="82"/>
+      <c r="C89" s="81"/>
       <c r="D89" s="7"/>
       <c r="E89" s="18"/>
       <c r="F89" s="18"/>
@@ -4605,7 +4618,7 @@
     <row r="90" ht="17.25" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
-      <c r="C90" s="82"/>
+      <c r="C90" s="81"/>
       <c r="D90" s="7"/>
       <c r="E90" s="18"/>
       <c r="F90" s="18"/>
@@ -4635,7 +4648,7 @@
     <row r="91" ht="17.25" customHeight="1">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
-      <c r="C91" s="82"/>
+      <c r="C91" s="81"/>
       <c r="D91" s="7"/>
       <c r="E91" s="18"/>
       <c r="F91" s="18"/>
@@ -4665,7 +4678,7 @@
     <row r="92" ht="17.25" customHeight="1">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
-      <c r="C92" s="82"/>
+      <c r="C92" s="81"/>
       <c r="D92" s="7"/>
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
@@ -4695,7 +4708,7 @@
     <row r="93" ht="17.25" customHeight="1">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
-      <c r="C93" s="82"/>
+      <c r="C93" s="81"/>
       <c r="D93" s="7"/>
       <c r="E93" s="18"/>
       <c r="F93" s="18"/>
@@ -4725,7 +4738,7 @@
     <row r="94" ht="17.25" customHeight="1">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
-      <c r="C94" s="82"/>
+      <c r="C94" s="81"/>
       <c r="D94" s="7"/>
       <c r="E94" s="18"/>
       <c r="F94" s="18"/>
@@ -4755,7 +4768,7 @@
     <row r="95" ht="17.25" customHeight="1">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
-      <c r="C95" s="82"/>
+      <c r="C95" s="81"/>
       <c r="D95" s="7"/>
       <c r="E95" s="18"/>
       <c r="F95" s="18"/>
@@ -4785,7 +4798,7 @@
     <row r="96" ht="17.25" customHeight="1">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
-      <c r="C96" s="82"/>
+      <c r="C96" s="81"/>
       <c r="D96" s="7"/>
       <c r="E96" s="18"/>
       <c r="F96" s="18"/>
@@ -4815,7 +4828,7 @@
     <row r="97" ht="17.25" customHeight="1">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
-      <c r="C97" s="82"/>
+      <c r="C97" s="81"/>
       <c r="D97" s="7"/>
       <c r="E97" s="18"/>
       <c r="F97" s="18"/>
@@ -4845,7 +4858,7 @@
     <row r="98" ht="17.25" customHeight="1">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
-      <c r="C98" s="82"/>
+      <c r="C98" s="81"/>
       <c r="D98" s="7"/>
       <c r="E98" s="18"/>
       <c r="F98" s="18"/>
@@ -4875,7 +4888,7 @@
     <row r="99" ht="17.25" customHeight="1">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
-      <c r="C99" s="82"/>
+      <c r="C99" s="81"/>
       <c r="D99" s="7"/>
       <c r="E99" s="18"/>
       <c r="F99" s="18"/>
@@ -4905,7 +4918,7 @@
     <row r="100" ht="17.25" customHeight="1">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
-      <c r="C100" s="82"/>
+      <c r="C100" s="81"/>
       <c r="D100" s="7"/>
       <c r="E100" s="18"/>
       <c r="F100" s="18"/>
@@ -4935,7 +4948,7 @@
     <row r="101" ht="17.25" customHeight="1">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101" s="82"/>
+      <c r="C101" s="81"/>
       <c r="D101" s="7"/>
       <c r="E101" s="18"/>
       <c r="F101" s="18"/>
@@ -4965,7 +4978,7 @@
     <row r="102" ht="17.25" customHeight="1">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102" s="82"/>
+      <c r="C102" s="81"/>
       <c r="D102" s="7"/>
       <c r="E102" s="18"/>
       <c r="F102" s="18"/>
@@ -4995,7 +5008,7 @@
     <row r="103" ht="17.25" customHeight="1">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
-      <c r="C103" s="82"/>
+      <c r="C103" s="81"/>
       <c r="D103" s="7"/>
       <c r="E103" s="18"/>
       <c r="F103" s="18"/>
@@ -5025,7 +5038,7 @@
     <row r="104" ht="17.25" customHeight="1">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
-      <c r="C104" s="82"/>
+      <c r="C104" s="81"/>
       <c r="D104" s="7"/>
       <c r="E104" s="18"/>
       <c r="F104" s="18"/>
@@ -5055,7 +5068,7 @@
     <row r="105" ht="17.25" customHeight="1">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
-      <c r="C105" s="82"/>
+      <c r="C105" s="81"/>
       <c r="D105" s="7"/>
       <c r="E105" s="18"/>
       <c r="F105" s="18"/>
@@ -5085,7 +5098,7 @@
     <row r="106" ht="17.25" customHeight="1">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
-      <c r="C106" s="82"/>
+      <c r="C106" s="81"/>
       <c r="D106" s="7"/>
       <c r="E106" s="18"/>
       <c r="F106" s="18"/>
@@ -5115,7 +5128,7 @@
     <row r="107" ht="17.25" customHeight="1">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
-      <c r="C107" s="82"/>
+      <c r="C107" s="81"/>
       <c r="D107" s="7"/>
       <c r="E107" s="18"/>
       <c r="F107" s="18"/>
@@ -5145,7 +5158,7 @@
     <row r="108" ht="17.25" customHeight="1">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
-      <c r="C108" s="82"/>
+      <c r="C108" s="81"/>
       <c r="D108" s="7"/>
       <c r="E108" s="18"/>
       <c r="F108" s="18"/>
@@ -5175,7 +5188,7 @@
     <row r="109" ht="17.25" customHeight="1">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
-      <c r="C109" s="82"/>
+      <c r="C109" s="81"/>
       <c r="D109" s="7"/>
       <c r="E109" s="18"/>
       <c r="F109" s="18"/>
@@ -5205,7 +5218,7 @@
     <row r="110" ht="17.25" customHeight="1">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
-      <c r="C110" s="82"/>
+      <c r="C110" s="81"/>
       <c r="D110" s="7"/>
       <c r="E110" s="18"/>
       <c r="F110" s="18"/>
@@ -5235,7 +5248,7 @@
     <row r="111" ht="17.25" customHeight="1">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
-      <c r="C111" s="82"/>
+      <c r="C111" s="81"/>
       <c r="D111" s="7"/>
       <c r="E111" s="18"/>
       <c r="F111" s="18"/>
@@ -5265,7 +5278,7 @@
     <row r="112" ht="17.25" customHeight="1">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
-      <c r="C112" s="82"/>
+      <c r="C112" s="81"/>
       <c r="D112" s="7"/>
       <c r="E112" s="18"/>
       <c r="F112" s="18"/>
@@ -5295,7 +5308,7 @@
     <row r="113" ht="17.25" customHeight="1">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
-      <c r="C113" s="82"/>
+      <c r="C113" s="81"/>
       <c r="D113" s="7"/>
       <c r="E113" s="18"/>
       <c r="F113" s="18"/>
@@ -5325,7 +5338,7 @@
     <row r="114" ht="17.25" customHeight="1">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
-      <c r="C114" s="82"/>
+      <c r="C114" s="81"/>
       <c r="D114" s="7"/>
       <c r="E114" s="18"/>
       <c r="F114" s="18"/>
@@ -5355,7 +5368,7 @@
     <row r="115" ht="17.25" customHeight="1">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
-      <c r="C115" s="82"/>
+      <c r="C115" s="81"/>
       <c r="D115" s="7"/>
       <c r="E115" s="18"/>
       <c r="F115" s="18"/>
@@ -5385,7 +5398,7 @@
     <row r="116" ht="17.25" customHeight="1">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
-      <c r="C116" s="82"/>
+      <c r="C116" s="81"/>
       <c r="D116" s="7"/>
       <c r="E116" s="18"/>
       <c r="F116" s="18"/>
@@ -5415,7 +5428,7 @@
     <row r="117" ht="17.25" customHeight="1">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
-      <c r="C117" s="82"/>
+      <c r="C117" s="81"/>
       <c r="D117" s="7"/>
       <c r="E117" s="18"/>
       <c r="F117" s="18"/>
@@ -5445,7 +5458,7 @@
     <row r="118" ht="17.25" customHeight="1">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
-      <c r="C118" s="82"/>
+      <c r="C118" s="81"/>
       <c r="D118" s="7"/>
       <c r="E118" s="18"/>
       <c r="F118" s="18"/>
@@ -5475,7 +5488,7 @@
     <row r="119" ht="17.25" customHeight="1">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
-      <c r="C119" s="82"/>
+      <c r="C119" s="81"/>
       <c r="D119" s="7"/>
       <c r="E119" s="18"/>
       <c r="F119" s="18"/>
@@ -5505,7 +5518,7 @@
     <row r="120" ht="17.25" customHeight="1">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
-      <c r="C120" s="82"/>
+      <c r="C120" s="81"/>
       <c r="D120" s="7"/>
       <c r="E120" s="18"/>
       <c r="F120" s="18"/>
@@ -5535,7 +5548,7 @@
     <row r="121" ht="17.25" customHeight="1">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
-      <c r="C121" s="82"/>
+      <c r="C121" s="81"/>
       <c r="D121" s="7"/>
       <c r="E121" s="18"/>
       <c r="F121" s="18"/>
@@ -5565,7 +5578,7 @@
     <row r="122" ht="17.25" customHeight="1">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
-      <c r="C122" s="82"/>
+      <c r="C122" s="81"/>
       <c r="D122" s="7"/>
       <c r="E122" s="18"/>
       <c r="F122" s="18"/>
@@ -5595,7 +5608,7 @@
     <row r="123" ht="17.25" customHeight="1">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
-      <c r="C123" s="82"/>
+      <c r="C123" s="81"/>
       <c r="D123" s="7"/>
       <c r="E123" s="18"/>
       <c r="F123" s="18"/>
@@ -5625,7 +5638,7 @@
     <row r="124" ht="17.25" customHeight="1">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
-      <c r="C124" s="82"/>
+      <c r="C124" s="81"/>
       <c r="D124" s="7"/>
       <c r="E124" s="18"/>
       <c r="F124" s="18"/>
@@ -5655,7 +5668,7 @@
     <row r="125" ht="17.25" customHeight="1">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
-      <c r="C125" s="82"/>
+      <c r="C125" s="81"/>
       <c r="D125" s="7"/>
       <c r="E125" s="18"/>
       <c r="F125" s="18"/>
@@ -5685,7 +5698,7 @@
     <row r="126" ht="17.25" customHeight="1">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
-      <c r="C126" s="82"/>
+      <c r="C126" s="81"/>
       <c r="D126" s="7"/>
       <c r="E126" s="18"/>
       <c r="F126" s="18"/>
@@ -5715,7 +5728,7 @@
     <row r="127" ht="17.25" customHeight="1">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
-      <c r="C127" s="82"/>
+      <c r="C127" s="81"/>
       <c r="D127" s="7"/>
       <c r="E127" s="18"/>
       <c r="F127" s="18"/>
@@ -5745,7 +5758,7 @@
     <row r="128" ht="17.25" customHeight="1">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
-      <c r="C128" s="82"/>
+      <c r="C128" s="81"/>
       <c r="D128" s="7"/>
       <c r="E128" s="18"/>
       <c r="F128" s="18"/>
@@ -5775,7 +5788,7 @@
     <row r="129" ht="17.25" customHeight="1">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
-      <c r="C129" s="82"/>
+      <c r="C129" s="81"/>
       <c r="D129" s="7"/>
       <c r="E129" s="18"/>
       <c r="F129" s="18"/>
@@ -5805,7 +5818,7 @@
     <row r="130" ht="17.25" customHeight="1">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
-      <c r="C130" s="82"/>
+      <c r="C130" s="81"/>
       <c r="D130" s="7"/>
       <c r="E130" s="18"/>
       <c r="F130" s="18"/>
@@ -5835,7 +5848,7 @@
     <row r="131" ht="17.25" customHeight="1">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
-      <c r="C131" s="82"/>
+      <c r="C131" s="81"/>
       <c r="D131" s="7"/>
       <c r="E131" s="18"/>
       <c r="F131" s="18"/>
@@ -5865,7 +5878,7 @@
     <row r="132" ht="17.25" customHeight="1">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
-      <c r="C132" s="82"/>
+      <c r="C132" s="81"/>
       <c r="D132" s="7"/>
       <c r="E132" s="18"/>
       <c r="F132" s="18"/>
@@ -5895,7 +5908,7 @@
     <row r="133" ht="17.25" customHeight="1">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
-      <c r="C133" s="82"/>
+      <c r="C133" s="81"/>
       <c r="D133" s="7"/>
       <c r="E133" s="18"/>
       <c r="F133" s="18"/>
@@ -5925,7 +5938,7 @@
     <row r="134" ht="17.25" customHeight="1">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
-      <c r="C134" s="82"/>
+      <c r="C134" s="81"/>
       <c r="D134" s="7"/>
       <c r="E134" s="18"/>
       <c r="F134" s="18"/>
@@ -5955,7 +5968,7 @@
     <row r="135" ht="17.25" customHeight="1">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
-      <c r="C135" s="82"/>
+      <c r="C135" s="81"/>
       <c r="D135" s="7"/>
       <c r="E135" s="18"/>
       <c r="F135" s="18"/>
@@ -5985,7 +5998,7 @@
     <row r="136" ht="17.25" customHeight="1">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
-      <c r="C136" s="82"/>
+      <c r="C136" s="81"/>
       <c r="D136" s="7"/>
       <c r="E136" s="18"/>
       <c r="F136" s="18"/>
@@ -6015,7 +6028,7 @@
     <row r="137" ht="17.25" customHeight="1">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
-      <c r="C137" s="82"/>
+      <c r="C137" s="81"/>
       <c r="D137" s="7"/>
       <c r="E137" s="18"/>
       <c r="F137" s="18"/>
@@ -6045,7 +6058,7 @@
     <row r="138" ht="17.25" customHeight="1">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
-      <c r="C138" s="82"/>
+      <c r="C138" s="81"/>
       <c r="D138" s="7"/>
       <c r="E138" s="18"/>
       <c r="F138" s="18"/>
@@ -6075,7 +6088,7 @@
     <row r="139" ht="17.25" customHeight="1">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
-      <c r="C139" s="82"/>
+      <c r="C139" s="81"/>
       <c r="D139" s="7"/>
       <c r="E139" s="18"/>
       <c r="F139" s="18"/>
@@ -6105,7 +6118,7 @@
     <row r="140" ht="17.25" customHeight="1">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="82"/>
+      <c r="C140" s="81"/>
       <c r="D140" s="7"/>
       <c r="E140" s="18"/>
       <c r="F140" s="18"/>
@@ -6135,7 +6148,7 @@
     <row r="141" ht="17.25" customHeight="1">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
-      <c r="C141" s="82"/>
+      <c r="C141" s="81"/>
       <c r="D141" s="7"/>
       <c r="E141" s="18"/>
       <c r="F141" s="18"/>
@@ -6165,7 +6178,7 @@
     <row r="142" ht="17.25" customHeight="1">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
-      <c r="C142" s="82"/>
+      <c r="C142" s="81"/>
       <c r="D142" s="7"/>
       <c r="E142" s="18"/>
       <c r="F142" s="18"/>
@@ -6195,7 +6208,7 @@
     <row r="143" ht="17.25" customHeight="1">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
-      <c r="C143" s="82"/>
+      <c r="C143" s="81"/>
       <c r="D143" s="7"/>
       <c r="E143" s="18"/>
       <c r="F143" s="18"/>
@@ -6225,7 +6238,7 @@
     <row r="144" ht="17.25" customHeight="1">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
-      <c r="C144" s="82"/>
+      <c r="C144" s="81"/>
       <c r="D144" s="7"/>
       <c r="E144" s="18"/>
       <c r="F144" s="18"/>
@@ -6255,7 +6268,7 @@
     <row r="145" ht="17.25" customHeight="1">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
-      <c r="C145" s="82"/>
+      <c r="C145" s="81"/>
       <c r="D145" s="7"/>
       <c r="E145" s="18"/>
       <c r="F145" s="18"/>
@@ -6285,7 +6298,7 @@
     <row r="146" ht="17.25" customHeight="1">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="82"/>
+      <c r="C146" s="81"/>
       <c r="D146" s="7"/>
       <c r="E146" s="18"/>
       <c r="F146" s="18"/>
@@ -6315,7 +6328,7 @@
     <row r="147" ht="17.25" customHeight="1">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
-      <c r="C147" s="82"/>
+      <c r="C147" s="81"/>
       <c r="D147" s="7"/>
       <c r="E147" s="18"/>
       <c r="F147" s="18"/>
@@ -6345,7 +6358,7 @@
     <row r="148" ht="17.25" customHeight="1">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
-      <c r="C148" s="82"/>
+      <c r="C148" s="81"/>
       <c r="D148" s="7"/>
       <c r="E148" s="18"/>
       <c r="F148" s="18"/>
@@ -6375,7 +6388,7 @@
     <row r="149" ht="17.25" customHeight="1">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="82"/>
+      <c r="C149" s="81"/>
       <c r="D149" s="7"/>
       <c r="E149" s="18"/>
       <c r="F149" s="18"/>
@@ -6405,7 +6418,7 @@
     <row r="150" ht="17.25" customHeight="1">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
-      <c r="C150" s="82"/>
+      <c r="C150" s="81"/>
       <c r="D150" s="7"/>
       <c r="E150" s="18"/>
       <c r="F150" s="18"/>
@@ -6435,7 +6448,7 @@
     <row r="151" ht="17.25" customHeight="1">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
-      <c r="C151" s="82"/>
+      <c r="C151" s="81"/>
       <c r="D151" s="7"/>
       <c r="E151" s="18"/>
       <c r="F151" s="18"/>
@@ -6465,7 +6478,7 @@
     <row r="152" ht="17.25" customHeight="1">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
-      <c r="C152" s="82"/>
+      <c r="C152" s="81"/>
       <c r="D152" s="7"/>
       <c r="E152" s="18"/>
       <c r="F152" s="18"/>
@@ -6495,7 +6508,7 @@
     <row r="153" ht="17.25" customHeight="1">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
-      <c r="C153" s="82"/>
+      <c r="C153" s="81"/>
       <c r="D153" s="7"/>
       <c r="E153" s="18"/>
       <c r="F153" s="18"/>
@@ -6525,7 +6538,7 @@
     <row r="154" ht="17.25" customHeight="1">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
-      <c r="C154" s="82"/>
+      <c r="C154" s="81"/>
       <c r="D154" s="7"/>
       <c r="E154" s="18"/>
       <c r="F154" s="18"/>
@@ -6555,7 +6568,7 @@
     <row r="155" ht="17.25" customHeight="1">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
-      <c r="C155" s="82"/>
+      <c r="C155" s="81"/>
       <c r="D155" s="7"/>
       <c r="E155" s="18"/>
       <c r="F155" s="18"/>
@@ -6585,7 +6598,7 @@
     <row r="156" ht="17.25" customHeight="1">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
-      <c r="C156" s="82"/>
+      <c r="C156" s="81"/>
       <c r="D156" s="7"/>
       <c r="E156" s="18"/>
       <c r="F156" s="18"/>
@@ -6615,7 +6628,7 @@
     <row r="157" ht="17.25" customHeight="1">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
-      <c r="C157" s="82"/>
+      <c r="C157" s="81"/>
       <c r="D157" s="7"/>
       <c r="E157" s="18"/>
       <c r="F157" s="18"/>
@@ -6645,7 +6658,7 @@
     <row r="158" ht="17.25" customHeight="1">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
-      <c r="C158" s="82"/>
+      <c r="C158" s="81"/>
       <c r="D158" s="7"/>
       <c r="E158" s="18"/>
       <c r="F158" s="18"/>
@@ -6675,7 +6688,7 @@
     <row r="159" ht="17.25" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
-      <c r="C159" s="82"/>
+      <c r="C159" s="81"/>
       <c r="D159" s="7"/>
       <c r="E159" s="18"/>
       <c r="F159" s="18"/>
@@ -6705,7 +6718,7 @@
     <row r="160" ht="17.25" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
-      <c r="C160" s="82"/>
+      <c r="C160" s="81"/>
       <c r="D160" s="7"/>
       <c r="E160" s="18"/>
       <c r="F160" s="18"/>
@@ -6735,7 +6748,7 @@
     <row r="161" ht="17.25" customHeight="1">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
-      <c r="C161" s="82"/>
+      <c r="C161" s="81"/>
       <c r="D161" s="7"/>
       <c r="E161" s="18"/>
       <c r="F161" s="18"/>
@@ -6765,7 +6778,7 @@
     <row r="162" ht="17.25" customHeight="1">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
-      <c r="C162" s="82"/>
+      <c r="C162" s="81"/>
       <c r="D162" s="7"/>
       <c r="E162" s="18"/>
       <c r="F162" s="18"/>
@@ -6795,7 +6808,7 @@
     <row r="163" ht="17.25" customHeight="1">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
-      <c r="C163" s="82"/>
+      <c r="C163" s="81"/>
       <c r="D163" s="7"/>
       <c r="E163" s="18"/>
       <c r="F163" s="18"/>
@@ -6825,7 +6838,7 @@
     <row r="164" ht="17.25" customHeight="1">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
-      <c r="C164" s="82"/>
+      <c r="C164" s="81"/>
       <c r="D164" s="7"/>
       <c r="E164" s="18"/>
       <c r="F164" s="18"/>
@@ -6855,7 +6868,7 @@
     <row r="165" ht="17.25" customHeight="1">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
-      <c r="C165" s="82"/>
+      <c r="C165" s="81"/>
       <c r="D165" s="7"/>
       <c r="E165" s="18"/>
       <c r="F165" s="18"/>
@@ -6885,7 +6898,7 @@
     <row r="166" ht="17.25" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
-      <c r="C166" s="82"/>
+      <c r="C166" s="81"/>
       <c r="D166" s="7"/>
       <c r="E166" s="18"/>
       <c r="F166" s="18"/>
@@ -6915,7 +6928,7 @@
     <row r="167" ht="17.25" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
-      <c r="C167" s="82"/>
+      <c r="C167" s="81"/>
       <c r="D167" s="7"/>
       <c r="E167" s="18"/>
       <c r="F167" s="18"/>
@@ -6945,7 +6958,7 @@
     <row r="168" ht="17.25" customHeight="1">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
-      <c r="C168" s="82"/>
+      <c r="C168" s="81"/>
       <c r="D168" s="7"/>
       <c r="E168" s="18"/>
       <c r="F168" s="18"/>
@@ -6975,7 +6988,7 @@
     <row r="169" ht="17.25" customHeight="1">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
-      <c r="C169" s="82"/>
+      <c r="C169" s="81"/>
       <c r="D169" s="7"/>
       <c r="E169" s="18"/>
       <c r="F169" s="18"/>
@@ -7005,7 +7018,7 @@
     <row r="170" ht="17.25" customHeight="1">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
-      <c r="C170" s="82"/>
+      <c r="C170" s="81"/>
       <c r="D170" s="7"/>
       <c r="E170" s="18"/>
       <c r="F170" s="18"/>
@@ -7035,7 +7048,7 @@
     <row r="171" ht="17.25" customHeight="1">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
-      <c r="C171" s="82"/>
+      <c r="C171" s="81"/>
       <c r="D171" s="7"/>
       <c r="E171" s="18"/>
       <c r="F171" s="18"/>
@@ -7065,7 +7078,7 @@
     <row r="172" ht="17.25" customHeight="1">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
-      <c r="C172" s="82"/>
+      <c r="C172" s="81"/>
       <c r="D172" s="7"/>
       <c r="E172" s="18"/>
       <c r="F172" s="18"/>
@@ -7095,7 +7108,7 @@
     <row r="173" ht="17.25" customHeight="1">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
-      <c r="C173" s="82"/>
+      <c r="C173" s="81"/>
       <c r="D173" s="7"/>
       <c r="E173" s="18"/>
       <c r="F173" s="18"/>
@@ -7125,7 +7138,7 @@
     <row r="174" ht="17.25" customHeight="1">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
-      <c r="C174" s="82"/>
+      <c r="C174" s="81"/>
       <c r="D174" s="7"/>
       <c r="E174" s="18"/>
       <c r="F174" s="18"/>
@@ -7155,7 +7168,7 @@
     <row r="175" ht="17.25" customHeight="1">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
-      <c r="C175" s="82"/>
+      <c r="C175" s="81"/>
       <c r="D175" s="7"/>
       <c r="E175" s="18"/>
       <c r="F175" s="18"/>
@@ -7185,7 +7198,7 @@
     <row r="176" ht="17.25" customHeight="1">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
-      <c r="C176" s="82"/>
+      <c r="C176" s="81"/>
       <c r="D176" s="7"/>
       <c r="E176" s="18"/>
       <c r="F176" s="18"/>
@@ -7215,7 +7228,7 @@
     <row r="177" ht="17.25" customHeight="1">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
-      <c r="C177" s="82"/>
+      <c r="C177" s="81"/>
       <c r="D177" s="7"/>
       <c r="E177" s="18"/>
       <c r="F177" s="18"/>
@@ -7245,7 +7258,7 @@
     <row r="178" ht="17.25" customHeight="1">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
-      <c r="C178" s="82"/>
+      <c r="C178" s="81"/>
       <c r="D178" s="7"/>
       <c r="E178" s="18"/>
       <c r="F178" s="18"/>
@@ -7275,7 +7288,7 @@
     <row r="179" ht="17.25" customHeight="1">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
-      <c r="C179" s="82"/>
+      <c r="C179" s="81"/>
       <c r="D179" s="7"/>
       <c r="E179" s="18"/>
       <c r="F179" s="18"/>
@@ -7305,7 +7318,7 @@
     <row r="180" ht="17.25" customHeight="1">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
-      <c r="C180" s="82"/>
+      <c r="C180" s="81"/>
       <c r="D180" s="7"/>
       <c r="E180" s="18"/>
       <c r="F180" s="18"/>
@@ -7335,7 +7348,7 @@
     <row r="181" ht="17.25" customHeight="1">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
-      <c r="C181" s="82"/>
+      <c r="C181" s="81"/>
       <c r="D181" s="7"/>
       <c r="E181" s="18"/>
       <c r="F181" s="18"/>
@@ -7365,7 +7378,7 @@
     <row r="182" ht="17.25" customHeight="1">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
-      <c r="C182" s="82"/>
+      <c r="C182" s="81"/>
       <c r="D182" s="7"/>
       <c r="E182" s="18"/>
       <c r="F182" s="18"/>
@@ -7395,7 +7408,7 @@
     <row r="183" ht="17.25" customHeight="1">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
-      <c r="C183" s="82"/>
+      <c r="C183" s="81"/>
       <c r="D183" s="7"/>
       <c r="E183" s="18"/>
       <c r="F183" s="18"/>
@@ -7425,7 +7438,7 @@
     <row r="184" ht="17.25" customHeight="1">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
-      <c r="C184" s="82"/>
+      <c r="C184" s="81"/>
       <c r="D184" s="7"/>
       <c r="E184" s="18"/>
       <c r="F184" s="18"/>
@@ -7455,7 +7468,7 @@
     <row r="185" ht="17.25" customHeight="1">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
-      <c r="C185" s="82"/>
+      <c r="C185" s="81"/>
       <c r="D185" s="7"/>
       <c r="E185" s="18"/>
       <c r="F185" s="18"/>
@@ -7485,7 +7498,7 @@
     <row r="186" ht="17.25" customHeight="1">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
-      <c r="C186" s="82"/>
+      <c r="C186" s="81"/>
       <c r="D186" s="7"/>
       <c r="E186" s="18"/>
       <c r="F186" s="18"/>
@@ -7515,7 +7528,7 @@
     <row r="187" ht="17.25" customHeight="1">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
-      <c r="C187" s="82"/>
+      <c r="C187" s="81"/>
       <c r="D187" s="7"/>
       <c r="E187" s="18"/>
       <c r="F187" s="18"/>
@@ -7545,7 +7558,7 @@
     <row r="188" ht="17.25" customHeight="1">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
-      <c r="C188" s="82"/>
+      <c r="C188" s="81"/>
       <c r="D188" s="7"/>
       <c r="E188" s="18"/>
       <c r="F188" s="18"/>
@@ -7575,7 +7588,7 @@
     <row r="189" ht="17.25" customHeight="1">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
-      <c r="C189" s="82"/>
+      <c r="C189" s="81"/>
       <c r="D189" s="7"/>
       <c r="E189" s="18"/>
       <c r="F189" s="18"/>
@@ -7605,7 +7618,7 @@
     <row r="190" ht="17.25" customHeight="1">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
-      <c r="C190" s="82"/>
+      <c r="C190" s="81"/>
       <c r="D190" s="7"/>
       <c r="E190" s="18"/>
       <c r="F190" s="18"/>
@@ -7635,7 +7648,7 @@
     <row r="191" ht="17.25" customHeight="1">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
-      <c r="C191" s="82"/>
+      <c r="C191" s="81"/>
       <c r="D191" s="7"/>
       <c r="E191" s="18"/>
       <c r="F191" s="18"/>
@@ -7665,7 +7678,7 @@
     <row r="192" ht="17.25" customHeight="1">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
-      <c r="C192" s="82"/>
+      <c r="C192" s="81"/>
       <c r="D192" s="7"/>
       <c r="E192" s="18"/>
       <c r="F192" s="18"/>
@@ -7695,7 +7708,7 @@
     <row r="193" ht="17.25" customHeight="1">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
-      <c r="C193" s="82"/>
+      <c r="C193" s="81"/>
       <c r="D193" s="7"/>
       <c r="E193" s="18"/>
       <c r="F193" s="18"/>
@@ -7725,7 +7738,7 @@
     <row r="194" ht="17.25" customHeight="1">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
-      <c r="C194" s="82"/>
+      <c r="C194" s="81"/>
       <c r="D194" s="7"/>
       <c r="E194" s="18"/>
       <c r="F194" s="18"/>
@@ -7755,7 +7768,7 @@
     <row r="195" ht="17.25" customHeight="1">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
-      <c r="C195" s="82"/>
+      <c r="C195" s="81"/>
       <c r="D195" s="7"/>
       <c r="E195" s="18"/>
       <c r="F195" s="18"/>
@@ -7785,7 +7798,7 @@
     <row r="196" ht="17.25" customHeight="1">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
-      <c r="C196" s="82"/>
+      <c r="C196" s="81"/>
       <c r="D196" s="7"/>
       <c r="E196" s="18"/>
       <c r="F196" s="18"/>
@@ -7815,7 +7828,7 @@
     <row r="197" ht="17.25" customHeight="1">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
-      <c r="C197" s="82"/>
+      <c r="C197" s="81"/>
       <c r="D197" s="7"/>
       <c r="E197" s="18"/>
       <c r="F197" s="18"/>
@@ -7845,7 +7858,7 @@
     <row r="198" ht="17.25" customHeight="1">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
-      <c r="C198" s="82"/>
+      <c r="C198" s="81"/>
       <c r="D198" s="7"/>
       <c r="E198" s="18"/>
       <c r="F198" s="18"/>
@@ -7875,7 +7888,7 @@
     <row r="199" ht="17.25" customHeight="1">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
-      <c r="C199" s="82"/>
+      <c r="C199" s="81"/>
       <c r="D199" s="7"/>
       <c r="E199" s="18"/>
       <c r="F199" s="18"/>
@@ -7905,7 +7918,7 @@
     <row r="200" ht="17.25" customHeight="1">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
-      <c r="C200" s="82"/>
+      <c r="C200" s="81"/>
       <c r="D200" s="7"/>
       <c r="E200" s="18"/>
       <c r="F200" s="18"/>
@@ -7935,7 +7948,7 @@
     <row r="201" ht="17.25" customHeight="1">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
-      <c r="C201" s="82"/>
+      <c r="C201" s="81"/>
       <c r="D201" s="7"/>
       <c r="E201" s="18"/>
       <c r="F201" s="18"/>
@@ -7965,7 +7978,7 @@
     <row r="202" ht="17.25" customHeight="1">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
-      <c r="C202" s="82"/>
+      <c r="C202" s="81"/>
       <c r="D202" s="7"/>
       <c r="E202" s="18"/>
       <c r="F202" s="18"/>
@@ -7995,7 +8008,7 @@
     <row r="203" ht="17.25" customHeight="1">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
-      <c r="C203" s="82"/>
+      <c r="C203" s="81"/>
       <c r="D203" s="7"/>
       <c r="E203" s="18"/>
       <c r="F203" s="18"/>
@@ -8025,7 +8038,7 @@
     <row r="204" ht="17.25" customHeight="1">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
-      <c r="C204" s="82"/>
+      <c r="C204" s="81"/>
       <c r="D204" s="7"/>
       <c r="E204" s="18"/>
       <c r="F204" s="18"/>
@@ -8055,7 +8068,7 @@
     <row r="205" ht="17.25" customHeight="1">
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
-      <c r="C205" s="82"/>
+      <c r="C205" s="81"/>
       <c r="D205" s="7"/>
       <c r="E205" s="18"/>
       <c r="F205" s="18"/>
@@ -8085,7 +8098,7 @@
     <row r="206" ht="17.25" customHeight="1">
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
-      <c r="C206" s="82"/>
+      <c r="C206" s="81"/>
       <c r="D206" s="7"/>
       <c r="E206" s="18"/>
       <c r="F206" s="18"/>
@@ -8115,7 +8128,7 @@
     <row r="207" ht="17.25" customHeight="1">
       <c r="A207" s="7"/>
       <c r="B207" s="7"/>
-      <c r="C207" s="82"/>
+      <c r="C207" s="81"/>
       <c r="D207" s="7"/>
       <c r="E207" s="18"/>
       <c r="F207" s="18"/>
@@ -8145,7 +8158,7 @@
     <row r="208" ht="17.25" customHeight="1">
       <c r="A208" s="7"/>
       <c r="B208" s="7"/>
-      <c r="C208" s="82"/>
+      <c r="C208" s="81"/>
       <c r="D208" s="7"/>
       <c r="E208" s="18"/>
       <c r="F208" s="18"/>
@@ -8175,7 +8188,7 @@
     <row r="209" ht="17.25" customHeight="1">
       <c r="A209" s="7"/>
       <c r="B209" s="7"/>
-      <c r="C209" s="82"/>
+      <c r="C209" s="81"/>
       <c r="D209" s="7"/>
       <c r="E209" s="18"/>
       <c r="F209" s="18"/>
@@ -8205,7 +8218,7 @@
     <row r="210" ht="17.25" customHeight="1">
       <c r="A210" s="7"/>
       <c r="B210" s="7"/>
-      <c r="C210" s="82"/>
+      <c r="C210" s="81"/>
       <c r="D210" s="7"/>
       <c r="E210" s="18"/>
       <c r="F210" s="18"/>
@@ -8235,7 +8248,7 @@
     <row r="211" ht="17.25" customHeight="1">
       <c r="A211" s="7"/>
       <c r="B211" s="7"/>
-      <c r="C211" s="82"/>
+      <c r="C211" s="81"/>
       <c r="D211" s="7"/>
       <c r="E211" s="18"/>
       <c r="F211" s="18"/>
@@ -8265,7 +8278,7 @@
     <row r="212" ht="17.25" customHeight="1">
       <c r="A212" s="7"/>
       <c r="B212" s="7"/>
-      <c r="C212" s="82"/>
+      <c r="C212" s="81"/>
       <c r="D212" s="7"/>
       <c r="E212" s="18"/>
       <c r="F212" s="18"/>
@@ -8295,7 +8308,7 @@
     <row r="213" ht="17.25" customHeight="1">
       <c r="A213" s="7"/>
       <c r="B213" s="7"/>
-      <c r="C213" s="82"/>
+      <c r="C213" s="81"/>
       <c r="D213" s="7"/>
       <c r="E213" s="18"/>
       <c r="F213" s="18"/>
@@ -8325,7 +8338,7 @@
     <row r="214" ht="17.25" customHeight="1">
       <c r="A214" s="7"/>
       <c r="B214" s="7"/>
-      <c r="C214" s="82"/>
+      <c r="C214" s="81"/>
       <c r="D214" s="7"/>
       <c r="E214" s="18"/>
       <c r="F214" s="18"/>
@@ -8355,7 +8368,7 @@
     <row r="215" ht="17.25" customHeight="1">
       <c r="A215" s="7"/>
       <c r="B215" s="7"/>
-      <c r="C215" s="82"/>
+      <c r="C215" s="81"/>
       <c r="D215" s="7"/>
       <c r="E215" s="18"/>
       <c r="F215" s="18"/>
@@ -8385,7 +8398,7 @@
     <row r="216" ht="17.25" customHeight="1">
       <c r="A216" s="7"/>
       <c r="B216" s="7"/>
-      <c r="C216" s="82"/>
+      <c r="C216" s="81"/>
       <c r="D216" s="7"/>
       <c r="E216" s="18"/>
       <c r="F216" s="18"/>
@@ -8415,7 +8428,7 @@
     <row r="217" ht="17.25" customHeight="1">
       <c r="A217" s="7"/>
       <c r="B217" s="7"/>
-      <c r="C217" s="82"/>
+      <c r="C217" s="81"/>
       <c r="D217" s="7"/>
       <c r="E217" s="18"/>
       <c r="F217" s="18"/>
@@ -8445,7 +8458,7 @@
     <row r="218" ht="17.25" customHeight="1">
       <c r="A218" s="7"/>
       <c r="B218" s="7"/>
-      <c r="C218" s="82"/>
+      <c r="C218" s="81"/>
       <c r="D218" s="7"/>
       <c r="E218" s="18"/>
       <c r="F218" s="18"/>
@@ -8475,7 +8488,7 @@
     <row r="219" ht="17.25" customHeight="1">
       <c r="A219" s="7"/>
       <c r="B219" s="7"/>
-      <c r="C219" s="82"/>
+      <c r="C219" s="81"/>
       <c r="D219" s="7"/>
       <c r="E219" s="18"/>
       <c r="F219" s="18"/>
@@ -8505,7 +8518,7 @@
     <row r="220" ht="17.25" customHeight="1">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
-      <c r="C220" s="82"/>
+      <c r="C220" s="81"/>
       <c r="D220" s="7"/>
       <c r="E220" s="18"/>
       <c r="F220" s="18"/>
@@ -8535,7 +8548,7 @@
     <row r="221" ht="17.25" customHeight="1">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
-      <c r="C221" s="82"/>
+      <c r="C221" s="81"/>
       <c r="D221" s="7"/>
       <c r="E221" s="18"/>
       <c r="F221" s="18"/>
@@ -8565,7 +8578,7 @@
     <row r="222" ht="17.25" customHeight="1">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
-      <c r="C222" s="82"/>
+      <c r="C222" s="81"/>
       <c r="D222" s="7"/>
       <c r="E222" s="18"/>
       <c r="F222" s="18"/>
@@ -8595,7 +8608,7 @@
     <row r="223" ht="17.25" customHeight="1">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
-      <c r="C223" s="82"/>
+      <c r="C223" s="81"/>
       <c r="D223" s="7"/>
       <c r="E223" s="18"/>
       <c r="F223" s="18"/>
@@ -8625,7 +8638,7 @@
     <row r="224" ht="17.25" customHeight="1">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
-      <c r="C224" s="82"/>
+      <c r="C224" s="81"/>
       <c r="D224" s="7"/>
       <c r="E224" s="18"/>
       <c r="F224" s="18"/>
@@ -8655,7 +8668,7 @@
     <row r="225" ht="17.25" customHeight="1">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
-      <c r="C225" s="82"/>
+      <c r="C225" s="81"/>
       <c r="D225" s="7"/>
       <c r="E225" s="18"/>
       <c r="F225" s="18"/>
@@ -8685,7 +8698,7 @@
     <row r="226" ht="17.25" customHeight="1">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
-      <c r="C226" s="82"/>
+      <c r="C226" s="81"/>
       <c r="D226" s="7"/>
       <c r="E226" s="18"/>
       <c r="F226" s="18"/>
@@ -8715,7 +8728,7 @@
     <row r="227" ht="17.25" customHeight="1">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
-      <c r="C227" s="82"/>
+      <c r="C227" s="81"/>
       <c r="D227" s="7"/>
       <c r="E227" s="18"/>
       <c r="F227" s="18"/>
@@ -8745,7 +8758,7 @@
     <row r="228" ht="17.25" customHeight="1">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
-      <c r="C228" s="82"/>
+      <c r="C228" s="81"/>
       <c r="D228" s="7"/>
       <c r="E228" s="18"/>
       <c r="F228" s="18"/>
@@ -8775,7 +8788,7 @@
     <row r="229" ht="17.25" customHeight="1">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
-      <c r="C229" s="82"/>
+      <c r="C229" s="81"/>
       <c r="D229" s="7"/>
       <c r="E229" s="18"/>
       <c r="F229" s="18"/>
@@ -8805,7 +8818,7 @@
     <row r="230" ht="17.25" customHeight="1">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
-      <c r="C230" s="82"/>
+      <c r="C230" s="81"/>
       <c r="D230" s="7"/>
       <c r="E230" s="18"/>
       <c r="F230" s="18"/>
@@ -8835,7 +8848,7 @@
     <row r="231" ht="17.25" customHeight="1">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
-      <c r="C231" s="82"/>
+      <c r="C231" s="81"/>
       <c r="D231" s="7"/>
       <c r="E231" s="18"/>
       <c r="F231" s="18"/>
@@ -8865,7 +8878,7 @@
     <row r="232" ht="17.25" customHeight="1">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
-      <c r="C232" s="82"/>
+      <c r="C232" s="81"/>
       <c r="D232" s="7"/>
       <c r="E232" s="18"/>
       <c r="F232" s="18"/>
@@ -8895,7 +8908,7 @@
     <row r="233" ht="17.25" customHeight="1">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
-      <c r="C233" s="82"/>
+      <c r="C233" s="81"/>
       <c r="D233" s="7"/>
       <c r="E233" s="18"/>
       <c r="F233" s="18"/>
@@ -8925,7 +8938,7 @@
     <row r="234" ht="17.25" customHeight="1">
       <c r="A234" s="7"/>
       <c r="B234" s="7"/>
-      <c r="C234" s="82"/>
+      <c r="C234" s="81"/>
       <c r="D234" s="7"/>
       <c r="E234" s="18"/>
       <c r="F234" s="18"/>
@@ -8955,7 +8968,7 @@
     <row r="235" ht="17.25" customHeight="1">
       <c r="A235" s="7"/>
       <c r="B235" s="7"/>
-      <c r="C235" s="82"/>
+      <c r="C235" s="81"/>
       <c r="D235" s="7"/>
       <c r="E235" s="18"/>
       <c r="F235" s="18"/>
@@ -8985,7 +8998,7 @@
     <row r="236" ht="17.25" customHeight="1">
       <c r="A236" s="7"/>
       <c r="B236" s="7"/>
-      <c r="C236" s="82"/>
+      <c r="C236" s="81"/>
       <c r="D236" s="7"/>
       <c r="E236" s="18"/>
       <c r="F236" s="18"/>
@@ -9015,7 +9028,7 @@
     <row r="237" ht="17.25" customHeight="1">
       <c r="A237" s="7"/>
       <c r="B237" s="7"/>
-      <c r="C237" s="82"/>
+      <c r="C237" s="81"/>
       <c r="D237" s="7"/>
       <c r="E237" s="18"/>
       <c r="F237" s="18"/>
@@ -9045,7 +9058,7 @@
     <row r="238" ht="17.25" customHeight="1">
       <c r="A238" s="7"/>
       <c r="B238" s="7"/>
-      <c r="C238" s="82"/>
+      <c r="C238" s="81"/>
       <c r="D238" s="7"/>
       <c r="E238" s="18"/>
       <c r="F238" s="18"/>
@@ -9075,7 +9088,7 @@
     <row r="239" ht="17.25" customHeight="1">
       <c r="A239" s="7"/>
       <c r="B239" s="7"/>
-      <c r="C239" s="82"/>
+      <c r="C239" s="81"/>
       <c r="D239" s="7"/>
       <c r="E239" s="18"/>
       <c r="F239" s="18"/>
@@ -9105,7 +9118,7 @@
     <row r="240" ht="17.25" customHeight="1">
       <c r="A240" s="7"/>
       <c r="B240" s="7"/>
-      <c r="C240" s="82"/>
+      <c r="C240" s="81"/>
       <c r="D240" s="7"/>
       <c r="E240" s="18"/>
       <c r="F240" s="18"/>
@@ -9135,7 +9148,7 @@
     <row r="241" ht="17.25" customHeight="1">
       <c r="A241" s="7"/>
       <c r="B241" s="7"/>
-      <c r="C241" s="82"/>
+      <c r="C241" s="81"/>
       <c r="D241" s="7"/>
       <c r="E241" s="18"/>
       <c r="F241" s="18"/>
@@ -9165,7 +9178,7 @@
     <row r="242" ht="17.25" customHeight="1">
       <c r="A242" s="7"/>
       <c r="B242" s="7"/>
-      <c r="C242" s="82"/>
+      <c r="C242" s="81"/>
       <c r="D242" s="7"/>
       <c r="E242" s="18"/>
       <c r="F242" s="18"/>
@@ -9195,7 +9208,7 @@
     <row r="243" ht="17.25" customHeight="1">
       <c r="A243" s="7"/>
       <c r="B243" s="7"/>
-      <c r="C243" s="82"/>
+      <c r="C243" s="81"/>
       <c r="D243" s="7"/>
       <c r="E243" s="18"/>
       <c r="F243" s="18"/>
@@ -9225,7 +9238,7 @@
     <row r="244" ht="17.25" customHeight="1">
       <c r="A244" s="7"/>
       <c r="B244" s="7"/>
-      <c r="C244" s="82"/>
+      <c r="C244" s="81"/>
       <c r="D244" s="7"/>
       <c r="E244" s="18"/>
       <c r="F244" s="18"/>
@@ -9255,7 +9268,7 @@
     <row r="245" ht="17.25" customHeight="1">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
-      <c r="C245" s="82"/>
+      <c r="C245" s="81"/>
       <c r="D245" s="7"/>
       <c r="E245" s="18"/>
       <c r="F245" s="18"/>
@@ -9285,7 +9298,7 @@
     <row r="246" ht="17.25" customHeight="1">
       <c r="A246" s="7"/>
       <c r="B246" s="7"/>
-      <c r="C246" s="82"/>
+      <c r="C246" s="81"/>
       <c r="D246" s="7"/>
       <c r="E246" s="18"/>
       <c r="F246" s="18"/>
@@ -9315,7 +9328,7 @@
     <row r="247" ht="17.25" customHeight="1">
       <c r="A247" s="7"/>
       <c r="B247" s="7"/>
-      <c r="C247" s="82"/>
+      <c r="C247" s="81"/>
       <c r="D247" s="7"/>
       <c r="E247" s="18"/>
       <c r="F247" s="18"/>
@@ -9345,7 +9358,7 @@
     <row r="248" ht="17.25" customHeight="1">
       <c r="A248" s="7"/>
       <c r="B248" s="7"/>
-      <c r="C248" s="82"/>
+      <c r="C248" s="81"/>
       <c r="D248" s="7"/>
       <c r="E248" s="18"/>
       <c r="F248" s="18"/>
@@ -9375,7 +9388,7 @@
     <row r="249" ht="17.25" customHeight="1">
       <c r="A249" s="7"/>
       <c r="B249" s="7"/>
-      <c r="C249" s="82"/>
+      <c r="C249" s="81"/>
       <c r="D249" s="7"/>
       <c r="E249" s="18"/>
       <c r="F249" s="18"/>
@@ -9405,7 +9418,7 @@
     <row r="250" ht="17.25" customHeight="1">
       <c r="A250" s="7"/>
       <c r="B250" s="7"/>
-      <c r="C250" s="82"/>
+      <c r="C250" s="81"/>
       <c r="D250" s="7"/>
       <c r="E250" s="18"/>
       <c r="F250" s="18"/>
@@ -9435,7 +9448,7 @@
     <row r="251" ht="17.25" customHeight="1">
       <c r="A251" s="7"/>
       <c r="B251" s="7"/>
-      <c r="C251" s="82"/>
+      <c r="C251" s="81"/>
       <c r="D251" s="7"/>
       <c r="E251" s="18"/>
       <c r="F251" s="18"/>
@@ -9465,7 +9478,7 @@
     <row r="252" ht="17.25" customHeight="1">
       <c r="A252" s="7"/>
       <c r="B252" s="7"/>
-      <c r="C252" s="82"/>
+      <c r="C252" s="81"/>
       <c r="D252" s="7"/>
       <c r="E252" s="18"/>
       <c r="F252" s="18"/>
@@ -9495,7 +9508,7 @@
     <row r="253" ht="17.25" customHeight="1">
       <c r="A253" s="7"/>
       <c r="B253" s="7"/>
-      <c r="C253" s="82"/>
+      <c r="C253" s="81"/>
       <c r="D253" s="7"/>
       <c r="E253" s="18"/>
       <c r="F253" s="18"/>
@@ -9525,7 +9538,7 @@
     <row r="254" ht="17.25" customHeight="1">
       <c r="A254" s="7"/>
       <c r="B254" s="7"/>
-      <c r="C254" s="82"/>
+      <c r="C254" s="81"/>
       <c r="D254" s="7"/>
       <c r="E254" s="18"/>
       <c r="F254" s="18"/>
@@ -9555,7 +9568,7 @@
     <row r="255" ht="17.25" customHeight="1">
       <c r="A255" s="7"/>
       <c r="B255" s="7"/>
-      <c r="C255" s="82"/>
+      <c r="C255" s="81"/>
       <c r="D255" s="7"/>
       <c r="E255" s="18"/>
       <c r="F255" s="18"/>
@@ -9585,7 +9598,7 @@
     <row r="256" ht="17.25" customHeight="1">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
-      <c r="C256" s="82"/>
+      <c r="C256" s="81"/>
       <c r="D256" s="7"/>
       <c r="E256" s="18"/>
       <c r="F256" s="18"/>
@@ -9615,7 +9628,7 @@
     <row r="257" ht="17.25" customHeight="1">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
-      <c r="C257" s="82"/>
+      <c r="C257" s="81"/>
       <c r="D257" s="7"/>
       <c r="E257" s="18"/>
       <c r="F257" s="18"/>
@@ -9645,7 +9658,7 @@
     <row r="258" ht="17.25" customHeight="1">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
-      <c r="C258" s="82"/>
+      <c r="C258" s="81"/>
       <c r="D258" s="7"/>
       <c r="E258" s="18"/>
       <c r="F258" s="18"/>
@@ -9675,7 +9688,7 @@
     <row r="259" ht="17.25" customHeight="1">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
-      <c r="C259" s="82"/>
+      <c r="C259" s="81"/>
       <c r="D259" s="7"/>
       <c r="E259" s="18"/>
       <c r="F259" s="18"/>
@@ -9705,7 +9718,7 @@
     <row r="260" ht="17.25" customHeight="1">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
-      <c r="C260" s="82"/>
+      <c r="C260" s="81"/>
       <c r="D260" s="7"/>
       <c r="E260" s="18"/>
       <c r="F260" s="18"/>
@@ -9735,7 +9748,7 @@
     <row r="261" ht="17.25" customHeight="1">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
-      <c r="C261" s="82"/>
+      <c r="C261" s="81"/>
       <c r="D261" s="7"/>
       <c r="E261" s="18"/>
       <c r="F261" s="18"/>
@@ -9765,7 +9778,7 @@
     <row r="262" ht="17.25" customHeight="1">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
-      <c r="C262" s="82"/>
+      <c r="C262" s="81"/>
       <c r="D262" s="7"/>
       <c r="E262" s="18"/>
       <c r="F262" s="18"/>
@@ -9795,7 +9808,7 @@
     <row r="263" ht="17.25" customHeight="1">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
-      <c r="C263" s="82"/>
+      <c r="C263" s="81"/>
       <c r="D263" s="7"/>
       <c r="E263" s="18"/>
       <c r="F263" s="18"/>
@@ -9825,7 +9838,7 @@
     <row r="264" ht="17.25" customHeight="1">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
-      <c r="C264" s="82"/>
+      <c r="C264" s="81"/>
       <c r="D264" s="7"/>
       <c r="E264" s="18"/>
       <c r="F264" s="18"/>
@@ -9855,7 +9868,7 @@
     <row r="265" ht="17.25" customHeight="1">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
-      <c r="C265" s="82"/>
+      <c r="C265" s="81"/>
       <c r="D265" s="7"/>
       <c r="E265" s="18"/>
       <c r="F265" s="18"/>
@@ -9885,7 +9898,7 @@
     <row r="266" ht="17.25" customHeight="1">
       <c r="A266" s="7"/>
       <c r="B266" s="7"/>
-      <c r="C266" s="82"/>
+      <c r="C266" s="81"/>
       <c r="D266" s="7"/>
       <c r="E266" s="18"/>
       <c r="F266" s="18"/>
@@ -9915,7 +9928,7 @@
     <row r="267" ht="17.25" customHeight="1">
       <c r="A267" s="7"/>
       <c r="B267" s="7"/>
-      <c r="C267" s="82"/>
+      <c r="C267" s="81"/>
       <c r="D267" s="7"/>
       <c r="E267" s="18"/>
       <c r="F267" s="18"/>
@@ -9945,7 +9958,7 @@
     <row r="268" ht="17.25" customHeight="1">
       <c r="A268" s="7"/>
       <c r="B268" s="7"/>
-      <c r="C268" s="82"/>
+      <c r="C268" s="81"/>
       <c r="D268" s="7"/>
       <c r="E268" s="18"/>
       <c r="F268" s="18"/>
@@ -9975,7 +9988,7 @@
     <row r="269" ht="17.25" customHeight="1">
       <c r="A269" s="7"/>
       <c r="B269" s="7"/>
-      <c r="C269" s="82"/>
+      <c r="C269" s="81"/>
       <c r="D269" s="7"/>
       <c r="E269" s="18"/>
       <c r="F269" s="18"/>
@@ -10005,7 +10018,7 @@
     <row r="270" ht="17.25" customHeight="1">
       <c r="A270" s="7"/>
       <c r="B270" s="7"/>
-      <c r="C270" s="82"/>
+      <c r="C270" s="81"/>
       <c r="D270" s="7"/>
       <c r="E270" s="18"/>
       <c r="F270" s="18"/>
@@ -10035,7 +10048,7 @@
     <row r="271" ht="17.25" customHeight="1">
       <c r="A271" s="7"/>
       <c r="B271" s="7"/>
-      <c r="C271" s="82"/>
+      <c r="C271" s="81"/>
       <c r="D271" s="7"/>
       <c r="E271" s="18"/>
       <c r="F271" s="18"/>
@@ -10065,7 +10078,7 @@
     <row r="272" ht="17.25" customHeight="1">
       <c r="A272" s="7"/>
       <c r="B272" s="7"/>
-      <c r="C272" s="82"/>
+      <c r="C272" s="81"/>
       <c r="D272" s="7"/>
       <c r="E272" s="18"/>
       <c r="F272" s="18"/>
@@ -10095,7 +10108,7 @@
     <row r="273" ht="17.25" customHeight="1">
       <c r="A273" s="7"/>
       <c r="B273" s="7"/>
-      <c r="C273" s="82"/>
+      <c r="C273" s="81"/>
       <c r="D273" s="7"/>
       <c r="E273" s="18"/>
       <c r="F273" s="18"/>
@@ -10125,7 +10138,7 @@
     <row r="274" ht="17.25" customHeight="1">
       <c r="A274" s="7"/>
       <c r="B274" s="7"/>
-      <c r="C274" s="82"/>
+      <c r="C274" s="81"/>
       <c r="D274" s="7"/>
       <c r="E274" s="18"/>
       <c r="F274" s="18"/>
@@ -10155,7 +10168,7 @@
     <row r="275" ht="17.25" customHeight="1">
       <c r="A275" s="7"/>
       <c r="B275" s="7"/>
-      <c r="C275" s="82"/>
+      <c r="C275" s="81"/>
       <c r="D275" s="7"/>
       <c r="E275" s="18"/>
       <c r="F275" s="18"/>
@@ -10185,7 +10198,7 @@
     <row r="276" ht="17.25" customHeight="1">
       <c r="A276" s="7"/>
       <c r="B276" s="7"/>
-      <c r="C276" s="82"/>
+      <c r="C276" s="81"/>
       <c r="D276" s="7"/>
       <c r="E276" s="18"/>
       <c r="F276" s="18"/>
@@ -10215,7 +10228,7 @@
     <row r="277" ht="17.25" customHeight="1">
       <c r="A277" s="7"/>
       <c r="B277" s="7"/>
-      <c r="C277" s="82"/>
+      <c r="C277" s="81"/>
       <c r="D277" s="7"/>
       <c r="E277" s="18"/>
       <c r="F277" s="18"/>
@@ -10245,7 +10258,7 @@
     <row r="278" ht="17.25" customHeight="1">
       <c r="A278" s="7"/>
       <c r="B278" s="7"/>
-      <c r="C278" s="82"/>
+      <c r="C278" s="81"/>
       <c r="D278" s="7"/>
       <c r="E278" s="18"/>
       <c r="F278" s="18"/>
@@ -10275,7 +10288,7 @@
     <row r="279" ht="17.25" customHeight="1">
       <c r="A279" s="7"/>
       <c r="B279" s="7"/>
-      <c r="C279" s="82"/>
+      <c r="C279" s="81"/>
       <c r="D279" s="7"/>
       <c r="E279" s="18"/>
       <c r="F279" s="18"/>
@@ -10305,7 +10318,7 @@
     <row r="280" ht="17.25" customHeight="1">
       <c r="A280" s="7"/>
       <c r="B280" s="7"/>
-      <c r="C280" s="82"/>
+      <c r="C280" s="81"/>
       <c r="D280" s="7"/>
       <c r="E280" s="18"/>
       <c r="F280" s="18"/>
@@ -10335,7 +10348,7 @@
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="7"/>
       <c r="B281" s="7"/>
-      <c r="C281" s="82"/>
+      <c r="C281" s="81"/>
       <c r="D281" s="7"/>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -10365,7 +10378,7 @@
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="7"/>
       <c r="B282" s="7"/>
-      <c r="C282" s="82"/>
+      <c r="C282" s="81"/>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -10395,7 +10408,7 @@
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="7"/>
       <c r="B283" s="7"/>
-      <c r="C283" s="82"/>
+      <c r="C283" s="81"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -10425,7 +10438,7 @@
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="7"/>
       <c r="B284" s="7"/>
-      <c r="C284" s="82"/>
+      <c r="C284" s="81"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -10455,7 +10468,7 @@
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="7"/>
       <c r="B285" s="7"/>
-      <c r="C285" s="82"/>
+      <c r="C285" s="81"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -10485,7 +10498,7 @@
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="7"/>
       <c r="B286" s="7"/>
-      <c r="C286" s="82"/>
+      <c r="C286" s="81"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -10515,7 +10528,7 @@
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="7"/>
       <c r="B287" s="7"/>
-      <c r="C287" s="82"/>
+      <c r="C287" s="81"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -10545,7 +10558,7 @@
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="7"/>
       <c r="B288" s="7"/>
-      <c r="C288" s="82"/>
+      <c r="C288" s="81"/>
       <c r="D288" s="7"/>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -10575,7 +10588,7 @@
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="7"/>
       <c r="B289" s="7"/>
-      <c r="C289" s="82"/>
+      <c r="C289" s="81"/>
       <c r="D289" s="7"/>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -10605,7 +10618,7 @@
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="7"/>
       <c r="B290" s="7"/>
-      <c r="C290" s="82"/>
+      <c r="C290" s="81"/>
       <c r="D290" s="7"/>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -10635,7 +10648,7 @@
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="7"/>
       <c r="B291" s="7"/>
-      <c r="C291" s="82"/>
+      <c r="C291" s="81"/>
       <c r="D291" s="7"/>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -10665,7 +10678,7 @@
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="7"/>
       <c r="B292" s="7"/>
-      <c r="C292" s="82"/>
+      <c r="C292" s="81"/>
       <c r="D292" s="7"/>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -10695,7 +10708,7 @@
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="7"/>
       <c r="B293" s="7"/>
-      <c r="C293" s="82"/>
+      <c r="C293" s="81"/>
       <c r="D293" s="7"/>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -10725,7 +10738,7 @@
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="7"/>
       <c r="B294" s="7"/>
-      <c r="C294" s="82"/>
+      <c r="C294" s="81"/>
       <c r="D294" s="7"/>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -10755,7 +10768,7 @@
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="7"/>
       <c r="B295" s="7"/>
-      <c r="C295" s="82"/>
+      <c r="C295" s="81"/>
       <c r="D295" s="7"/>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -10785,7 +10798,7 @@
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="7"/>
       <c r="B296" s="7"/>
-      <c r="C296" s="82"/>
+      <c r="C296" s="81"/>
       <c r="D296" s="7"/>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -10815,7 +10828,7 @@
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="7"/>
       <c r="B297" s="7"/>
-      <c r="C297" s="82"/>
+      <c r="C297" s="81"/>
       <c r="D297" s="7"/>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -10845,7 +10858,7 @@
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="7"/>
       <c r="B298" s="7"/>
-      <c r="C298" s="82"/>
+      <c r="C298" s="81"/>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -10875,7 +10888,7 @@
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="7"/>
       <c r="B299" s="7"/>
-      <c r="C299" s="82"/>
+      <c r="C299" s="81"/>
       <c r="D299" s="7"/>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -10905,7 +10918,7 @@
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="7"/>
       <c r="B300" s="7"/>
-      <c r="C300" s="82"/>
+      <c r="C300" s="81"/>
       <c r="D300" s="7"/>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -10935,7 +10948,7 @@
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="7"/>
       <c r="B301" s="7"/>
-      <c r="C301" s="82"/>
+      <c r="C301" s="81"/>
       <c r="D301" s="7"/>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -10965,7 +10978,7 @@
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="7"/>
       <c r="B302" s="7"/>
-      <c r="C302" s="82"/>
+      <c r="C302" s="81"/>
       <c r="D302" s="7"/>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -10995,7 +11008,7 @@
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="7"/>
       <c r="B303" s="7"/>
-      <c r="C303" s="82"/>
+      <c r="C303" s="81"/>
       <c r="D303" s="7"/>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -11025,7 +11038,7 @@
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="7"/>
       <c r="B304" s="7"/>
-      <c r="C304" s="82"/>
+      <c r="C304" s="81"/>
       <c r="D304" s="7"/>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -11055,7 +11068,7 @@
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="7"/>
       <c r="B305" s="7"/>
-      <c r="C305" s="82"/>
+      <c r="C305" s="81"/>
       <c r="D305" s="7"/>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -11085,7 +11098,7 @@
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="7"/>
       <c r="B306" s="7"/>
-      <c r="C306" s="82"/>
+      <c r="C306" s="81"/>
       <c r="D306" s="7"/>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -11115,7 +11128,7 @@
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="7"/>
       <c r="B307" s="7"/>
-      <c r="C307" s="82"/>
+      <c r="C307" s="81"/>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -11145,7 +11158,7 @@
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="7"/>
       <c r="B308" s="7"/>
-      <c r="C308" s="82"/>
+      <c r="C308" s="81"/>
       <c r="D308" s="7"/>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -11175,7 +11188,7 @@
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="7"/>
       <c r="B309" s="7"/>
-      <c r="C309" s="82"/>
+      <c r="C309" s="81"/>
       <c r="D309" s="7"/>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -11205,7 +11218,7 @@
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="7"/>
       <c r="B310" s="7"/>
-      <c r="C310" s="82"/>
+      <c r="C310" s="81"/>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -11235,7 +11248,7 @@
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="7"/>
       <c r="B311" s="7"/>
-      <c r="C311" s="82"/>
+      <c r="C311" s="81"/>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -11265,7 +11278,7 @@
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="7"/>
       <c r="B312" s="7"/>
-      <c r="C312" s="82"/>
+      <c r="C312" s="81"/>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -11295,7 +11308,7 @@
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="7"/>
       <c r="B313" s="7"/>
-      <c r="C313" s="82"/>
+      <c r="C313" s="81"/>
       <c r="D313" s="7"/>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -11325,7 +11338,7 @@
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="7"/>
       <c r="B314" s="7"/>
-      <c r="C314" s="82"/>
+      <c r="C314" s="81"/>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -11355,7 +11368,7 @@
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="7"/>
       <c r="B315" s="7"/>
-      <c r="C315" s="82"/>
+      <c r="C315" s="81"/>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
       <c r="F315" s="7"/>
@@ -11385,7 +11398,7 @@
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="7"/>
       <c r="B316" s="7"/>
-      <c r="C316" s="82"/>
+      <c r="C316" s="81"/>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -11415,7 +11428,7 @@
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="7"/>
       <c r="B317" s="7"/>
-      <c r="C317" s="82"/>
+      <c r="C317" s="81"/>
       <c r="D317" s="7"/>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -11445,7 +11458,7 @@
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="7"/>
       <c r="B318" s="7"/>
-      <c r="C318" s="82"/>
+      <c r="C318" s="81"/>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -11475,7 +11488,7 @@
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="7"/>
       <c r="B319" s="7"/>
-      <c r="C319" s="82"/>
+      <c r="C319" s="81"/>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -11505,7 +11518,7 @@
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="7"/>
       <c r="B320" s="7"/>
-      <c r="C320" s="82"/>
+      <c r="C320" s="81"/>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -11535,7 +11548,7 @@
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="7"/>
       <c r="B321" s="7"/>
-      <c r="C321" s="82"/>
+      <c r="C321" s="81"/>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
       <c r="F321" s="7"/>
@@ -11565,7 +11578,7 @@
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="7"/>
       <c r="B322" s="7"/>
-      <c r="C322" s="82"/>
+      <c r="C322" s="81"/>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -11595,7 +11608,7 @@
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="7"/>
       <c r="B323" s="7"/>
-      <c r="C323" s="82"/>
+      <c r="C323" s="81"/>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -11625,7 +11638,7 @@
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="7"/>
       <c r="B324" s="7"/>
-      <c r="C324" s="82"/>
+      <c r="C324" s="81"/>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -11655,7 +11668,7 @@
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="7"/>
       <c r="B325" s="7"/>
-      <c r="C325" s="82"/>
+      <c r="C325" s="81"/>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
       <c r="F325" s="7"/>
@@ -11685,7 +11698,7 @@
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="7"/>
       <c r="B326" s="7"/>
-      <c r="C326" s="82"/>
+      <c r="C326" s="81"/>
       <c r="D326" s="7"/>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -11715,7 +11728,7 @@
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="7"/>
       <c r="B327" s="7"/>
-      <c r="C327" s="82"/>
+      <c r="C327" s="81"/>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
       <c r="F327" s="7"/>
@@ -11745,7 +11758,7 @@
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="7"/>
       <c r="B328" s="7"/>
-      <c r="C328" s="82"/>
+      <c r="C328" s="81"/>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -11775,7 +11788,7 @@
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="7"/>
       <c r="B329" s="7"/>
-      <c r="C329" s="82"/>
+      <c r="C329" s="81"/>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
       <c r="F329" s="7"/>
@@ -11805,7 +11818,7 @@
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="7"/>
       <c r="B330" s="7"/>
-      <c r="C330" s="82"/>
+      <c r="C330" s="81"/>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
       <c r="F330" s="7"/>
@@ -11835,7 +11848,7 @@
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="7"/>
       <c r="B331" s="7"/>
-      <c r="C331" s="82"/>
+      <c r="C331" s="81"/>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
       <c r="F331" s="7"/>
@@ -11865,7 +11878,7 @@
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="7"/>
       <c r="B332" s="7"/>
-      <c r="C332" s="82"/>
+      <c r="C332" s="81"/>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
       <c r="F332" s="7"/>
@@ -11895,7 +11908,7 @@
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="7"/>
       <c r="B333" s="7"/>
-      <c r="C333" s="82"/>
+      <c r="C333" s="81"/>
       <c r="D333" s="7"/>
       <c r="E333" s="7"/>
       <c r="F333" s="7"/>
@@ -11925,7 +11938,7 @@
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="7"/>
       <c r="B334" s="7"/>
-      <c r="C334" s="82"/>
+      <c r="C334" s="81"/>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
       <c r="F334" s="7"/>
@@ -11955,7 +11968,7 @@
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="7"/>
       <c r="B335" s="7"/>
-      <c r="C335" s="82"/>
+      <c r="C335" s="81"/>
       <c r="D335" s="7"/>
       <c r="E335" s="7"/>
       <c r="F335" s="7"/>
@@ -11985,7 +11998,7 @@
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="7"/>
       <c r="B336" s="7"/>
-      <c r="C336" s="82"/>
+      <c r="C336" s="81"/>
       <c r="D336" s="7"/>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -12015,7 +12028,7 @@
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="7"/>
       <c r="B337" s="7"/>
-      <c r="C337" s="82"/>
+      <c r="C337" s="81"/>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -12045,7 +12058,7 @@
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="7"/>
       <c r="B338" s="7"/>
-      <c r="C338" s="82"/>
+      <c r="C338" s="81"/>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -12075,7 +12088,7 @@
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="7"/>
       <c r="B339" s="7"/>
-      <c r="C339" s="82"/>
+      <c r="C339" s="81"/>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
       <c r="F339" s="7"/>
@@ -12105,7 +12118,7 @@
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="7"/>
       <c r="B340" s="7"/>
-      <c r="C340" s="82"/>
+      <c r="C340" s="81"/>
       <c r="D340" s="7"/>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -12135,7 +12148,7 @@
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="7"/>
       <c r="B341" s="7"/>
-      <c r="C341" s="82"/>
+      <c r="C341" s="81"/>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -12165,7 +12178,7 @@
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="7"/>
       <c r="B342" s="7"/>
-      <c r="C342" s="82"/>
+      <c r="C342" s="81"/>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -12195,7 +12208,7 @@
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="7"/>
       <c r="B343" s="7"/>
-      <c r="C343" s="82"/>
+      <c r="C343" s="81"/>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -12225,7 +12238,7 @@
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="7"/>
       <c r="B344" s="7"/>
-      <c r="C344" s="82"/>
+      <c r="C344" s="81"/>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -12255,7 +12268,7 @@
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="7"/>
       <c r="B345" s="7"/>
-      <c r="C345" s="82"/>
+      <c r="C345" s="81"/>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -12285,7 +12298,7 @@
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="7"/>
       <c r="B346" s="7"/>
-      <c r="C346" s="82"/>
+      <c r="C346" s="81"/>
       <c r="D346" s="7"/>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -12315,7 +12328,7 @@
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="7"/>
       <c r="B347" s="7"/>
-      <c r="C347" s="82"/>
+      <c r="C347" s="81"/>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -12345,7 +12358,7 @@
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="7"/>
       <c r="B348" s="7"/>
-      <c r="C348" s="82"/>
+      <c r="C348" s="81"/>
       <c r="D348" s="7"/>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -12375,7 +12388,7 @@
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="7"/>
       <c r="B349" s="7"/>
-      <c r="C349" s="82"/>
+      <c r="C349" s="81"/>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -12405,7 +12418,7 @@
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="7"/>
       <c r="B350" s="7"/>
-      <c r="C350" s="82"/>
+      <c r="C350" s="81"/>
       <c r="D350" s="7"/>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -12435,7 +12448,7 @@
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="7"/>
       <c r="B351" s="7"/>
-      <c r="C351" s="82"/>
+      <c r="C351" s="81"/>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -12465,7 +12478,7 @@
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="7"/>
       <c r="B352" s="7"/>
-      <c r="C352" s="82"/>
+      <c r="C352" s="81"/>
       <c r="D352" s="7"/>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -12495,7 +12508,7 @@
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="7"/>
       <c r="B353" s="7"/>
-      <c r="C353" s="82"/>
+      <c r="C353" s="81"/>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -12525,7 +12538,7 @@
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="7"/>
       <c r="B354" s="7"/>
-      <c r="C354" s="82"/>
+      <c r="C354" s="81"/>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -12555,7 +12568,7 @@
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="7"/>
       <c r="B355" s="7"/>
-      <c r="C355" s="82"/>
+      <c r="C355" s="81"/>
       <c r="D355" s="7"/>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -12585,7 +12598,7 @@
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="7"/>
       <c r="B356" s="7"/>
-      <c r="C356" s="82"/>
+      <c r="C356" s="81"/>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -12615,7 +12628,7 @@
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="7"/>
       <c r="B357" s="7"/>
-      <c r="C357" s="82"/>
+      <c r="C357" s="81"/>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -12645,7 +12658,7 @@
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="7"/>
       <c r="B358" s="7"/>
-      <c r="C358" s="82"/>
+      <c r="C358" s="81"/>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -12675,7 +12688,7 @@
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="7"/>
       <c r="B359" s="7"/>
-      <c r="C359" s="82"/>
+      <c r="C359" s="81"/>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -12705,7 +12718,7 @@
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="7"/>
       <c r="B360" s="7"/>
-      <c r="C360" s="82"/>
+      <c r="C360" s="81"/>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -12735,7 +12748,7 @@
     <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="7"/>
       <c r="B361" s="7"/>
-      <c r="C361" s="82"/>
+      <c r="C361" s="81"/>
       <c r="D361" s="7"/>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -12765,7 +12778,7 @@
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="7"/>
       <c r="B362" s="7"/>
-      <c r="C362" s="82"/>
+      <c r="C362" s="81"/>
       <c r="D362" s="7"/>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -12795,7 +12808,7 @@
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="7"/>
       <c r="B363" s="7"/>
-      <c r="C363" s="82"/>
+      <c r="C363" s="81"/>
       <c r="D363" s="7"/>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -12825,7 +12838,7 @@
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="7"/>
       <c r="B364" s="7"/>
-      <c r="C364" s="82"/>
+      <c r="C364" s="81"/>
       <c r="D364" s="7"/>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -12855,7 +12868,7 @@
     <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="7"/>
       <c r="B365" s="7"/>
-      <c r="C365" s="82"/>
+      <c r="C365" s="81"/>
       <c r="D365" s="7"/>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -12885,7 +12898,7 @@
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="7"/>
       <c r="B366" s="7"/>
-      <c r="C366" s="82"/>
+      <c r="C366" s="81"/>
       <c r="D366" s="7"/>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -12915,7 +12928,7 @@
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="7"/>
       <c r="B367" s="7"/>
-      <c r="C367" s="82"/>
+      <c r="C367" s="81"/>
       <c r="D367" s="7"/>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -12945,7 +12958,7 @@
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="7"/>
       <c r="B368" s="7"/>
-      <c r="C368" s="82"/>
+      <c r="C368" s="81"/>
       <c r="D368" s="7"/>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -12975,7 +12988,7 @@
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="7"/>
       <c r="B369" s="7"/>
-      <c r="C369" s="82"/>
+      <c r="C369" s="81"/>
       <c r="D369" s="7"/>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -13005,7 +13018,7 @@
     <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="7"/>
       <c r="B370" s="7"/>
-      <c r="C370" s="82"/>
+      <c r="C370" s="81"/>
       <c r="D370" s="7"/>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -13035,7 +13048,7 @@
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="7"/>
       <c r="B371" s="7"/>
-      <c r="C371" s="82"/>
+      <c r="C371" s="81"/>
       <c r="D371" s="7"/>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -13065,7 +13078,7 @@
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="7"/>
       <c r="B372" s="7"/>
-      <c r="C372" s="82"/>
+      <c r="C372" s="81"/>
       <c r="D372" s="7"/>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -13095,7 +13108,7 @@
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="7"/>
       <c r="B373" s="7"/>
-      <c r="C373" s="82"/>
+      <c r="C373" s="81"/>
       <c r="D373" s="7"/>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -13125,7 +13138,7 @@
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="7"/>
       <c r="B374" s="7"/>
-      <c r="C374" s="82"/>
+      <c r="C374" s="81"/>
       <c r="D374" s="7"/>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -13155,7 +13168,7 @@
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="7"/>
       <c r="B375" s="7"/>
-      <c r="C375" s="82"/>
+      <c r="C375" s="81"/>
       <c r="D375" s="7"/>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -13185,7 +13198,7 @@
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="7"/>
       <c r="B376" s="7"/>
-      <c r="C376" s="82"/>
+      <c r="C376" s="81"/>
       <c r="D376" s="7"/>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -13215,7 +13228,7 @@
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="7"/>
       <c r="B377" s="7"/>
-      <c r="C377" s="82"/>
+      <c r="C377" s="81"/>
       <c r="D377" s="7"/>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -13245,7 +13258,7 @@
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="7"/>
       <c r="B378" s="7"/>
-      <c r="C378" s="82"/>
+      <c r="C378" s="81"/>
       <c r="D378" s="7"/>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -13275,7 +13288,7 @@
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="7"/>
       <c r="B379" s="7"/>
-      <c r="C379" s="82"/>
+      <c r="C379" s="81"/>
       <c r="D379" s="7"/>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -13305,7 +13318,7 @@
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="7"/>
       <c r="B380" s="7"/>
-      <c r="C380" s="82"/>
+      <c r="C380" s="81"/>
       <c r="D380" s="7"/>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
@@ -13335,7 +13348,7 @@
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="7"/>
       <c r="B381" s="7"/>
-      <c r="C381" s="82"/>
+      <c r="C381" s="81"/>
       <c r="D381" s="7"/>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
@@ -13365,7 +13378,7 @@
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="7"/>
       <c r="B382" s="7"/>
-      <c r="C382" s="82"/>
+      <c r="C382" s="81"/>
       <c r="D382" s="7"/>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
@@ -13395,7 +13408,7 @@
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="7"/>
       <c r="B383" s="7"/>
-      <c r="C383" s="82"/>
+      <c r="C383" s="81"/>
       <c r="D383" s="7"/>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
@@ -13425,7 +13438,7 @@
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="7"/>
       <c r="B384" s="7"/>
-      <c r="C384" s="82"/>
+      <c r="C384" s="81"/>
       <c r="D384" s="7"/>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
@@ -13455,7 +13468,7 @@
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="7"/>
       <c r="B385" s="7"/>
-      <c r="C385" s="82"/>
+      <c r="C385" s="81"/>
       <c r="D385" s="7"/>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -13485,7 +13498,7 @@
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="7"/>
       <c r="B386" s="7"/>
-      <c r="C386" s="82"/>
+      <c r="C386" s="81"/>
       <c r="D386" s="7"/>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -13515,7 +13528,7 @@
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="7"/>
       <c r="B387" s="7"/>
-      <c r="C387" s="82"/>
+      <c r="C387" s="81"/>
       <c r="D387" s="7"/>
       <c r="E387" s="7"/>
       <c r="F387" s="7"/>
@@ -13545,7 +13558,7 @@
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="7"/>
       <c r="B388" s="7"/>
-      <c r="C388" s="82"/>
+      <c r="C388" s="81"/>
       <c r="D388" s="7"/>
       <c r="E388" s="7"/>
       <c r="F388" s="7"/>
@@ -13575,7 +13588,7 @@
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="7"/>
       <c r="B389" s="7"/>
-      <c r="C389" s="82"/>
+      <c r="C389" s="81"/>
       <c r="D389" s="7"/>
       <c r="E389" s="7"/>
       <c r="F389" s="7"/>
@@ -13605,7 +13618,7 @@
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="7"/>
       <c r="B390" s="7"/>
-      <c r="C390" s="82"/>
+      <c r="C390" s="81"/>
       <c r="D390" s="7"/>
       <c r="E390" s="7"/>
       <c r="F390" s="7"/>
@@ -13635,7 +13648,7 @@
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="7"/>
       <c r="B391" s="7"/>
-      <c r="C391" s="82"/>
+      <c r="C391" s="81"/>
       <c r="D391" s="7"/>
       <c r="E391" s="7"/>
       <c r="F391" s="7"/>
@@ -13665,7 +13678,7 @@
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="7"/>
       <c r="B392" s="7"/>
-      <c r="C392" s="82"/>
+      <c r="C392" s="81"/>
       <c r="D392" s="7"/>
       <c r="E392" s="7"/>
       <c r="F392" s="7"/>
@@ -13695,7 +13708,7 @@
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="7"/>
       <c r="B393" s="7"/>
-      <c r="C393" s="82"/>
+      <c r="C393" s="81"/>
       <c r="D393" s="7"/>
       <c r="E393" s="7"/>
       <c r="F393" s="7"/>
@@ -13725,7 +13738,7 @@
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="7"/>
       <c r="B394" s="7"/>
-      <c r="C394" s="82"/>
+      <c r="C394" s="81"/>
       <c r="D394" s="7"/>
       <c r="E394" s="7"/>
       <c r="F394" s="7"/>
@@ -13755,7 +13768,7 @@
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="7"/>
       <c r="B395" s="7"/>
-      <c r="C395" s="82"/>
+      <c r="C395" s="81"/>
       <c r="D395" s="7"/>
       <c r="E395" s="7"/>
       <c r="F395" s="7"/>
@@ -13785,7 +13798,7 @@
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="7"/>
       <c r="B396" s="7"/>
-      <c r="C396" s="82"/>
+      <c r="C396" s="81"/>
       <c r="D396" s="7"/>
       <c r="E396" s="7"/>
       <c r="F396" s="7"/>
@@ -13815,7 +13828,7 @@
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="7"/>
       <c r="B397" s="7"/>
-      <c r="C397" s="82"/>
+      <c r="C397" s="81"/>
       <c r="D397" s="7"/>
       <c r="E397" s="7"/>
       <c r="F397" s="7"/>
@@ -13845,7 +13858,7 @@
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="7"/>
       <c r="B398" s="7"/>
-      <c r="C398" s="82"/>
+      <c r="C398" s="81"/>
       <c r="D398" s="7"/>
       <c r="E398" s="7"/>
       <c r="F398" s="7"/>
@@ -13875,7 +13888,7 @@
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="7"/>
       <c r="B399" s="7"/>
-      <c r="C399" s="82"/>
+      <c r="C399" s="81"/>
       <c r="D399" s="7"/>
       <c r="E399" s="7"/>
       <c r="F399" s="7"/>
@@ -13905,7 +13918,7 @@
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="7"/>
       <c r="B400" s="7"/>
-      <c r="C400" s="82"/>
+      <c r="C400" s="81"/>
       <c r="D400" s="7"/>
       <c r="E400" s="7"/>
       <c r="F400" s="7"/>
@@ -13935,7 +13948,7 @@
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="7"/>
       <c r="B401" s="7"/>
-      <c r="C401" s="82"/>
+      <c r="C401" s="81"/>
       <c r="D401" s="7"/>
       <c r="E401" s="7"/>
       <c r="F401" s="7"/>
@@ -13965,7 +13978,7 @@
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="7"/>
       <c r="B402" s="7"/>
-      <c r="C402" s="82"/>
+      <c r="C402" s="81"/>
       <c r="D402" s="7"/>
       <c r="E402" s="7"/>
       <c r="F402" s="7"/>
@@ -13995,7 +14008,7 @@
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="7"/>
       <c r="B403" s="7"/>
-      <c r="C403" s="82"/>
+      <c r="C403" s="81"/>
       <c r="D403" s="7"/>
       <c r="E403" s="7"/>
       <c r="F403" s="7"/>
@@ -14025,7 +14038,7 @@
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="7"/>
       <c r="B404" s="7"/>
-      <c r="C404" s="82"/>
+      <c r="C404" s="81"/>
       <c r="D404" s="7"/>
       <c r="E404" s="7"/>
       <c r="F404" s="7"/>
@@ -14055,7 +14068,7 @@
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="7"/>
       <c r="B405" s="7"/>
-      <c r="C405" s="82"/>
+      <c r="C405" s="81"/>
       <c r="D405" s="7"/>
       <c r="E405" s="7"/>
       <c r="F405" s="7"/>
@@ -14085,7 +14098,7 @@
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="7"/>
       <c r="B406" s="7"/>
-      <c r="C406" s="82"/>
+      <c r="C406" s="81"/>
       <c r="D406" s="7"/>
       <c r="E406" s="7"/>
       <c r="F406" s="7"/>
@@ -14115,7 +14128,7 @@
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="7"/>
       <c r="B407" s="7"/>
-      <c r="C407" s="82"/>
+      <c r="C407" s="81"/>
       <c r="D407" s="7"/>
       <c r="E407" s="7"/>
       <c r="F407" s="7"/>
@@ -14145,7 +14158,7 @@
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="7"/>
       <c r="B408" s="7"/>
-      <c r="C408" s="82"/>
+      <c r="C408" s="81"/>
       <c r="D408" s="7"/>
       <c r="E408" s="7"/>
       <c r="F408" s="7"/>
@@ -14175,7 +14188,7 @@
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="7"/>
       <c r="B409" s="7"/>
-      <c r="C409" s="82"/>
+      <c r="C409" s="81"/>
       <c r="D409" s="7"/>
       <c r="E409" s="7"/>
       <c r="F409" s="7"/>
@@ -14205,7 +14218,7 @@
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="7"/>
       <c r="B410" s="7"/>
-      <c r="C410" s="82"/>
+      <c r="C410" s="81"/>
       <c r="D410" s="7"/>
       <c r="E410" s="7"/>
       <c r="F410" s="7"/>
@@ -14235,7 +14248,7 @@
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="7"/>
       <c r="B411" s="7"/>
-      <c r="C411" s="82"/>
+      <c r="C411" s="81"/>
       <c r="D411" s="7"/>
       <c r="E411" s="7"/>
       <c r="F411" s="7"/>
@@ -14265,7 +14278,7 @@
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="7"/>
       <c r="B412" s="7"/>
-      <c r="C412" s="82"/>
+      <c r="C412" s="81"/>
       <c r="D412" s="7"/>
       <c r="E412" s="7"/>
       <c r="F412" s="7"/>
@@ -14295,7 +14308,7 @@
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="7"/>
       <c r="B413" s="7"/>
-      <c r="C413" s="82"/>
+      <c r="C413" s="81"/>
       <c r="D413" s="7"/>
       <c r="E413" s="7"/>
       <c r="F413" s="7"/>
@@ -14325,7 +14338,7 @@
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="7"/>
       <c r="B414" s="7"/>
-      <c r="C414" s="82"/>
+      <c r="C414" s="81"/>
       <c r="D414" s="7"/>
       <c r="E414" s="7"/>
       <c r="F414" s="7"/>
@@ -14355,7 +14368,7 @@
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="7"/>
       <c r="B415" s="7"/>
-      <c r="C415" s="82"/>
+      <c r="C415" s="81"/>
       <c r="D415" s="7"/>
       <c r="E415" s="7"/>
       <c r="F415" s="7"/>
@@ -14385,7 +14398,7 @@
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="7"/>
       <c r="B416" s="7"/>
-      <c r="C416" s="82"/>
+      <c r="C416" s="81"/>
       <c r="D416" s="7"/>
       <c r="E416" s="7"/>
       <c r="F416" s="7"/>
@@ -14415,7 +14428,7 @@
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="7"/>
       <c r="B417" s="7"/>
-      <c r="C417" s="82"/>
+      <c r="C417" s="81"/>
       <c r="D417" s="7"/>
       <c r="E417" s="7"/>
       <c r="F417" s="7"/>
@@ -14445,7 +14458,7 @@
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="7"/>
       <c r="B418" s="7"/>
-      <c r="C418" s="82"/>
+      <c r="C418" s="81"/>
       <c r="D418" s="7"/>
       <c r="E418" s="7"/>
       <c r="F418" s="7"/>
@@ -14475,7 +14488,7 @@
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="7"/>
       <c r="B419" s="7"/>
-      <c r="C419" s="82"/>
+      <c r="C419" s="81"/>
       <c r="D419" s="7"/>
       <c r="E419" s="7"/>
       <c r="F419" s="7"/>
@@ -14505,7 +14518,7 @@
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="7"/>
       <c r="B420" s="7"/>
-      <c r="C420" s="82"/>
+      <c r="C420" s="81"/>
       <c r="D420" s="7"/>
       <c r="E420" s="7"/>
       <c r="F420" s="7"/>
@@ -14535,7 +14548,7 @@
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="7"/>
       <c r="B421" s="7"/>
-      <c r="C421" s="82"/>
+      <c r="C421" s="81"/>
       <c r="D421" s="7"/>
       <c r="E421" s="7"/>
       <c r="F421" s="7"/>
@@ -14565,7 +14578,7 @@
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="7"/>
       <c r="B422" s="7"/>
-      <c r="C422" s="82"/>
+      <c r="C422" s="81"/>
       <c r="D422" s="7"/>
       <c r="E422" s="7"/>
       <c r="F422" s="7"/>
@@ -14595,7 +14608,7 @@
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="7"/>
       <c r="B423" s="7"/>
-      <c r="C423" s="82"/>
+      <c r="C423" s="81"/>
       <c r="D423" s="7"/>
       <c r="E423" s="7"/>
       <c r="F423" s="7"/>
@@ -14625,7 +14638,7 @@
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="7"/>
       <c r="B424" s="7"/>
-      <c r="C424" s="82"/>
+      <c r="C424" s="81"/>
       <c r="D424" s="7"/>
       <c r="E424" s="7"/>
       <c r="F424" s="7"/>
@@ -14655,7 +14668,7 @@
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="7"/>
       <c r="B425" s="7"/>
-      <c r="C425" s="82"/>
+      <c r="C425" s="81"/>
       <c r="D425" s="7"/>
       <c r="E425" s="7"/>
       <c r="F425" s="7"/>
@@ -14685,7 +14698,7 @@
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="7"/>
       <c r="B426" s="7"/>
-      <c r="C426" s="82"/>
+      <c r="C426" s="81"/>
       <c r="D426" s="7"/>
       <c r="E426" s="7"/>
       <c r="F426" s="7"/>
@@ -14715,7 +14728,7 @@
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="7"/>
       <c r="B427" s="7"/>
-      <c r="C427" s="82"/>
+      <c r="C427" s="81"/>
       <c r="D427" s="7"/>
       <c r="E427" s="7"/>
       <c r="F427" s="7"/>
@@ -14745,7 +14758,7 @@
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="7"/>
       <c r="B428" s="7"/>
-      <c r="C428" s="82"/>
+      <c r="C428" s="81"/>
       <c r="D428" s="7"/>
       <c r="E428" s="7"/>
       <c r="F428" s="7"/>
@@ -14775,7 +14788,7 @@
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="7"/>
       <c r="B429" s="7"/>
-      <c r="C429" s="82"/>
+      <c r="C429" s="81"/>
       <c r="D429" s="7"/>
       <c r="E429" s="7"/>
       <c r="F429" s="7"/>
@@ -14805,7 +14818,7 @@
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="7"/>
       <c r="B430" s="7"/>
-      <c r="C430" s="82"/>
+      <c r="C430" s="81"/>
       <c r="D430" s="7"/>
       <c r="E430" s="7"/>
       <c r="F430" s="7"/>
@@ -14835,7 +14848,7 @@
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="7"/>
       <c r="B431" s="7"/>
-      <c r="C431" s="82"/>
+      <c r="C431" s="81"/>
       <c r="D431" s="7"/>
       <c r="E431" s="7"/>
       <c r="F431" s="7"/>
@@ -14865,7 +14878,7 @@
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="7"/>
       <c r="B432" s="7"/>
-      <c r="C432" s="82"/>
+      <c r="C432" s="81"/>
       <c r="D432" s="7"/>
       <c r="E432" s="7"/>
       <c r="F432" s="7"/>
@@ -14895,7 +14908,7 @@
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="7"/>
       <c r="B433" s="7"/>
-      <c r="C433" s="82"/>
+      <c r="C433" s="81"/>
       <c r="D433" s="7"/>
       <c r="E433" s="7"/>
       <c r="F433" s="7"/>
@@ -14925,7 +14938,7 @@
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="7"/>
       <c r="B434" s="7"/>
-      <c r="C434" s="82"/>
+      <c r="C434" s="81"/>
       <c r="D434" s="7"/>
       <c r="E434" s="7"/>
       <c r="F434" s="7"/>
@@ -14955,7 +14968,7 @@
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="7"/>
       <c r="B435" s="7"/>
-      <c r="C435" s="82"/>
+      <c r="C435" s="81"/>
       <c r="D435" s="7"/>
       <c r="E435" s="7"/>
       <c r="F435" s="7"/>
@@ -14985,7 +14998,7 @@
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="7"/>
       <c r="B436" s="7"/>
-      <c r="C436" s="82"/>
+      <c r="C436" s="81"/>
       <c r="D436" s="7"/>
       <c r="E436" s="7"/>
       <c r="F436" s="7"/>
@@ -15015,7 +15028,7 @@
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="7"/>
       <c r="B437" s="7"/>
-      <c r="C437" s="82"/>
+      <c r="C437" s="81"/>
       <c r="D437" s="7"/>
       <c r="E437" s="7"/>
       <c r="F437" s="7"/>
@@ -15045,7 +15058,7 @@
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="7"/>
       <c r="B438" s="7"/>
-      <c r="C438" s="82"/>
+      <c r="C438" s="81"/>
       <c r="D438" s="7"/>
       <c r="E438" s="7"/>
       <c r="F438" s="7"/>
@@ -15075,7 +15088,7 @@
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="7"/>
       <c r="B439" s="7"/>
-      <c r="C439" s="82"/>
+      <c r="C439" s="81"/>
       <c r="D439" s="7"/>
       <c r="E439" s="7"/>
       <c r="F439" s="7"/>
@@ -15105,7 +15118,7 @@
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="7"/>
       <c r="B440" s="7"/>
-      <c r="C440" s="82"/>
+      <c r="C440" s="81"/>
       <c r="D440" s="7"/>
       <c r="E440" s="7"/>
       <c r="F440" s="7"/>
@@ -15135,7 +15148,7 @@
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="7"/>
       <c r="B441" s="7"/>
-      <c r="C441" s="82"/>
+      <c r="C441" s="81"/>
       <c r="D441" s="7"/>
       <c r="E441" s="7"/>
       <c r="F441" s="7"/>
@@ -15165,7 +15178,7 @@
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="7"/>
       <c r="B442" s="7"/>
-      <c r="C442" s="82"/>
+      <c r="C442" s="81"/>
       <c r="D442" s="7"/>
       <c r="E442" s="7"/>
       <c r="F442" s="7"/>
@@ -15195,7 +15208,7 @@
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="7"/>
       <c r="B443" s="7"/>
-      <c r="C443" s="82"/>
+      <c r="C443" s="81"/>
       <c r="D443" s="7"/>
       <c r="E443" s="7"/>
       <c r="F443" s="7"/>
@@ -15225,7 +15238,7 @@
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="7"/>
       <c r="B444" s="7"/>
-      <c r="C444" s="82"/>
+      <c r="C444" s="81"/>
       <c r="D444" s="7"/>
       <c r="E444" s="7"/>
       <c r="F444" s="7"/>
@@ -15255,7 +15268,7 @@
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="7"/>
       <c r="B445" s="7"/>
-      <c r="C445" s="82"/>
+      <c r="C445" s="81"/>
       <c r="D445" s="7"/>
       <c r="E445" s="7"/>
       <c r="F445" s="7"/>
@@ -15285,7 +15298,7 @@
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="7"/>
       <c r="B446" s="7"/>
-      <c r="C446" s="82"/>
+      <c r="C446" s="81"/>
       <c r="D446" s="7"/>
       <c r="E446" s="7"/>
       <c r="F446" s="7"/>
@@ -15315,7 +15328,7 @@
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="7"/>
       <c r="B447" s="7"/>
-      <c r="C447" s="82"/>
+      <c r="C447" s="81"/>
       <c r="D447" s="7"/>
       <c r="E447" s="7"/>
       <c r="F447" s="7"/>
@@ -15345,7 +15358,7 @@
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="7"/>
       <c r="B448" s="7"/>
-      <c r="C448" s="82"/>
+      <c r="C448" s="81"/>
       <c r="D448" s="7"/>
       <c r="E448" s="7"/>
       <c r="F448" s="7"/>
@@ -15375,7 +15388,7 @@
     <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="7"/>
       <c r="B449" s="7"/>
-      <c r="C449" s="82"/>
+      <c r="C449" s="81"/>
       <c r="D449" s="7"/>
       <c r="E449" s="7"/>
       <c r="F449" s="7"/>
@@ -15405,7 +15418,7 @@
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="7"/>
       <c r="B450" s="7"/>
-      <c r="C450" s="82"/>
+      <c r="C450" s="81"/>
       <c r="D450" s="7"/>
       <c r="E450" s="7"/>
       <c r="F450" s="7"/>
@@ -15435,7 +15448,7 @@
     <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="7"/>
       <c r="B451" s="7"/>
-      <c r="C451" s="82"/>
+      <c r="C451" s="81"/>
       <c r="D451" s="7"/>
       <c r="E451" s="7"/>
       <c r="F451" s="7"/>
@@ -15465,7 +15478,7 @@
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="7"/>
       <c r="B452" s="7"/>
-      <c r="C452" s="82"/>
+      <c r="C452" s="81"/>
       <c r="D452" s="7"/>
       <c r="E452" s="7"/>
       <c r="F452" s="7"/>
@@ -15495,7 +15508,7 @@
     <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="7"/>
       <c r="B453" s="7"/>
-      <c r="C453" s="82"/>
+      <c r="C453" s="81"/>
       <c r="D453" s="7"/>
       <c r="E453" s="7"/>
       <c r="F453" s="7"/>
@@ -15525,7 +15538,7 @@
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="7"/>
       <c r="B454" s="7"/>
-      <c r="C454" s="82"/>
+      <c r="C454" s="81"/>
       <c r="D454" s="7"/>
       <c r="E454" s="7"/>
       <c r="F454" s="7"/>
@@ -15555,7 +15568,7 @@
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="7"/>
       <c r="B455" s="7"/>
-      <c r="C455" s="82"/>
+      <c r="C455" s="81"/>
       <c r="D455" s="7"/>
       <c r="E455" s="7"/>
       <c r="F455" s="7"/>
@@ -15585,7 +15598,7 @@
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="7"/>
       <c r="B456" s="7"/>
-      <c r="C456" s="82"/>
+      <c r="C456" s="81"/>
       <c r="D456" s="7"/>
       <c r="E456" s="7"/>
       <c r="F456" s="7"/>
@@ -15615,7 +15628,7 @@
     <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="7"/>
       <c r="B457" s="7"/>
-      <c r="C457" s="82"/>
+      <c r="C457" s="81"/>
       <c r="D457" s="7"/>
       <c r="E457" s="7"/>
       <c r="F457" s="7"/>
@@ -15645,7 +15658,7 @@
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="7"/>
       <c r="B458" s="7"/>
-      <c r="C458" s="82"/>
+      <c r="C458" s="81"/>
       <c r="D458" s="7"/>
       <c r="E458" s="7"/>
       <c r="F458" s="7"/>
@@ -15675,7 +15688,7 @@
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="7"/>
       <c r="B459" s="7"/>
-      <c r="C459" s="82"/>
+      <c r="C459" s="81"/>
       <c r="D459" s="7"/>
       <c r="E459" s="7"/>
       <c r="F459" s="7"/>
@@ -15705,7 +15718,7 @@
     <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="7"/>
       <c r="B460" s="7"/>
-      <c r="C460" s="82"/>
+      <c r="C460" s="81"/>
       <c r="D460" s="7"/>
       <c r="E460" s="7"/>
       <c r="F460" s="7"/>
@@ -15735,7 +15748,7 @@
     <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="7"/>
       <c r="B461" s="7"/>
-      <c r="C461" s="82"/>
+      <c r="C461" s="81"/>
       <c r="D461" s="7"/>
       <c r="E461" s="7"/>
       <c r="F461" s="7"/>
@@ -15765,7 +15778,7 @@
     <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="7"/>
       <c r="B462" s="7"/>
-      <c r="C462" s="82"/>
+      <c r="C462" s="81"/>
       <c r="D462" s="7"/>
       <c r="E462" s="7"/>
       <c r="F462" s="7"/>
@@ -15795,7 +15808,7 @@
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="7"/>
       <c r="B463" s="7"/>
-      <c r="C463" s="82"/>
+      <c r="C463" s="81"/>
       <c r="D463" s="7"/>
       <c r="E463" s="7"/>
       <c r="F463" s="7"/>
@@ -15825,7 +15838,7 @@
     <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="7"/>
       <c r="B464" s="7"/>
-      <c r="C464" s="82"/>
+      <c r="C464" s="81"/>
       <c r="D464" s="7"/>
       <c r="E464" s="7"/>
       <c r="F464" s="7"/>
@@ -15855,7 +15868,7 @@
     <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="7"/>
       <c r="B465" s="7"/>
-      <c r="C465" s="82"/>
+      <c r="C465" s="81"/>
       <c r="D465" s="7"/>
       <c r="E465" s="7"/>
       <c r="F465" s="7"/>
@@ -15885,7 +15898,7 @@
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="7"/>
       <c r="B466" s="7"/>
-      <c r="C466" s="82"/>
+      <c r="C466" s="81"/>
       <c r="D466" s="7"/>
       <c r="E466" s="7"/>
       <c r="F466" s="7"/>
@@ -15915,7 +15928,7 @@
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="7"/>
       <c r="B467" s="7"/>
-      <c r="C467" s="82"/>
+      <c r="C467" s="81"/>
       <c r="D467" s="7"/>
       <c r="E467" s="7"/>
       <c r="F467" s="7"/>
@@ -15945,7 +15958,7 @@
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="7"/>
       <c r="B468" s="7"/>
-      <c r="C468" s="82"/>
+      <c r="C468" s="81"/>
       <c r="D468" s="7"/>
       <c r="E468" s="7"/>
       <c r="F468" s="7"/>
@@ -15975,7 +15988,7 @@
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="7"/>
       <c r="B469" s="7"/>
-      <c r="C469" s="82"/>
+      <c r="C469" s="81"/>
       <c r="D469" s="7"/>
       <c r="E469" s="7"/>
       <c r="F469" s="7"/>
@@ -16005,7 +16018,7 @@
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="7"/>
       <c r="B470" s="7"/>
-      <c r="C470" s="82"/>
+      <c r="C470" s="81"/>
       <c r="D470" s="7"/>
       <c r="E470" s="7"/>
       <c r="F470" s="7"/>
@@ -16035,7 +16048,7 @@
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="7"/>
       <c r="B471" s="7"/>
-      <c r="C471" s="82"/>
+      <c r="C471" s="81"/>
       <c r="D471" s="7"/>
       <c r="E471" s="7"/>
       <c r="F471" s="7"/>
@@ -16065,7 +16078,7 @@
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="7"/>
       <c r="B472" s="7"/>
-      <c r="C472" s="82"/>
+      <c r="C472" s="81"/>
       <c r="D472" s="7"/>
       <c r="E472" s="7"/>
       <c r="F472" s="7"/>
@@ -16095,7 +16108,7 @@
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="7"/>
       <c r="B473" s="7"/>
-      <c r="C473" s="82"/>
+      <c r="C473" s="81"/>
       <c r="D473" s="7"/>
       <c r="E473" s="7"/>
       <c r="F473" s="7"/>
@@ -16125,7 +16138,7 @@
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="7"/>
       <c r="B474" s="7"/>
-      <c r="C474" s="82"/>
+      <c r="C474" s="81"/>
       <c r="D474" s="7"/>
       <c r="E474" s="7"/>
       <c r="F474" s="7"/>
@@ -16155,7 +16168,7 @@
     <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="7"/>
       <c r="B475" s="7"/>
-      <c r="C475" s="82"/>
+      <c r="C475" s="81"/>
       <c r="D475" s="7"/>
       <c r="E475" s="7"/>
       <c r="F475" s="7"/>
@@ -16185,7 +16198,7 @@
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="7"/>
       <c r="B476" s="7"/>
-      <c r="C476" s="82"/>
+      <c r="C476" s="81"/>
       <c r="D476" s="7"/>
       <c r="E476" s="7"/>
       <c r="F476" s="7"/>
@@ -16215,7 +16228,7 @@
     <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="7"/>
       <c r="B477" s="7"/>
-      <c r="C477" s="82"/>
+      <c r="C477" s="81"/>
       <c r="D477" s="7"/>
       <c r="E477" s="7"/>
       <c r="F477" s="7"/>
@@ -16245,7 +16258,7 @@
     <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="7"/>
       <c r="B478" s="7"/>
-      <c r="C478" s="82"/>
+      <c r="C478" s="81"/>
       <c r="D478" s="7"/>
       <c r="E478" s="7"/>
       <c r="F478" s="7"/>
@@ -16275,7 +16288,7 @@
     <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="7"/>
       <c r="B479" s="7"/>
-      <c r="C479" s="82"/>
+      <c r="C479" s="81"/>
       <c r="D479" s="7"/>
       <c r="E479" s="7"/>
       <c r="F479" s="7"/>
@@ -16305,7 +16318,7 @@
     <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="7"/>
       <c r="B480" s="7"/>
-      <c r="C480" s="82"/>
+      <c r="C480" s="81"/>
       <c r="D480" s="7"/>
       <c r="E480" s="7"/>
       <c r="F480" s="7"/>
@@ -16335,7 +16348,7 @@
     <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="7"/>
       <c r="B481" s="7"/>
-      <c r="C481" s="82"/>
+      <c r="C481" s="81"/>
       <c r="D481" s="7"/>
       <c r="E481" s="7"/>
       <c r="F481" s="7"/>
@@ -16365,7 +16378,7 @@
     <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="7"/>
       <c r="B482" s="7"/>
-      <c r="C482" s="82"/>
+      <c r="C482" s="81"/>
       <c r="D482" s="7"/>
       <c r="E482" s="7"/>
       <c r="F482" s="7"/>
@@ -16395,7 +16408,7 @@
     <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="7"/>
       <c r="B483" s="7"/>
-      <c r="C483" s="82"/>
+      <c r="C483" s="81"/>
       <c r="D483" s="7"/>
       <c r="E483" s="7"/>
       <c r="F483" s="7"/>
@@ -16425,7 +16438,7 @@
     <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="7"/>
       <c r="B484" s="7"/>
-      <c r="C484" s="82"/>
+      <c r="C484" s="81"/>
       <c r="D484" s="7"/>
       <c r="E484" s="7"/>
       <c r="F484" s="7"/>
@@ -16455,7 +16468,7 @@
     <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="7"/>
       <c r="B485" s="7"/>
-      <c r="C485" s="82"/>
+      <c r="C485" s="81"/>
       <c r="D485" s="7"/>
       <c r="E485" s="7"/>
       <c r="F485" s="7"/>
@@ -16485,7 +16498,7 @@
     <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="7"/>
       <c r="B486" s="7"/>
-      <c r="C486" s="82"/>
+      <c r="C486" s="81"/>
       <c r="D486" s="7"/>
       <c r="E486" s="7"/>
       <c r="F486" s="7"/>
@@ -16515,7 +16528,7 @@
     <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="7"/>
       <c r="B487" s="7"/>
-      <c r="C487" s="82"/>
+      <c r="C487" s="81"/>
       <c r="D487" s="7"/>
       <c r="E487" s="7"/>
       <c r="F487" s="7"/>
@@ -16545,7 +16558,7 @@
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="7"/>
       <c r="B488" s="7"/>
-      <c r="C488" s="82"/>
+      <c r="C488" s="81"/>
       <c r="D488" s="7"/>
       <c r="E488" s="7"/>
       <c r="F488" s="7"/>
@@ -16575,7 +16588,7 @@
     <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="7"/>
       <c r="B489" s="7"/>
-      <c r="C489" s="82"/>
+      <c r="C489" s="81"/>
       <c r="D489" s="7"/>
       <c r="E489" s="7"/>
       <c r="F489" s="7"/>
@@ -16605,7 +16618,7 @@
     <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="7"/>
       <c r="B490" s="7"/>
-      <c r="C490" s="82"/>
+      <c r="C490" s="81"/>
       <c r="D490" s="7"/>
       <c r="E490" s="7"/>
       <c r="F490" s="7"/>
@@ -16635,7 +16648,7 @@
     <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="7"/>
       <c r="B491" s="7"/>
-      <c r="C491" s="82"/>
+      <c r="C491" s="81"/>
       <c r="D491" s="7"/>
       <c r="E491" s="7"/>
       <c r="F491" s="7"/>
@@ -16665,7 +16678,7 @@
     <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="7"/>
       <c r="B492" s="7"/>
-      <c r="C492" s="82"/>
+      <c r="C492" s="81"/>
       <c r="D492" s="7"/>
       <c r="E492" s="7"/>
       <c r="F492" s="7"/>
@@ -16695,7 +16708,7 @@
     <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="7"/>
       <c r="B493" s="7"/>
-      <c r="C493" s="82"/>
+      <c r="C493" s="81"/>
       <c r="D493" s="7"/>
       <c r="E493" s="7"/>
       <c r="F493" s="7"/>
@@ -16725,7 +16738,7 @@
     <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="7"/>
       <c r="B494" s="7"/>
-      <c r="C494" s="82"/>
+      <c r="C494" s="81"/>
       <c r="D494" s="7"/>
       <c r="E494" s="7"/>
       <c r="F494" s="7"/>
@@ -16755,7 +16768,7 @@
     <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="7"/>
       <c r="B495" s="7"/>
-      <c r="C495" s="82"/>
+      <c r="C495" s="81"/>
       <c r="D495" s="7"/>
       <c r="E495" s="7"/>
       <c r="F495" s="7"/>
@@ -16785,7 +16798,7 @@
     <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="7"/>
       <c r="B496" s="7"/>
-      <c r="C496" s="82"/>
+      <c r="C496" s="81"/>
       <c r="D496" s="7"/>
       <c r="E496" s="7"/>
       <c r="F496" s="7"/>
@@ -16815,7 +16828,7 @@
     <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="7"/>
       <c r="B497" s="7"/>
-      <c r="C497" s="82"/>
+      <c r="C497" s="81"/>
       <c r="D497" s="7"/>
       <c r="E497" s="7"/>
       <c r="F497" s="7"/>
@@ -16845,7 +16858,7 @@
     <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="7"/>
       <c r="B498" s="7"/>
-      <c r="C498" s="82"/>
+      <c r="C498" s="81"/>
       <c r="D498" s="7"/>
       <c r="E498" s="7"/>
       <c r="F498" s="7"/>
@@ -16875,7 +16888,7 @@
     <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="7"/>
       <c r="B499" s="7"/>
-      <c r="C499" s="82"/>
+      <c r="C499" s="81"/>
       <c r="D499" s="7"/>
       <c r="E499" s="7"/>
       <c r="F499" s="7"/>
@@ -16905,7 +16918,7 @@
     <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="7"/>
       <c r="B500" s="7"/>
-      <c r="C500" s="82"/>
+      <c r="C500" s="81"/>
       <c r="D500" s="7"/>
       <c r="E500" s="7"/>
       <c r="F500" s="7"/>
@@ -16935,7 +16948,7 @@
     <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="7"/>
       <c r="B501" s="7"/>
-      <c r="C501" s="82"/>
+      <c r="C501" s="81"/>
       <c r="D501" s="7"/>
       <c r="E501" s="7"/>
       <c r="F501" s="7"/>
@@ -16965,7 +16978,7 @@
     <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="7"/>
       <c r="B502" s="7"/>
-      <c r="C502" s="82"/>
+      <c r="C502" s="81"/>
       <c r="D502" s="7"/>
       <c r="E502" s="7"/>
       <c r="F502" s="7"/>
@@ -16995,7 +17008,7 @@
     <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="7"/>
       <c r="B503" s="7"/>
-      <c r="C503" s="82"/>
+      <c r="C503" s="81"/>
       <c r="D503" s="7"/>
       <c r="E503" s="7"/>
       <c r="F503" s="7"/>
@@ -17025,7 +17038,7 @@
     <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="7"/>
       <c r="B504" s="7"/>
-      <c r="C504" s="82"/>
+      <c r="C504" s="81"/>
       <c r="D504" s="7"/>
       <c r="E504" s="7"/>
       <c r="F504" s="7"/>
@@ -17055,7 +17068,7 @@
     <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="7"/>
       <c r="B505" s="7"/>
-      <c r="C505" s="82"/>
+      <c r="C505" s="81"/>
       <c r="D505" s="7"/>
       <c r="E505" s="7"/>
       <c r="F505" s="7"/>
@@ -17085,7 +17098,7 @@
     <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="7"/>
       <c r="B506" s="7"/>
-      <c r="C506" s="82"/>
+      <c r="C506" s="81"/>
       <c r="D506" s="7"/>
       <c r="E506" s="7"/>
       <c r="F506" s="7"/>
@@ -17115,7 +17128,7 @@
     <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="7"/>
       <c r="B507" s="7"/>
-      <c r="C507" s="82"/>
+      <c r="C507" s="81"/>
       <c r="D507" s="7"/>
       <c r="E507" s="7"/>
       <c r="F507" s="7"/>
@@ -17145,7 +17158,7 @@
     <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="7"/>
       <c r="B508" s="7"/>
-      <c r="C508" s="82"/>
+      <c r="C508" s="81"/>
       <c r="D508" s="7"/>
       <c r="E508" s="7"/>
       <c r="F508" s="7"/>
@@ -17175,7 +17188,7 @@
     <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="7"/>
       <c r="B509" s="7"/>
-      <c r="C509" s="82"/>
+      <c r="C509" s="81"/>
       <c r="D509" s="7"/>
       <c r="E509" s="7"/>
       <c r="F509" s="7"/>
@@ -17205,7 +17218,7 @@
     <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="7"/>
       <c r="B510" s="7"/>
-      <c r="C510" s="82"/>
+      <c r="C510" s="81"/>
       <c r="D510" s="7"/>
       <c r="E510" s="7"/>
       <c r="F510" s="7"/>
@@ -17235,7 +17248,7 @@
     <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="7"/>
       <c r="B511" s="7"/>
-      <c r="C511" s="82"/>
+      <c r="C511" s="81"/>
       <c r="D511" s="7"/>
       <c r="E511" s="7"/>
       <c r="F511" s="7"/>
@@ -17265,7 +17278,7 @@
     <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="7"/>
       <c r="B512" s="7"/>
-      <c r="C512" s="82"/>
+      <c r="C512" s="81"/>
       <c r="D512" s="7"/>
       <c r="E512" s="7"/>
       <c r="F512" s="7"/>
@@ -17295,7 +17308,7 @@
     <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="7"/>
       <c r="B513" s="7"/>
-      <c r="C513" s="82"/>
+      <c r="C513" s="81"/>
       <c r="D513" s="7"/>
       <c r="E513" s="7"/>
       <c r="F513" s="7"/>
@@ -17325,7 +17338,7 @@
     <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="7"/>
       <c r="B514" s="7"/>
-      <c r="C514" s="82"/>
+      <c r="C514" s="81"/>
       <c r="D514" s="7"/>
       <c r="E514" s="7"/>
       <c r="F514" s="7"/>
@@ -17355,7 +17368,7 @@
     <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="7"/>
       <c r="B515" s="7"/>
-      <c r="C515" s="82"/>
+      <c r="C515" s="81"/>
       <c r="D515" s="7"/>
       <c r="E515" s="7"/>
       <c r="F515" s="7"/>
@@ -17385,7 +17398,7 @@
     <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="7"/>
       <c r="B516" s="7"/>
-      <c r="C516" s="82"/>
+      <c r="C516" s="81"/>
       <c r="D516" s="7"/>
       <c r="E516" s="7"/>
       <c r="F516" s="7"/>
@@ -17415,7 +17428,7 @@
     <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="7"/>
       <c r="B517" s="7"/>
-      <c r="C517" s="82"/>
+      <c r="C517" s="81"/>
       <c r="D517" s="7"/>
       <c r="E517" s="7"/>
       <c r="F517" s="7"/>
@@ -17445,7 +17458,7 @@
     <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="7"/>
       <c r="B518" s="7"/>
-      <c r="C518" s="82"/>
+      <c r="C518" s="81"/>
       <c r="D518" s="7"/>
       <c r="E518" s="7"/>
       <c r="F518" s="7"/>
@@ -17475,7 +17488,7 @@
     <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="7"/>
       <c r="B519" s="7"/>
-      <c r="C519" s="82"/>
+      <c r="C519" s="81"/>
       <c r="D519" s="7"/>
       <c r="E519" s="7"/>
       <c r="F519" s="7"/>
@@ -17505,7 +17518,7 @@
     <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="7"/>
       <c r="B520" s="7"/>
-      <c r="C520" s="82"/>
+      <c r="C520" s="81"/>
       <c r="D520" s="7"/>
       <c r="E520" s="7"/>
       <c r="F520" s="7"/>
@@ -17535,7 +17548,7 @@
     <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="7"/>
       <c r="B521" s="7"/>
-      <c r="C521" s="82"/>
+      <c r="C521" s="81"/>
       <c r="D521" s="7"/>
       <c r="E521" s="7"/>
       <c r="F521" s="7"/>
@@ -17565,7 +17578,7 @@
     <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="7"/>
       <c r="B522" s="7"/>
-      <c r="C522" s="82"/>
+      <c r="C522" s="81"/>
       <c r="D522" s="7"/>
       <c r="E522" s="7"/>
       <c r="F522" s="7"/>
@@ -17595,7 +17608,7 @@
     <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="7"/>
       <c r="B523" s="7"/>
-      <c r="C523" s="82"/>
+      <c r="C523" s="81"/>
       <c r="D523" s="7"/>
       <c r="E523" s="7"/>
       <c r="F523" s="7"/>
@@ -17625,7 +17638,7 @@
     <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="7"/>
       <c r="B524" s="7"/>
-      <c r="C524" s="82"/>
+      <c r="C524" s="81"/>
       <c r="D524" s="7"/>
       <c r="E524" s="7"/>
       <c r="F524" s="7"/>
@@ -17655,7 +17668,7 @@
     <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="7"/>
       <c r="B525" s="7"/>
-      <c r="C525" s="82"/>
+      <c r="C525" s="81"/>
       <c r="D525" s="7"/>
       <c r="E525" s="7"/>
       <c r="F525" s="7"/>
@@ -17685,7 +17698,7 @@
     <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="7"/>
       <c r="B526" s="7"/>
-      <c r="C526" s="82"/>
+      <c r="C526" s="81"/>
       <c r="D526" s="7"/>
       <c r="E526" s="7"/>
       <c r="F526" s="7"/>
@@ -17715,7 +17728,7 @@
     <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="7"/>
       <c r="B527" s="7"/>
-      <c r="C527" s="82"/>
+      <c r="C527" s="81"/>
       <c r="D527" s="7"/>
       <c r="E527" s="7"/>
       <c r="F527" s="7"/>
@@ -17745,7 +17758,7 @@
     <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="7"/>
       <c r="B528" s="7"/>
-      <c r="C528" s="82"/>
+      <c r="C528" s="81"/>
       <c r="D528" s="7"/>
       <c r="E528" s="7"/>
       <c r="F528" s="7"/>
@@ -17775,7 +17788,7 @@
     <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="7"/>
       <c r="B529" s="7"/>
-      <c r="C529" s="82"/>
+      <c r="C529" s="81"/>
       <c r="D529" s="7"/>
       <c r="E529" s="7"/>
       <c r="F529" s="7"/>
@@ -17805,7 +17818,7 @@
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="7"/>
       <c r="B530" s="7"/>
-      <c r="C530" s="82"/>
+      <c r="C530" s="81"/>
       <c r="D530" s="7"/>
       <c r="E530" s="7"/>
       <c r="F530" s="7"/>
@@ -17835,7 +17848,7 @@
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="7"/>
       <c r="B531" s="7"/>
-      <c r="C531" s="82"/>
+      <c r="C531" s="81"/>
       <c r="D531" s="7"/>
       <c r="E531" s="7"/>
       <c r="F531" s="7"/>
@@ -17865,7 +17878,7 @@
     <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="7"/>
       <c r="B532" s="7"/>
-      <c r="C532" s="82"/>
+      <c r="C532" s="81"/>
       <c r="D532" s="7"/>
       <c r="E532" s="7"/>
       <c r="F532" s="7"/>
@@ -17895,7 +17908,7 @@
     <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="7"/>
       <c r="B533" s="7"/>
-      <c r="C533" s="82"/>
+      <c r="C533" s="81"/>
       <c r="D533" s="7"/>
       <c r="E533" s="7"/>
       <c r="F533" s="7"/>
@@ -17925,7 +17938,7 @@
     <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="7"/>
       <c r="B534" s="7"/>
-      <c r="C534" s="82"/>
+      <c r="C534" s="81"/>
       <c r="D534" s="7"/>
       <c r="E534" s="7"/>
       <c r="F534" s="7"/>
@@ -17955,7 +17968,7 @@
     <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="7"/>
       <c r="B535" s="7"/>
-      <c r="C535" s="82"/>
+      <c r="C535" s="81"/>
       <c r="D535" s="7"/>
       <c r="E535" s="7"/>
       <c r="F535" s="7"/>
@@ -17985,7 +17998,7 @@
     <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="7"/>
       <c r="B536" s="7"/>
-      <c r="C536" s="82"/>
+      <c r="C536" s="81"/>
       <c r="D536" s="7"/>
       <c r="E536" s="7"/>
       <c r="F536" s="7"/>
@@ -18015,7 +18028,7 @@
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="7"/>
       <c r="B537" s="7"/>
-      <c r="C537" s="82"/>
+      <c r="C537" s="81"/>
       <c r="D537" s="7"/>
       <c r="E537" s="7"/>
       <c r="F537" s="7"/>
@@ -18045,7 +18058,7 @@
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="7"/>
       <c r="B538" s="7"/>
-      <c r="C538" s="82"/>
+      <c r="C538" s="81"/>
       <c r="D538" s="7"/>
       <c r="E538" s="7"/>
       <c r="F538" s="7"/>
@@ -18075,7 +18088,7 @@
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="7"/>
       <c r="B539" s="7"/>
-      <c r="C539" s="82"/>
+      <c r="C539" s="81"/>
       <c r="D539" s="7"/>
       <c r="E539" s="7"/>
       <c r="F539" s="7"/>
@@ -18105,7 +18118,7 @@
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="7"/>
       <c r="B540" s="7"/>
-      <c r="C540" s="82"/>
+      <c r="C540" s="81"/>
       <c r="D540" s="7"/>
       <c r="E540" s="7"/>
       <c r="F540" s="7"/>
@@ -18135,7 +18148,7 @@
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="7"/>
       <c r="B541" s="7"/>
-      <c r="C541" s="82"/>
+      <c r="C541" s="81"/>
       <c r="D541" s="7"/>
       <c r="E541" s="7"/>
       <c r="F541" s="7"/>
@@ -18165,7 +18178,7 @@
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="7"/>
       <c r="B542" s="7"/>
-      <c r="C542" s="82"/>
+      <c r="C542" s="81"/>
       <c r="D542" s="7"/>
       <c r="E542" s="7"/>
       <c r="F542" s="7"/>
@@ -18195,7 +18208,7 @@
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="7"/>
       <c r="B543" s="7"/>
-      <c r="C543" s="82"/>
+      <c r="C543" s="81"/>
       <c r="D543" s="7"/>
       <c r="E543" s="7"/>
       <c r="F543" s="7"/>
@@ -18225,7 +18238,7 @@
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="7"/>
       <c r="B544" s="7"/>
-      <c r="C544" s="82"/>
+      <c r="C544" s="81"/>
       <c r="D544" s="7"/>
       <c r="E544" s="7"/>
       <c r="F544" s="7"/>
@@ -18255,7 +18268,7 @@
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="7"/>
       <c r="B545" s="7"/>
-      <c r="C545" s="82"/>
+      <c r="C545" s="81"/>
       <c r="D545" s="7"/>
       <c r="E545" s="7"/>
       <c r="F545" s="7"/>
@@ -18285,7 +18298,7 @@
     <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="7"/>
       <c r="B546" s="7"/>
-      <c r="C546" s="82"/>
+      <c r="C546" s="81"/>
       <c r="D546" s="7"/>
       <c r="E546" s="7"/>
       <c r="F546" s="7"/>
@@ -18315,7 +18328,7 @@
     <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="7"/>
       <c r="B547" s="7"/>
-      <c r="C547" s="82"/>
+      <c r="C547" s="81"/>
       <c r="D547" s="7"/>
       <c r="E547" s="7"/>
       <c r="F547" s="7"/>
@@ -18345,7 +18358,7 @@
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="7"/>
       <c r="B548" s="7"/>
-      <c r="C548" s="82"/>
+      <c r="C548" s="81"/>
       <c r="D548" s="7"/>
       <c r="E548" s="7"/>
       <c r="F548" s="7"/>
@@ -18375,7 +18388,7 @@
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="7"/>
       <c r="B549" s="7"/>
-      <c r="C549" s="82"/>
+      <c r="C549" s="81"/>
       <c r="D549" s="7"/>
       <c r="E549" s="7"/>
       <c r="F549" s="7"/>
@@ -18405,7 +18418,7 @@
     <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="7"/>
       <c r="B550" s="7"/>
-      <c r="C550" s="82"/>
+      <c r="C550" s="81"/>
       <c r="D550" s="7"/>
       <c r="E550" s="7"/>
       <c r="F550" s="7"/>
@@ -18435,7 +18448,7 @@
     <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="7"/>
       <c r="B551" s="7"/>
-      <c r="C551" s="82"/>
+      <c r="C551" s="81"/>
       <c r="D551" s="7"/>
       <c r="E551" s="7"/>
       <c r="F551" s="7"/>
@@ -18465,7 +18478,7 @@
     <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="7"/>
       <c r="B552" s="7"/>
-      <c r="C552" s="82"/>
+      <c r="C552" s="81"/>
       <c r="D552" s="7"/>
       <c r="E552" s="7"/>
       <c r="F552" s="7"/>
@@ -18495,7 +18508,7 @@
     <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="7"/>
       <c r="B553" s="7"/>
-      <c r="C553" s="82"/>
+      <c r="C553" s="81"/>
       <c r="D553" s="7"/>
       <c r="E553" s="7"/>
       <c r="F553" s="7"/>
@@ -18525,7 +18538,7 @@
     <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="7"/>
       <c r="B554" s="7"/>
-      <c r="C554" s="82"/>
+      <c r="C554" s="81"/>
       <c r="D554" s="7"/>
       <c r="E554" s="7"/>
       <c r="F554" s="7"/>
@@ -18555,7 +18568,7 @@
     <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="7"/>
       <c r="B555" s="7"/>
-      <c r="C555" s="82"/>
+      <c r="C555" s="81"/>
       <c r="D555" s="7"/>
       <c r="E555" s="7"/>
       <c r="F555" s="7"/>
@@ -18585,7 +18598,7 @@
     <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="7"/>
       <c r="B556" s="7"/>
-      <c r="C556" s="82"/>
+      <c r="C556" s="81"/>
       <c r="D556" s="7"/>
       <c r="E556" s="7"/>
       <c r="F556" s="7"/>
@@ -18615,7 +18628,7 @@
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="7"/>
       <c r="B557" s="7"/>
-      <c r="C557" s="82"/>
+      <c r="C557" s="81"/>
       <c r="D557" s="7"/>
       <c r="E557" s="7"/>
       <c r="F557" s="7"/>
@@ -18645,7 +18658,7 @@
     <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="7"/>
       <c r="B558" s="7"/>
-      <c r="C558" s="82"/>
+      <c r="C558" s="81"/>
       <c r="D558" s="7"/>
       <c r="E558" s="7"/>
       <c r="F558" s="7"/>
@@ -18675,7 +18688,7 @@
     <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="7"/>
       <c r="B559" s="7"/>
-      <c r="C559" s="82"/>
+      <c r="C559" s="81"/>
       <c r="D559" s="7"/>
       <c r="E559" s="7"/>
       <c r="F559" s="7"/>
@@ -18705,7 +18718,7 @@
     <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="7"/>
       <c r="B560" s="7"/>
-      <c r="C560" s="82"/>
+      <c r="C560" s="81"/>
       <c r="D560" s="7"/>
       <c r="E560" s="7"/>
       <c r="F560" s="7"/>
@@ -18735,7 +18748,7 @@
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="7"/>
       <c r="B561" s="7"/>
-      <c r="C561" s="82"/>
+      <c r="C561" s="81"/>
       <c r="D561" s="7"/>
       <c r="E561" s="7"/>
       <c r="F561" s="7"/>
@@ -18765,7 +18778,7 @@
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="7"/>
       <c r="B562" s="7"/>
-      <c r="C562" s="82"/>
+      <c r="C562" s="81"/>
       <c r="D562" s="7"/>
       <c r="E562" s="7"/>
       <c r="F562" s="7"/>
@@ -18795,7 +18808,7 @@
     <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="7"/>
       <c r="B563" s="7"/>
-      <c r="C563" s="82"/>
+      <c r="C563" s="81"/>
       <c r="D563" s="7"/>
       <c r="E563" s="7"/>
       <c r="F563" s="7"/>
@@ -18825,7 +18838,7 @@
     <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="7"/>
       <c r="B564" s="7"/>
-      <c r="C564" s="82"/>
+      <c r="C564" s="81"/>
       <c r="D564" s="7"/>
       <c r="E564" s="7"/>
       <c r="F564" s="7"/>
@@ -18855,7 +18868,7 @@
     <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="7"/>
       <c r="B565" s="7"/>
-      <c r="C565" s="82"/>
+      <c r="C565" s="81"/>
       <c r="D565" s="7"/>
       <c r="E565" s="7"/>
       <c r="F565" s="7"/>
@@ -18885,7 +18898,7 @@
     <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="7"/>
       <c r="B566" s="7"/>
-      <c r="C566" s="82"/>
+      <c r="C566" s="81"/>
       <c r="D566" s="7"/>
       <c r="E566" s="7"/>
       <c r="F566" s="7"/>
@@ -18915,7 +18928,7 @@
     <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="7"/>
       <c r="B567" s="7"/>
-      <c r="C567" s="82"/>
+      <c r="C567" s="81"/>
       <c r="D567" s="7"/>
       <c r="E567" s="7"/>
       <c r="F567" s="7"/>
@@ -18945,7 +18958,7 @@
     <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="7"/>
       <c r="B568" s="7"/>
-      <c r="C568" s="82"/>
+      <c r="C568" s="81"/>
       <c r="D568" s="7"/>
       <c r="E568" s="7"/>
       <c r="F568" s="7"/>
@@ -18975,7 +18988,7 @@
     <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="7"/>
       <c r="B569" s="7"/>
-      <c r="C569" s="82"/>
+      <c r="C569" s="81"/>
       <c r="D569" s="7"/>
       <c r="E569" s="7"/>
       <c r="F569" s="7"/>
@@ -19005,7 +19018,7 @@
     <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="7"/>
       <c r="B570" s="7"/>
-      <c r="C570" s="82"/>
+      <c r="C570" s="81"/>
       <c r="D570" s="7"/>
       <c r="E570" s="7"/>
       <c r="F570" s="7"/>
@@ -19035,7 +19048,7 @@
     <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="7"/>
       <c r="B571" s="7"/>
-      <c r="C571" s="82"/>
+      <c r="C571" s="81"/>
       <c r="D571" s="7"/>
       <c r="E571" s="7"/>
       <c r="F571" s="7"/>
@@ -19065,7 +19078,7 @@
     <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="7"/>
       <c r="B572" s="7"/>
-      <c r="C572" s="82"/>
+      <c r="C572" s="81"/>
       <c r="D572" s="7"/>
       <c r="E572" s="7"/>
       <c r="F572" s="7"/>
@@ -19095,7 +19108,7 @@
     <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="7"/>
       <c r="B573" s="7"/>
-      <c r="C573" s="82"/>
+      <c r="C573" s="81"/>
       <c r="D573" s="7"/>
       <c r="E573" s="7"/>
       <c r="F573" s="7"/>
@@ -19125,7 +19138,7 @@
     <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="7"/>
       <c r="B574" s="7"/>
-      <c r="C574" s="82"/>
+      <c r="C574" s="81"/>
       <c r="D574" s="7"/>
       <c r="E574" s="7"/>
       <c r="F574" s="7"/>
@@ -19155,7 +19168,7 @@
     <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="7"/>
       <c r="B575" s="7"/>
-      <c r="C575" s="82"/>
+      <c r="C575" s="81"/>
       <c r="D575" s="7"/>
       <c r="E575" s="7"/>
       <c r="F575" s="7"/>
@@ -19185,7 +19198,7 @@
     <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="7"/>
       <c r="B576" s="7"/>
-      <c r="C576" s="82"/>
+      <c r="C576" s="81"/>
       <c r="D576" s="7"/>
       <c r="E576" s="7"/>
       <c r="F576" s="7"/>
@@ -19215,7 +19228,7 @@
     <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="7"/>
       <c r="B577" s="7"/>
-      <c r="C577" s="82"/>
+      <c r="C577" s="81"/>
       <c r="D577" s="7"/>
       <c r="E577" s="7"/>
       <c r="F577" s="7"/>
@@ -19245,7 +19258,7 @@
     <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="7"/>
       <c r="B578" s="7"/>
-      <c r="C578" s="82"/>
+      <c r="C578" s="81"/>
       <c r="D578" s="7"/>
       <c r="E578" s="7"/>
       <c r="F578" s="7"/>
@@ -19275,7 +19288,7 @@
     <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="7"/>
       <c r="B579" s="7"/>
-      <c r="C579" s="82"/>
+      <c r="C579" s="81"/>
       <c r="D579" s="7"/>
       <c r="E579" s="7"/>
       <c r="F579" s="7"/>
@@ -19305,7 +19318,7 @@
     <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="7"/>
       <c r="B580" s="7"/>
-      <c r="C580" s="82"/>
+      <c r="C580" s="81"/>
       <c r="D580" s="7"/>
       <c r="E580" s="7"/>
       <c r="F580" s="7"/>
@@ -19335,7 +19348,7 @@
     <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="7"/>
       <c r="B581" s="7"/>
-      <c r="C581" s="82"/>
+      <c r="C581" s="81"/>
       <c r="D581" s="7"/>
       <c r="E581" s="7"/>
       <c r="F581" s="7"/>
@@ -19365,7 +19378,7 @@
     <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="7"/>
       <c r="B582" s="7"/>
-      <c r="C582" s="82"/>
+      <c r="C582" s="81"/>
       <c r="D582" s="7"/>
       <c r="E582" s="7"/>
       <c r="F582" s="7"/>
@@ -19395,7 +19408,7 @@
     <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="7"/>
       <c r="B583" s="7"/>
-      <c r="C583" s="82"/>
+      <c r="C583" s="81"/>
       <c r="D583" s="7"/>
       <c r="E583" s="7"/>
       <c r="F583" s="7"/>
@@ -19425,7 +19438,7 @@
     <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="7"/>
       <c r="B584" s="7"/>
-      <c r="C584" s="82"/>
+      <c r="C584" s="81"/>
       <c r="D584" s="7"/>
       <c r="E584" s="7"/>
       <c r="F584" s="7"/>
@@ -19455,7 +19468,7 @@
     <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="7"/>
       <c r="B585" s="7"/>
-      <c r="C585" s="82"/>
+      <c r="C585" s="81"/>
       <c r="D585" s="7"/>
       <c r="E585" s="7"/>
       <c r="F585" s="7"/>
@@ -19485,7 +19498,7 @@
     <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="7"/>
       <c r="B586" s="7"/>
-      <c r="C586" s="82"/>
+      <c r="C586" s="81"/>
       <c r="D586" s="7"/>
       <c r="E586" s="7"/>
       <c r="F586" s="7"/>
@@ -19515,7 +19528,7 @@
     <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="7"/>
       <c r="B587" s="7"/>
-      <c r="C587" s="82"/>
+      <c r="C587" s="81"/>
       <c r="D587" s="7"/>
       <c r="E587" s="7"/>
       <c r="F587" s="7"/>
@@ -19545,7 +19558,7 @@
     <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="7"/>
       <c r="B588" s="7"/>
-      <c r="C588" s="82"/>
+      <c r="C588" s="81"/>
       <c r="D588" s="7"/>
       <c r="E588" s="7"/>
       <c r="F588" s="7"/>
@@ -19575,7 +19588,7 @@
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="7"/>
       <c r="B589" s="7"/>
-      <c r="C589" s="82"/>
+      <c r="C589" s="81"/>
       <c r="D589" s="7"/>
       <c r="E589" s="7"/>
       <c r="F589" s="7"/>
@@ -19605,7 +19618,7 @@
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="7"/>
       <c r="B590" s="7"/>
-      <c r="C590" s="82"/>
+      <c r="C590" s="81"/>
       <c r="D590" s="7"/>
       <c r="E590" s="7"/>
       <c r="F590" s="7"/>
@@ -19635,7 +19648,7 @@
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="7"/>
       <c r="B591" s="7"/>
-      <c r="C591" s="82"/>
+      <c r="C591" s="81"/>
       <c r="D591" s="7"/>
       <c r="E591" s="7"/>
       <c r="F591" s="7"/>
@@ -19665,7 +19678,7 @@
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="7"/>
       <c r="B592" s="7"/>
-      <c r="C592" s="82"/>
+      <c r="C592" s="81"/>
       <c r="D592" s="7"/>
       <c r="E592" s="7"/>
       <c r="F592" s="7"/>
@@ -19695,7 +19708,7 @@
     <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="7"/>
       <c r="B593" s="7"/>
-      <c r="C593" s="82"/>
+      <c r="C593" s="81"/>
       <c r="D593" s="7"/>
       <c r="E593" s="7"/>
       <c r="F593" s="7"/>
@@ -19725,7 +19738,7 @@
     <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="7"/>
       <c r="B594" s="7"/>
-      <c r="C594" s="82"/>
+      <c r="C594" s="81"/>
       <c r="D594" s="7"/>
       <c r="E594" s="7"/>
       <c r="F594" s="7"/>
@@ -19755,7 +19768,7 @@
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="7"/>
       <c r="B595" s="7"/>
-      <c r="C595" s="82"/>
+      <c r="C595" s="81"/>
       <c r="D595" s="7"/>
       <c r="E595" s="7"/>
       <c r="F595" s="7"/>
@@ -19785,7 +19798,7 @@
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="7"/>
       <c r="B596" s="7"/>
-      <c r="C596" s="82"/>
+      <c r="C596" s="81"/>
       <c r="D596" s="7"/>
       <c r="E596" s="7"/>
       <c r="F596" s="7"/>
@@ -19815,7 +19828,7 @@
     <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="7"/>
       <c r="B597" s="7"/>
-      <c r="C597" s="82"/>
+      <c r="C597" s="81"/>
       <c r="D597" s="7"/>
       <c r="E597" s="7"/>
       <c r="F597" s="7"/>
@@ -19845,7 +19858,7 @@
     <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="7"/>
       <c r="B598" s="7"/>
-      <c r="C598" s="82"/>
+      <c r="C598" s="81"/>
       <c r="D598" s="7"/>
       <c r="E598" s="7"/>
       <c r="F598" s="7"/>
@@ -19875,7 +19888,7 @@
     <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="7"/>
       <c r="B599" s="7"/>
-      <c r="C599" s="82"/>
+      <c r="C599" s="81"/>
       <c r="D599" s="7"/>
       <c r="E599" s="7"/>
       <c r="F599" s="7"/>
@@ -19905,7 +19918,7 @@
     <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="7"/>
       <c r="B600" s="7"/>
-      <c r="C600" s="82"/>
+      <c r="C600" s="81"/>
       <c r="D600" s="7"/>
       <c r="E600" s="7"/>
       <c r="F600" s="7"/>
@@ -19935,7 +19948,7 @@
     <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="7"/>
       <c r="B601" s="7"/>
-      <c r="C601" s="82"/>
+      <c r="C601" s="81"/>
       <c r="D601" s="7"/>
       <c r="E601" s="7"/>
       <c r="F601" s="7"/>
@@ -19965,7 +19978,7 @@
     <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="7"/>
       <c r="B602" s="7"/>
-      <c r="C602" s="82"/>
+      <c r="C602" s="81"/>
       <c r="D602" s="7"/>
       <c r="E602" s="7"/>
       <c r="F602" s="7"/>
@@ -19995,7 +20008,7 @@
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="7"/>
       <c r="B603" s="7"/>
-      <c r="C603" s="82"/>
+      <c r="C603" s="81"/>
       <c r="D603" s="7"/>
       <c r="E603" s="7"/>
       <c r="F603" s="7"/>
@@ -20025,7 +20038,7 @@
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="7"/>
       <c r="B604" s="7"/>
-      <c r="C604" s="82"/>
+      <c r="C604" s="81"/>
       <c r="D604" s="7"/>
       <c r="E604" s="7"/>
       <c r="F604" s="7"/>
@@ -20055,7 +20068,7 @@
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="7"/>
       <c r="B605" s="7"/>
-      <c r="C605" s="82"/>
+      <c r="C605" s="81"/>
       <c r="D605" s="7"/>
       <c r="E605" s="7"/>
       <c r="F605" s="7"/>
@@ -20085,7 +20098,7 @@
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="7"/>
       <c r="B606" s="7"/>
-      <c r="C606" s="82"/>
+      <c r="C606" s="81"/>
       <c r="D606" s="7"/>
       <c r="E606" s="7"/>
       <c r="F606" s="7"/>
@@ -20115,7 +20128,7 @@
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="7"/>
       <c r="B607" s="7"/>
-      <c r="C607" s="82"/>
+      <c r="C607" s="81"/>
       <c r="D607" s="7"/>
       <c r="E607" s="7"/>
       <c r="F607" s="7"/>
@@ -20145,7 +20158,7 @@
     <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="7"/>
       <c r="B608" s="7"/>
-      <c r="C608" s="82"/>
+      <c r="C608" s="81"/>
       <c r="D608" s="7"/>
       <c r="E608" s="7"/>
       <c r="F608" s="7"/>
@@ -20175,7 +20188,7 @@
     <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="7"/>
       <c r="B609" s="7"/>
-      <c r="C609" s="82"/>
+      <c r="C609" s="81"/>
       <c r="D609" s="7"/>
       <c r="E609" s="7"/>
       <c r="F609" s="7"/>
@@ -20205,7 +20218,7 @@
     <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="7"/>
       <c r="B610" s="7"/>
-      <c r="C610" s="82"/>
+      <c r="C610" s="81"/>
       <c r="D610" s="7"/>
       <c r="E610" s="7"/>
       <c r="F610" s="7"/>
@@ -20235,7 +20248,7 @@
     <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="7"/>
       <c r="B611" s="7"/>
-      <c r="C611" s="82"/>
+      <c r="C611" s="81"/>
       <c r="D611" s="7"/>
       <c r="E611" s="7"/>
       <c r="F611" s="7"/>
@@ -20265,7 +20278,7 @@
     <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="7"/>
       <c r="B612" s="7"/>
-      <c r="C612" s="82"/>
+      <c r="C612" s="81"/>
       <c r="D612" s="7"/>
       <c r="E612" s="7"/>
       <c r="F612" s="7"/>
@@ -20295,7 +20308,7 @@
     <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="7"/>
       <c r="B613" s="7"/>
-      <c r="C613" s="82"/>
+      <c r="C613" s="81"/>
       <c r="D613" s="7"/>
       <c r="E613" s="7"/>
       <c r="F613" s="7"/>
@@ -20325,7 +20338,7 @@
     <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="7"/>
       <c r="B614" s="7"/>
-      <c r="C614" s="82"/>
+      <c r="C614" s="81"/>
       <c r="D614" s="7"/>
       <c r="E614" s="7"/>
       <c r="F614" s="7"/>
@@ -20355,7 +20368,7 @@
     <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="7"/>
       <c r="B615" s="7"/>
-      <c r="C615" s="82"/>
+      <c r="C615" s="81"/>
       <c r="D615" s="7"/>
       <c r="E615" s="7"/>
       <c r="F615" s="7"/>
@@ -20385,7 +20398,7 @@
     <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="7"/>
       <c r="B616" s="7"/>
-      <c r="C616" s="82"/>
+      <c r="C616" s="81"/>
       <c r="D616" s="7"/>
       <c r="E616" s="7"/>
       <c r="F616" s="7"/>
@@ -20415,7 +20428,7 @@
     <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="7"/>
       <c r="B617" s="7"/>
-      <c r="C617" s="82"/>
+      <c r="C617" s="81"/>
       <c r="D617" s="7"/>
       <c r="E617" s="7"/>
       <c r="F617" s="7"/>
@@ -20445,7 +20458,7 @@
     <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="7"/>
       <c r="B618" s="7"/>
-      <c r="C618" s="82"/>
+      <c r="C618" s="81"/>
       <c r="D618" s="7"/>
       <c r="E618" s="7"/>
       <c r="F618" s="7"/>
@@ -20475,7 +20488,7 @@
     <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="7"/>
       <c r="B619" s="7"/>
-      <c r="C619" s="82"/>
+      <c r="C619" s="81"/>
       <c r="D619" s="7"/>
       <c r="E619" s="7"/>
       <c r="F619" s="7"/>
@@ -20505,7 +20518,7 @@
     <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="7"/>
       <c r="B620" s="7"/>
-      <c r="C620" s="82"/>
+      <c r="C620" s="81"/>
       <c r="D620" s="7"/>
       <c r="E620" s="7"/>
       <c r="F620" s="7"/>
@@ -20535,7 +20548,7 @@
     <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="7"/>
       <c r="B621" s="7"/>
-      <c r="C621" s="82"/>
+      <c r="C621" s="81"/>
       <c r="D621" s="7"/>
       <c r="E621" s="7"/>
       <c r="F621" s="7"/>
@@ -20565,7 +20578,7 @@
     <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="7"/>
       <c r="B622" s="7"/>
-      <c r="C622" s="82"/>
+      <c r="C622" s="81"/>
       <c r="D622" s="7"/>
       <c r="E622" s="7"/>
       <c r="F622" s="7"/>
@@ -20595,7 +20608,7 @@
     <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="7"/>
       <c r="B623" s="7"/>
-      <c r="C623" s="82"/>
+      <c r="C623" s="81"/>
       <c r="D623" s="7"/>
       <c r="E623" s="7"/>
       <c r="F623" s="7"/>
@@ -20625,7 +20638,7 @@
     <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="7"/>
       <c r="B624" s="7"/>
-      <c r="C624" s="82"/>
+      <c r="C624" s="81"/>
       <c r="D624" s="7"/>
       <c r="E624" s="7"/>
       <c r="F624" s="7"/>
@@ -20655,7 +20668,7 @@
     <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="7"/>
       <c r="B625" s="7"/>
-      <c r="C625" s="82"/>
+      <c r="C625" s="81"/>
       <c r="D625" s="7"/>
       <c r="E625" s="7"/>
       <c r="F625" s="7"/>
@@ -20685,7 +20698,7 @@
     <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="7"/>
       <c r="B626" s="7"/>
-      <c r="C626" s="82"/>
+      <c r="C626" s="81"/>
       <c r="D626" s="7"/>
       <c r="E626" s="7"/>
       <c r="F626" s="7"/>
@@ -20715,7 +20728,7 @@
     <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="7"/>
       <c r="B627" s="7"/>
-      <c r="C627" s="82"/>
+      <c r="C627" s="81"/>
       <c r="D627" s="7"/>
       <c r="E627" s="7"/>
       <c r="F627" s="7"/>
@@ -20745,7 +20758,7 @@
     <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="7"/>
       <c r="B628" s="7"/>
-      <c r="C628" s="82"/>
+      <c r="C628" s="81"/>
       <c r="D628" s="7"/>
       <c r="E628" s="7"/>
       <c r="F628" s="7"/>
@@ -20775,7 +20788,7 @@
     <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="7"/>
       <c r="B629" s="7"/>
-      <c r="C629" s="82"/>
+      <c r="C629" s="81"/>
       <c r="D629" s="7"/>
       <c r="E629" s="7"/>
       <c r="F629" s="7"/>
@@ -20805,7 +20818,7 @@
     <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="7"/>
       <c r="B630" s="7"/>
-      <c r="C630" s="82"/>
+      <c r="C630" s="81"/>
       <c r="D630" s="7"/>
       <c r="E630" s="7"/>
       <c r="F630" s="7"/>
@@ -20835,7 +20848,7 @@
     <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="7"/>
       <c r="B631" s="7"/>
-      <c r="C631" s="82"/>
+      <c r="C631" s="81"/>
       <c r="D631" s="7"/>
       <c r="E631" s="7"/>
       <c r="F631" s="7"/>
@@ -20865,7 +20878,7 @@
     <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="7"/>
       <c r="B632" s="7"/>
-      <c r="C632" s="82"/>
+      <c r="C632" s="81"/>
       <c r="D632" s="7"/>
       <c r="E632" s="7"/>
       <c r="F632" s="7"/>
@@ -20895,7 +20908,7 @@
     <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="7"/>
       <c r="B633" s="7"/>
-      <c r="C633" s="82"/>
+      <c r="C633" s="81"/>
       <c r="D633" s="7"/>
       <c r="E633" s="7"/>
       <c r="F633" s="7"/>
@@ -20925,7 +20938,7 @@
     <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="7"/>
       <c r="B634" s="7"/>
-      <c r="C634" s="82"/>
+      <c r="C634" s="81"/>
       <c r="D634" s="7"/>
       <c r="E634" s="7"/>
       <c r="F634" s="7"/>
@@ -20955,7 +20968,7 @@
     <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="7"/>
       <c r="B635" s="7"/>
-      <c r="C635" s="82"/>
+      <c r="C635" s="81"/>
       <c r="D635" s="7"/>
       <c r="E635" s="7"/>
       <c r="F635" s="7"/>
@@ -20985,7 +20998,7 @@
     <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="7"/>
       <c r="B636" s="7"/>
-      <c r="C636" s="82"/>
+      <c r="C636" s="81"/>
       <c r="D636" s="7"/>
       <c r="E636" s="7"/>
       <c r="F636" s="7"/>
@@ -21015,7 +21028,7 @@
     <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="7"/>
       <c r="B637" s="7"/>
-      <c r="C637" s="82"/>
+      <c r="C637" s="81"/>
       <c r="D637" s="7"/>
       <c r="E637" s="7"/>
       <c r="F637" s="7"/>
@@ -21045,7 +21058,7 @@
     <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="7"/>
       <c r="B638" s="7"/>
-      <c r="C638" s="82"/>
+      <c r="C638" s="81"/>
       <c r="D638" s="7"/>
       <c r="E638" s="7"/>
       <c r="F638" s="7"/>
@@ -21075,7 +21088,7 @@
     <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="7"/>
       <c r="B639" s="7"/>
-      <c r="C639" s="82"/>
+      <c r="C639" s="81"/>
       <c r="D639" s="7"/>
       <c r="E639" s="7"/>
       <c r="F639" s="7"/>
@@ -21105,7 +21118,7 @@
     <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="7"/>
       <c r="B640" s="7"/>
-      <c r="C640" s="82"/>
+      <c r="C640" s="81"/>
       <c r="D640" s="7"/>
       <c r="E640" s="7"/>
       <c r="F640" s="7"/>
@@ -21135,7 +21148,7 @@
     <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="7"/>
       <c r="B641" s="7"/>
-      <c r="C641" s="82"/>
+      <c r="C641" s="81"/>
       <c r="D641" s="7"/>
       <c r="E641" s="7"/>
       <c r="F641" s="7"/>
@@ -21165,7 +21178,7 @@
     <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="7"/>
       <c r="B642" s="7"/>
-      <c r="C642" s="82"/>
+      <c r="C642" s="81"/>
       <c r="D642" s="7"/>
       <c r="E642" s="7"/>
       <c r="F642" s="7"/>
@@ -21195,7 +21208,7 @@
     <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="7"/>
       <c r="B643" s="7"/>
-      <c r="C643" s="82"/>
+      <c r="C643" s="81"/>
       <c r="D643" s="7"/>
       <c r="E643" s="7"/>
       <c r="F643" s="7"/>
@@ -21225,7 +21238,7 @@
     <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="7"/>
       <c r="B644" s="7"/>
-      <c r="C644" s="82"/>
+      <c r="C644" s="81"/>
       <c r="D644" s="7"/>
       <c r="E644" s="7"/>
       <c r="F644" s="7"/>
@@ -21255,7 +21268,7 @@
     <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="7"/>
       <c r="B645" s="7"/>
-      <c r="C645" s="82"/>
+      <c r="C645" s="81"/>
       <c r="D645" s="7"/>
       <c r="E645" s="7"/>
       <c r="F645" s="7"/>
@@ -21285,7 +21298,7 @@
     <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="7"/>
       <c r="B646" s="7"/>
-      <c r="C646" s="82"/>
+      <c r="C646" s="81"/>
       <c r="D646" s="7"/>
       <c r="E646" s="7"/>
       <c r="F646" s="7"/>
@@ -21315,7 +21328,7 @@
     <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="7"/>
       <c r="B647" s="7"/>
-      <c r="C647" s="82"/>
+      <c r="C647" s="81"/>
       <c r="D647" s="7"/>
       <c r="E647" s="7"/>
       <c r="F647" s="7"/>
@@ -21345,7 +21358,7 @@
     <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="7"/>
       <c r="B648" s="7"/>
-      <c r="C648" s="82"/>
+      <c r="C648" s="81"/>
       <c r="D648" s="7"/>
       <c r="E648" s="7"/>
       <c r="F648" s="7"/>
@@ -21375,7 +21388,7 @@
     <row r="649" ht="15.75" customHeight="1">
       <c r="A649" s="7"/>
       <c r="B649" s="7"/>
-      <c r="C649" s="82"/>
+      <c r="C649" s="81"/>
       <c r="D649" s="7"/>
       <c r="E649" s="7"/>
       <c r="F649" s="7"/>
@@ -21405,7 +21418,7 @@
     <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="7"/>
       <c r="B650" s="7"/>
-      <c r="C650" s="82"/>
+      <c r="C650" s="81"/>
       <c r="D650" s="7"/>
       <c r="E650" s="7"/>
       <c r="F650" s="7"/>
@@ -21435,7 +21448,7 @@
     <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="7"/>
       <c r="B651" s="7"/>
-      <c r="C651" s="82"/>
+      <c r="C651" s="81"/>
       <c r="D651" s="7"/>
       <c r="E651" s="7"/>
       <c r="F651" s="7"/>
@@ -21465,7 +21478,7 @@
     <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="7"/>
       <c r="B652" s="7"/>
-      <c r="C652" s="82"/>
+      <c r="C652" s="81"/>
       <c r="D652" s="7"/>
       <c r="E652" s="7"/>
       <c r="F652" s="7"/>
@@ -21495,7 +21508,7 @@
     <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="7"/>
       <c r="B653" s="7"/>
-      <c r="C653" s="82"/>
+      <c r="C653" s="81"/>
       <c r="D653" s="7"/>
       <c r="E653" s="7"/>
       <c r="F653" s="7"/>
@@ -21525,7 +21538,7 @@
     <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="7"/>
       <c r="B654" s="7"/>
-      <c r="C654" s="82"/>
+      <c r="C654" s="81"/>
       <c r="D654" s="7"/>
       <c r="E654" s="7"/>
       <c r="F654" s="7"/>
@@ -21555,7 +21568,7 @@
     <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="7"/>
       <c r="B655" s="7"/>
-      <c r="C655" s="82"/>
+      <c r="C655" s="81"/>
       <c r="D655" s="7"/>
       <c r="E655" s="7"/>
       <c r="F655" s="7"/>
@@ -21585,7 +21598,7 @@
     <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="7"/>
       <c r="B656" s="7"/>
-      <c r="C656" s="82"/>
+      <c r="C656" s="81"/>
       <c r="D656" s="7"/>
       <c r="E656" s="7"/>
       <c r="F656" s="7"/>
@@ -21615,7 +21628,7 @@
     <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="7"/>
       <c r="B657" s="7"/>
-      <c r="C657" s="82"/>
+      <c r="C657" s="81"/>
       <c r="D657" s="7"/>
       <c r="E657" s="7"/>
       <c r="F657" s="7"/>
@@ -21645,7 +21658,7 @@
     <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="7"/>
       <c r="B658" s="7"/>
-      <c r="C658" s="82"/>
+      <c r="C658" s="81"/>
       <c r="D658" s="7"/>
       <c r="E658" s="7"/>
       <c r="F658" s="7"/>
@@ -21675,7 +21688,7 @@
     <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="7"/>
       <c r="B659" s="7"/>
-      <c r="C659" s="82"/>
+      <c r="C659" s="81"/>
       <c r="D659" s="7"/>
       <c r="E659" s="7"/>
       <c r="F659" s="7"/>
@@ -21705,7 +21718,7 @@
     <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="7"/>
       <c r="B660" s="7"/>
-      <c r="C660" s="82"/>
+      <c r="C660" s="81"/>
       <c r="D660" s="7"/>
       <c r="E660" s="7"/>
       <c r="F660" s="7"/>
@@ -21735,7 +21748,7 @@
     <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="7"/>
       <c r="B661" s="7"/>
-      <c r="C661" s="82"/>
+      <c r="C661" s="81"/>
       <c r="D661" s="7"/>
       <c r="E661" s="7"/>
       <c r="F661" s="7"/>
@@ -21765,7 +21778,7 @@
     <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="7"/>
       <c r="B662" s="7"/>
-      <c r="C662" s="82"/>
+      <c r="C662" s="81"/>
       <c r="D662" s="7"/>
       <c r="E662" s="7"/>
       <c r="F662" s="7"/>
@@ -21795,7 +21808,7 @@
     <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="7"/>
       <c r="B663" s="7"/>
-      <c r="C663" s="82"/>
+      <c r="C663" s="81"/>
       <c r="D663" s="7"/>
       <c r="E663" s="7"/>
       <c r="F663" s="7"/>
@@ -21825,7 +21838,7 @@
     <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="7"/>
       <c r="B664" s="7"/>
-      <c r="C664" s="82"/>
+      <c r="C664" s="81"/>
       <c r="D664" s="7"/>
       <c r="E664" s="7"/>
       <c r="F664" s="7"/>
@@ -21855,7 +21868,7 @@
     <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="7"/>
       <c r="B665" s="7"/>
-      <c r="C665" s="82"/>
+      <c r="C665" s="81"/>
       <c r="D665" s="7"/>
       <c r="E665" s="7"/>
       <c r="F665" s="7"/>
@@ -21885,7 +21898,7 @@
     <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="7"/>
       <c r="B666" s="7"/>
-      <c r="C666" s="82"/>
+      <c r="C666" s="81"/>
       <c r="D666" s="7"/>
       <c r="E666" s="7"/>
       <c r="F666" s="7"/>
@@ -21915,7 +21928,7 @@
     <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="7"/>
       <c r="B667" s="7"/>
-      <c r="C667" s="82"/>
+      <c r="C667" s="81"/>
       <c r="D667" s="7"/>
       <c r="E667" s="7"/>
       <c r="F667" s="7"/>
@@ -21945,7 +21958,7 @@
     <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="7"/>
       <c r="B668" s="7"/>
-      <c r="C668" s="82"/>
+      <c r="C668" s="81"/>
       <c r="D668" s="7"/>
       <c r="E668" s="7"/>
       <c r="F668" s="7"/>
@@ -21975,7 +21988,7 @@
     <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="7"/>
       <c r="B669" s="7"/>
-      <c r="C669" s="82"/>
+      <c r="C669" s="81"/>
       <c r="D669" s="7"/>
       <c r="E669" s="7"/>
       <c r="F669" s="7"/>
@@ -22005,7 +22018,7 @@
     <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="7"/>
       <c r="B670" s="7"/>
-      <c r="C670" s="82"/>
+      <c r="C670" s="81"/>
       <c r="D670" s="7"/>
       <c r="E670" s="7"/>
       <c r="F670" s="7"/>
@@ -22035,7 +22048,7 @@
     <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="7"/>
       <c r="B671" s="7"/>
-      <c r="C671" s="82"/>
+      <c r="C671" s="81"/>
       <c r="D671" s="7"/>
       <c r="E671" s="7"/>
       <c r="F671" s="7"/>
@@ -22065,7 +22078,7 @@
     <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="7"/>
       <c r="B672" s="7"/>
-      <c r="C672" s="82"/>
+      <c r="C672" s="81"/>
       <c r="D672" s="7"/>
       <c r="E672" s="7"/>
       <c r="F672" s="7"/>
@@ -22095,7 +22108,7 @@
     <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="7"/>
       <c r="B673" s="7"/>
-      <c r="C673" s="82"/>
+      <c r="C673" s="81"/>
       <c r="D673" s="7"/>
       <c r="E673" s="7"/>
       <c r="F673" s="7"/>
@@ -22125,7 +22138,7 @@
     <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="7"/>
       <c r="B674" s="7"/>
-      <c r="C674" s="82"/>
+      <c r="C674" s="81"/>
       <c r="D674" s="7"/>
       <c r="E674" s="7"/>
       <c r="F674" s="7"/>
@@ -22155,7 +22168,7 @@
     <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="7"/>
       <c r="B675" s="7"/>
-      <c r="C675" s="82"/>
+      <c r="C675" s="81"/>
       <c r="D675" s="7"/>
       <c r="E675" s="7"/>
       <c r="F675" s="7"/>
@@ -22185,7 +22198,7 @@
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="7"/>
       <c r="B676" s="7"/>
-      <c r="C676" s="82"/>
+      <c r="C676" s="81"/>
       <c r="D676" s="7"/>
       <c r="E676" s="7"/>
       <c r="F676" s="7"/>
@@ -22215,7 +22228,7 @@
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="7"/>
       <c r="B677" s="7"/>
-      <c r="C677" s="82"/>
+      <c r="C677" s="81"/>
       <c r="D677" s="7"/>
       <c r="E677" s="7"/>
       <c r="F677" s="7"/>
@@ -22245,7 +22258,7 @@
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="7"/>
       <c r="B678" s="7"/>
-      <c r="C678" s="82"/>
+      <c r="C678" s="81"/>
       <c r="D678" s="7"/>
       <c r="E678" s="7"/>
       <c r="F678" s="7"/>
@@ -22275,7 +22288,7 @@
     <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="7"/>
       <c r="B679" s="7"/>
-      <c r="C679" s="82"/>
+      <c r="C679" s="81"/>
       <c r="D679" s="7"/>
       <c r="E679" s="7"/>
       <c r="F679" s="7"/>
@@ -22305,7 +22318,7 @@
     <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="7"/>
       <c r="B680" s="7"/>
-      <c r="C680" s="82"/>
+      <c r="C680" s="81"/>
       <c r="D680" s="7"/>
       <c r="E680" s="7"/>
       <c r="F680" s="7"/>
@@ -22335,7 +22348,7 @@
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="7"/>
       <c r="B681" s="7"/>
-      <c r="C681" s="82"/>
+      <c r="C681" s="81"/>
       <c r="D681" s="7"/>
       <c r="E681" s="7"/>
       <c r="F681" s="7"/>
@@ -22365,7 +22378,7 @@
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="7"/>
       <c r="B682" s="7"/>
-      <c r="C682" s="82"/>
+      <c r="C682" s="81"/>
       <c r="D682" s="7"/>
       <c r="E682" s="7"/>
       <c r="F682" s="7"/>
@@ -22395,7 +22408,7 @@
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="7"/>
       <c r="B683" s="7"/>
-      <c r="C683" s="82"/>
+      <c r="C683" s="81"/>
       <c r="D683" s="7"/>
       <c r="E683" s="7"/>
       <c r="F683" s="7"/>
@@ -22425,7 +22438,7 @@
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="7"/>
       <c r="B684" s="7"/>
-      <c r="C684" s="82"/>
+      <c r="C684" s="81"/>
       <c r="D684" s="7"/>
       <c r="E684" s="7"/>
       <c r="F684" s="7"/>
@@ -22455,7 +22468,7 @@
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="7"/>
       <c r="B685" s="7"/>
-      <c r="C685" s="82"/>
+      <c r="C685" s="81"/>
       <c r="D685" s="7"/>
       <c r="E685" s="7"/>
       <c r="F685" s="7"/>
@@ -22485,7 +22498,7 @@
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="7"/>
       <c r="B686" s="7"/>
-      <c r="C686" s="82"/>
+      <c r="C686" s="81"/>
       <c r="D686" s="7"/>
       <c r="E686" s="7"/>
       <c r="F686" s="7"/>
@@ -22515,7 +22528,7 @@
     <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="7"/>
       <c r="B687" s="7"/>
-      <c r="C687" s="82"/>
+      <c r="C687" s="81"/>
       <c r="D687" s="7"/>
       <c r="E687" s="7"/>
       <c r="F687" s="7"/>
@@ -22545,7 +22558,7 @@
     <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="7"/>
       <c r="B688" s="7"/>
-      <c r="C688" s="82"/>
+      <c r="C688" s="81"/>
       <c r="D688" s="7"/>
       <c r="E688" s="7"/>
       <c r="F688" s="7"/>
@@ -22575,7 +22588,7 @@
     <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="7"/>
       <c r="B689" s="7"/>
-      <c r="C689" s="82"/>
+      <c r="C689" s="81"/>
       <c r="D689" s="7"/>
       <c r="E689" s="7"/>
       <c r="F689" s="7"/>
@@ -22605,7 +22618,7 @@
     <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="7"/>
       <c r="B690" s="7"/>
-      <c r="C690" s="82"/>
+      <c r="C690" s="81"/>
       <c r="D690" s="7"/>
       <c r="E690" s="7"/>
       <c r="F690" s="7"/>
@@ -22635,7 +22648,7 @@
     <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="7"/>
       <c r="B691" s="7"/>
-      <c r="C691" s="82"/>
+      <c r="C691" s="81"/>
       <c r="D691" s="7"/>
       <c r="E691" s="7"/>
       <c r="F691" s="7"/>
@@ -22665,7 +22678,7 @@
     <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="7"/>
       <c r="B692" s="7"/>
-      <c r="C692" s="82"/>
+      <c r="C692" s="81"/>
       <c r="D692" s="7"/>
       <c r="E692" s="7"/>
       <c r="F692" s="7"/>
@@ -22695,7 +22708,7 @@
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="7"/>
       <c r="B693" s="7"/>
-      <c r="C693" s="82"/>
+      <c r="C693" s="81"/>
       <c r="D693" s="7"/>
       <c r="E693" s="7"/>
       <c r="F693" s="7"/>
@@ -22725,7 +22738,7 @@
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="7"/>
       <c r="B694" s="7"/>
-      <c r="C694" s="82"/>
+      <c r="C694" s="81"/>
       <c r="D694" s="7"/>
       <c r="E694" s="7"/>
       <c r="F694" s="7"/>
@@ -22755,7 +22768,7 @@
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="7"/>
       <c r="B695" s="7"/>
-      <c r="C695" s="82"/>
+      <c r="C695" s="81"/>
       <c r="D695" s="7"/>
       <c r="E695" s="7"/>
       <c r="F695" s="7"/>
@@ -22785,7 +22798,7 @@
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="7"/>
       <c r="B696" s="7"/>
-      <c r="C696" s="82"/>
+      <c r="C696" s="81"/>
       <c r="D696" s="7"/>
       <c r="E696" s="7"/>
       <c r="F696" s="7"/>
@@ -22815,7 +22828,7 @@
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="7"/>
       <c r="B697" s="7"/>
-      <c r="C697" s="82"/>
+      <c r="C697" s="81"/>
       <c r="D697" s="7"/>
       <c r="E697" s="7"/>
       <c r="F697" s="7"/>
@@ -22845,7 +22858,7 @@
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="7"/>
       <c r="B698" s="7"/>
-      <c r="C698" s="82"/>
+      <c r="C698" s="81"/>
       <c r="D698" s="7"/>
       <c r="E698" s="7"/>
       <c r="F698" s="7"/>
@@ -22875,7 +22888,7 @@
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="7"/>
       <c r="B699" s="7"/>
-      <c r="C699" s="82"/>
+      <c r="C699" s="81"/>
       <c r="D699" s="7"/>
       <c r="E699" s="7"/>
       <c r="F699" s="7"/>
@@ -22905,7 +22918,7 @@
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="7"/>
       <c r="B700" s="7"/>
-      <c r="C700" s="82"/>
+      <c r="C700" s="81"/>
       <c r="D700" s="7"/>
       <c r="E700" s="7"/>
       <c r="F700" s="7"/>
@@ -22935,7 +22948,7 @@
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="7"/>
       <c r="B701" s="7"/>
-      <c r="C701" s="82"/>
+      <c r="C701" s="81"/>
       <c r="D701" s="7"/>
       <c r="E701" s="7"/>
       <c r="F701" s="7"/>
@@ -22965,7 +22978,7 @@
     <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="7"/>
       <c r="B702" s="7"/>
-      <c r="C702" s="82"/>
+      <c r="C702" s="81"/>
       <c r="D702" s="7"/>
       <c r="E702" s="7"/>
       <c r="F702" s="7"/>
@@ -22995,7 +23008,7 @@
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="7"/>
       <c r="B703" s="7"/>
-      <c r="C703" s="82"/>
+      <c r="C703" s="81"/>
       <c r="D703" s="7"/>
       <c r="E703" s="7"/>
       <c r="F703" s="7"/>
@@ -23025,7 +23038,7 @@
     <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="7"/>
       <c r="B704" s="7"/>
-      <c r="C704" s="82"/>
+      <c r="C704" s="81"/>
       <c r="D704" s="7"/>
       <c r="E704" s="7"/>
       <c r="F704" s="7"/>
@@ -23055,7 +23068,7 @@
     <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="7"/>
       <c r="B705" s="7"/>
-      <c r="C705" s="82"/>
+      <c r="C705" s="81"/>
       <c r="D705" s="7"/>
       <c r="E705" s="7"/>
       <c r="F705" s="7"/>
@@ -23085,7 +23098,7 @@
     <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="7"/>
       <c r="B706" s="7"/>
-      <c r="C706" s="82"/>
+      <c r="C706" s="81"/>
       <c r="D706" s="7"/>
       <c r="E706" s="7"/>
       <c r="F706" s="7"/>
@@ -23115,7 +23128,7 @@
     <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="7"/>
       <c r="B707" s="7"/>
-      <c r="C707" s="82"/>
+      <c r="C707" s="81"/>
       <c r="D707" s="7"/>
       <c r="E707" s="7"/>
       <c r="F707" s="7"/>
@@ -23145,7 +23158,7 @@
     <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="7"/>
       <c r="B708" s="7"/>
-      <c r="C708" s="82"/>
+      <c r="C708" s="81"/>
       <c r="D708" s="7"/>
       <c r="E708" s="7"/>
       <c r="F708" s="7"/>
@@ -23175,7 +23188,7 @@
     <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="7"/>
       <c r="B709" s="7"/>
-      <c r="C709" s="82"/>
+      <c r="C709" s="81"/>
       <c r="D709" s="7"/>
       <c r="E709" s="7"/>
       <c r="F709" s="7"/>
@@ -23205,7 +23218,7 @@
     <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="7"/>
       <c r="B710" s="7"/>
-      <c r="C710" s="82"/>
+      <c r="C710" s="81"/>
       <c r="D710" s="7"/>
       <c r="E710" s="7"/>
       <c r="F710" s="7"/>
@@ -23235,7 +23248,7 @@
     <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="7"/>
       <c r="B711" s="7"/>
-      <c r="C711" s="82"/>
+      <c r="C711" s="81"/>
       <c r="D711" s="7"/>
       <c r="E711" s="7"/>
       <c r="F711" s="7"/>
@@ -23265,7 +23278,7 @@
     <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="7"/>
       <c r="B712" s="7"/>
-      <c r="C712" s="82"/>
+      <c r="C712" s="81"/>
       <c r="D712" s="7"/>
       <c r="E712" s="7"/>
       <c r="F712" s="7"/>
@@ -23295,7 +23308,7 @@
     <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="7"/>
       <c r="B713" s="7"/>
-      <c r="C713" s="82"/>
+      <c r="C713" s="81"/>
       <c r="D713" s="7"/>
       <c r="E713" s="7"/>
       <c r="F713" s="7"/>
@@ -23325,7 +23338,7 @@
     <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="7"/>
       <c r="B714" s="7"/>
-      <c r="C714" s="82"/>
+      <c r="C714" s="81"/>
       <c r="D714" s="7"/>
       <c r="E714" s="7"/>
       <c r="F714" s="7"/>
@@ -23355,7 +23368,7 @@
     <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="7"/>
       <c r="B715" s="7"/>
-      <c r="C715" s="82"/>
+      <c r="C715" s="81"/>
       <c r="D715" s="7"/>
       <c r="E715" s="7"/>
       <c r="F715" s="7"/>
@@ -23385,7 +23398,7 @@
     <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="7"/>
       <c r="B716" s="7"/>
-      <c r="C716" s="82"/>
+      <c r="C716" s="81"/>
       <c r="D716" s="7"/>
       <c r="E716" s="7"/>
       <c r="F716" s="7"/>
@@ -23415,7 +23428,7 @@
     <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="7"/>
       <c r="B717" s="7"/>
-      <c r="C717" s="82"/>
+      <c r="C717" s="81"/>
       <c r="D717" s="7"/>
       <c r="E717" s="7"/>
       <c r="F717" s="7"/>
@@ -23445,7 +23458,7 @@
     <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="7"/>
       <c r="B718" s="7"/>
-      <c r="C718" s="82"/>
+      <c r="C718" s="81"/>
       <c r="D718" s="7"/>
       <c r="E718" s="7"/>
       <c r="F718" s="7"/>
@@ -23475,7 +23488,7 @@
     <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="7"/>
       <c r="B719" s="7"/>
-      <c r="C719" s="82"/>
+      <c r="C719" s="81"/>
       <c r="D719" s="7"/>
       <c r="E719" s="7"/>
       <c r="F719" s="7"/>
@@ -23505,7 +23518,7 @@
     <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="7"/>
       <c r="B720" s="7"/>
-      <c r="C720" s="82"/>
+      <c r="C720" s="81"/>
       <c r="D720" s="7"/>
       <c r="E720" s="7"/>
       <c r="F720" s="7"/>
@@ -23535,7 +23548,7 @@
     <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="7"/>
       <c r="B721" s="7"/>
-      <c r="C721" s="82"/>
+      <c r="C721" s="81"/>
       <c r="D721" s="7"/>
       <c r="E721" s="7"/>
       <c r="F721" s="7"/>
@@ -23565,7 +23578,7 @@
     <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="7"/>
       <c r="B722" s="7"/>
-      <c r="C722" s="82"/>
+      <c r="C722" s="81"/>
       <c r="D722" s="7"/>
       <c r="E722" s="7"/>
       <c r="F722" s="7"/>
@@ -23595,7 +23608,7 @@
     <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="7"/>
       <c r="B723" s="7"/>
-      <c r="C723" s="82"/>
+      <c r="C723" s="81"/>
       <c r="D723" s="7"/>
       <c r="E723" s="7"/>
       <c r="F723" s="7"/>
@@ -23625,7 +23638,7 @@
     <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="7"/>
       <c r="B724" s="7"/>
-      <c r="C724" s="82"/>
+      <c r="C724" s="81"/>
       <c r="D724" s="7"/>
       <c r="E724" s="7"/>
       <c r="F724" s="7"/>
@@ -23655,7 +23668,7 @@
     <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="7"/>
       <c r="B725" s="7"/>
-      <c r="C725" s="82"/>
+      <c r="C725" s="81"/>
       <c r="D725" s="7"/>
       <c r="E725" s="7"/>
       <c r="F725" s="7"/>
@@ -23685,7 +23698,7 @@
     <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="7"/>
       <c r="B726" s="7"/>
-      <c r="C726" s="82"/>
+      <c r="C726" s="81"/>
       <c r="D726" s="7"/>
       <c r="E726" s="7"/>
       <c r="F726" s="7"/>
@@ -23715,7 +23728,7 @@
     <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="7"/>
       <c r="B727" s="7"/>
-      <c r="C727" s="82"/>
+      <c r="C727" s="81"/>
       <c r="D727" s="7"/>
       <c r="E727" s="7"/>
       <c r="F727" s="7"/>
@@ -23745,7 +23758,7 @@
     <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="7"/>
       <c r="B728" s="7"/>
-      <c r="C728" s="82"/>
+      <c r="C728" s="81"/>
       <c r="D728" s="7"/>
       <c r="E728" s="7"/>
       <c r="F728" s="7"/>
@@ -23775,7 +23788,7 @@
     <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="7"/>
       <c r="B729" s="7"/>
-      <c r="C729" s="82"/>
+      <c r="C729" s="81"/>
       <c r="D729" s="7"/>
       <c r="E729" s="7"/>
       <c r="F729" s="7"/>
@@ -23805,7 +23818,7 @@
     <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="7"/>
       <c r="B730" s="7"/>
-      <c r="C730" s="82"/>
+      <c r="C730" s="81"/>
       <c r="D730" s="7"/>
       <c r="E730" s="7"/>
       <c r="F730" s="7"/>
@@ -23835,7 +23848,7 @@
     <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="7"/>
       <c r="B731" s="7"/>
-      <c r="C731" s="82"/>
+      <c r="C731" s="81"/>
       <c r="D731" s="7"/>
       <c r="E731" s="7"/>
       <c r="F731" s="7"/>
@@ -23865,7 +23878,7 @@
     <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="7"/>
       <c r="B732" s="7"/>
-      <c r="C732" s="82"/>
+      <c r="C732" s="81"/>
       <c r="D732" s="7"/>
       <c r="E732" s="7"/>
       <c r="F732" s="7"/>
@@ -23895,7 +23908,7 @@
     <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="7"/>
       <c r="B733" s="7"/>
-      <c r="C733" s="82"/>
+      <c r="C733" s="81"/>
       <c r="D733" s="7"/>
       <c r="E733" s="7"/>
       <c r="F733" s="7"/>
@@ -23925,7 +23938,7 @@
     <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="7"/>
       <c r="B734" s="7"/>
-      <c r="C734" s="82"/>
+      <c r="C734" s="81"/>
       <c r="D734" s="7"/>
       <c r="E734" s="7"/>
       <c r="F734" s="7"/>
@@ -23955,7 +23968,7 @@
     <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="7"/>
       <c r="B735" s="7"/>
-      <c r="C735" s="82"/>
+      <c r="C735" s="81"/>
       <c r="D735" s="7"/>
       <c r="E735" s="7"/>
       <c r="F735" s="7"/>
@@ -23985,7 +23998,7 @@
     <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="7"/>
       <c r="B736" s="7"/>
-      <c r="C736" s="82"/>
+      <c r="C736" s="81"/>
       <c r="D736" s="7"/>
       <c r="E736" s="7"/>
       <c r="F736" s="7"/>
@@ -24015,7 +24028,7 @@
     <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="7"/>
       <c r="B737" s="7"/>
-      <c r="C737" s="82"/>
+      <c r="C737" s="81"/>
       <c r="D737" s="7"/>
       <c r="E737" s="7"/>
       <c r="F737" s="7"/>
@@ -24045,7 +24058,7 @@
     <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="7"/>
       <c r="B738" s="7"/>
-      <c r="C738" s="82"/>
+      <c r="C738" s="81"/>
       <c r="D738" s="7"/>
       <c r="E738" s="7"/>
       <c r="F738" s="7"/>
@@ -24075,7 +24088,7 @@
     <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="7"/>
       <c r="B739" s="7"/>
-      <c r="C739" s="82"/>
+      <c r="C739" s="81"/>
       <c r="D739" s="7"/>
       <c r="E739" s="7"/>
       <c r="F739" s="7"/>
@@ -24105,7 +24118,7 @@
     <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="7"/>
       <c r="B740" s="7"/>
-      <c r="C740" s="82"/>
+      <c r="C740" s="81"/>
       <c r="D740" s="7"/>
       <c r="E740" s="7"/>
       <c r="F740" s="7"/>
@@ -24135,7 +24148,7 @@
     <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="7"/>
       <c r="B741" s="7"/>
-      <c r="C741" s="82"/>
+      <c r="C741" s="81"/>
       <c r="D741" s="7"/>
       <c r="E741" s="7"/>
       <c r="F741" s="7"/>
@@ -24165,7 +24178,7 @@
     <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="7"/>
       <c r="B742" s="7"/>
-      <c r="C742" s="82"/>
+      <c r="C742" s="81"/>
       <c r="D742" s="7"/>
       <c r="E742" s="7"/>
       <c r="F742" s="7"/>
@@ -24195,7 +24208,7 @@
     <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="7"/>
       <c r="B743" s="7"/>
-      <c r="C743" s="82"/>
+      <c r="C743" s="81"/>
       <c r="D743" s="7"/>
       <c r="E743" s="7"/>
       <c r="F743" s="7"/>
@@ -24225,7 +24238,7 @@
     <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="7"/>
       <c r="B744" s="7"/>
-      <c r="C744" s="82"/>
+      <c r="C744" s="81"/>
       <c r="D744" s="7"/>
       <c r="E744" s="7"/>
       <c r="F744" s="7"/>
@@ -24255,7 +24268,7 @@
     <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="7"/>
       <c r="B745" s="7"/>
-      <c r="C745" s="82"/>
+      <c r="C745" s="81"/>
       <c r="D745" s="7"/>
       <c r="E745" s="7"/>
       <c r="F745" s="7"/>
@@ -24285,7 +24298,7 @@
     <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="7"/>
       <c r="B746" s="7"/>
-      <c r="C746" s="82"/>
+      <c r="C746" s="81"/>
       <c r="D746" s="7"/>
       <c r="E746" s="7"/>
       <c r="F746" s="7"/>
@@ -24315,7 +24328,7 @@
     <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="7"/>
       <c r="B747" s="7"/>
-      <c r="C747" s="82"/>
+      <c r="C747" s="81"/>
       <c r="D747" s="7"/>
       <c r="E747" s="7"/>
       <c r="F747" s="7"/>
@@ -24345,7 +24358,7 @@
     <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="7"/>
       <c r="B748" s="7"/>
-      <c r="C748" s="82"/>
+      <c r="C748" s="81"/>
       <c r="D748" s="7"/>
       <c r="E748" s="7"/>
       <c r="F748" s="7"/>
@@ -24375,7 +24388,7 @@
     <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="7"/>
       <c r="B749" s="7"/>
-      <c r="C749" s="82"/>
+      <c r="C749" s="81"/>
       <c r="D749" s="7"/>
       <c r="E749" s="7"/>
       <c r="F749" s="7"/>
@@ -24405,7 +24418,7 @@
     <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="7"/>
       <c r="B750" s="7"/>
-      <c r="C750" s="82"/>
+      <c r="C750" s="81"/>
       <c r="D750" s="7"/>
       <c r="E750" s="7"/>
       <c r="F750" s="7"/>
@@ -24435,7 +24448,7 @@
     <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="7"/>
       <c r="B751" s="7"/>
-      <c r="C751" s="82"/>
+      <c r="C751" s="81"/>
       <c r="D751" s="7"/>
       <c r="E751" s="7"/>
       <c r="F751" s="7"/>
@@ -24465,7 +24478,7 @@
     <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="7"/>
       <c r="B752" s="7"/>
-      <c r="C752" s="82"/>
+      <c r="C752" s="81"/>
       <c r="D752" s="7"/>
       <c r="E752" s="7"/>
       <c r="F752" s="7"/>
@@ -24495,7 +24508,7 @@
     <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="7"/>
       <c r="B753" s="7"/>
-      <c r="C753" s="82"/>
+      <c r="C753" s="81"/>
       <c r="D753" s="7"/>
       <c r="E753" s="7"/>
       <c r="F753" s="7"/>
@@ -24525,7 +24538,7 @@
     <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="7"/>
       <c r="B754" s="7"/>
-      <c r="C754" s="82"/>
+      <c r="C754" s="81"/>
       <c r="D754" s="7"/>
       <c r="E754" s="7"/>
       <c r="F754" s="7"/>
@@ -24555,7 +24568,7 @@
     <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="7"/>
       <c r="B755" s="7"/>
-      <c r="C755" s="82"/>
+      <c r="C755" s="81"/>
       <c r="D755" s="7"/>
       <c r="E755" s="7"/>
       <c r="F755" s="7"/>
@@ -24585,7 +24598,7 @@
     <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="7"/>
       <c r="B756" s="7"/>
-      <c r="C756" s="82"/>
+      <c r="C756" s="81"/>
       <c r="D756" s="7"/>
       <c r="E756" s="7"/>
       <c r="F756" s="7"/>
@@ -24615,7 +24628,7 @@
     <row r="757" ht="15.75" customHeight="1">
       <c r="A757" s="7"/>
       <c r="B757" s="7"/>
-      <c r="C757" s="82"/>
+      <c r="C757" s="81"/>
       <c r="D757" s="7"/>
       <c r="E757" s="7"/>
       <c r="F757" s="7"/>
@@ -24645,7 +24658,7 @@
     <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="7"/>
       <c r="B758" s="7"/>
-      <c r="C758" s="82"/>
+      <c r="C758" s="81"/>
       <c r="D758" s="7"/>
       <c r="E758" s="7"/>
       <c r="F758" s="7"/>
@@ -24675,7 +24688,7 @@
     <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="7"/>
       <c r="B759" s="7"/>
-      <c r="C759" s="82"/>
+      <c r="C759" s="81"/>
       <c r="D759" s="7"/>
       <c r="E759" s="7"/>
       <c r="F759" s="7"/>
@@ -24705,7 +24718,7 @@
     <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="7"/>
       <c r="B760" s="7"/>
-      <c r="C760" s="82"/>
+      <c r="C760" s="81"/>
       <c r="D760" s="7"/>
       <c r="E760" s="7"/>
       <c r="F760" s="7"/>
@@ -24735,7 +24748,7 @@
     <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="7"/>
       <c r="B761" s="7"/>
-      <c r="C761" s="82"/>
+      <c r="C761" s="81"/>
       <c r="D761" s="7"/>
       <c r="E761" s="7"/>
       <c r="F761" s="7"/>
@@ -24765,7 +24778,7 @@
     <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="7"/>
       <c r="B762" s="7"/>
-      <c r="C762" s="82"/>
+      <c r="C762" s="81"/>
       <c r="D762" s="7"/>
       <c r="E762" s="7"/>
       <c r="F762" s="7"/>
@@ -24795,7 +24808,7 @@
     <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="7"/>
       <c r="B763" s="7"/>
-      <c r="C763" s="82"/>
+      <c r="C763" s="81"/>
       <c r="D763" s="7"/>
       <c r="E763" s="7"/>
       <c r="F763" s="7"/>
@@ -24825,7 +24838,7 @@
     <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="7"/>
       <c r="B764" s="7"/>
-      <c r="C764" s="82"/>
+      <c r="C764" s="81"/>
       <c r="D764" s="7"/>
       <c r="E764" s="7"/>
       <c r="F764" s="7"/>
@@ -24855,7 +24868,7 @@
     <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="7"/>
       <c r="B765" s="7"/>
-      <c r="C765" s="82"/>
+      <c r="C765" s="81"/>
       <c r="D765" s="7"/>
       <c r="E765" s="7"/>
       <c r="F765" s="7"/>
@@ -24885,7 +24898,7 @@
     <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="7"/>
       <c r="B766" s="7"/>
-      <c r="C766" s="82"/>
+      <c r="C766" s="81"/>
       <c r="D766" s="7"/>
       <c r="E766" s="7"/>
       <c r="F766" s="7"/>
@@ -24915,7 +24928,7 @@
     <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="7"/>
       <c r="B767" s="7"/>
-      <c r="C767" s="82"/>
+      <c r="C767" s="81"/>
       <c r="D767" s="7"/>
       <c r="E767" s="7"/>
       <c r="F767" s="7"/>
@@ -24945,7 +24958,7 @@
     <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="7"/>
       <c r="B768" s="7"/>
-      <c r="C768" s="82"/>
+      <c r="C768" s="81"/>
       <c r="D768" s="7"/>
       <c r="E768" s="7"/>
       <c r="F768" s="7"/>
@@ -24975,7 +24988,7 @@
     <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="7"/>
       <c r="B769" s="7"/>
-      <c r="C769" s="82"/>
+      <c r="C769" s="81"/>
       <c r="D769" s="7"/>
       <c r="E769" s="7"/>
       <c r="F769" s="7"/>
@@ -25005,7 +25018,7 @@
     <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="7"/>
       <c r="B770" s="7"/>
-      <c r="C770" s="82"/>
+      <c r="C770" s="81"/>
       <c r="D770" s="7"/>
       <c r="E770" s="7"/>
       <c r="F770" s="7"/>
@@ -25035,7 +25048,7 @@
     <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="7"/>
       <c r="B771" s="7"/>
-      <c r="C771" s="82"/>
+      <c r="C771" s="81"/>
       <c r="D771" s="7"/>
       <c r="E771" s="7"/>
       <c r="F771" s="7"/>
@@ -25065,7 +25078,7 @@
     <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="7"/>
       <c r="B772" s="7"/>
-      <c r="C772" s="82"/>
+      <c r="C772" s="81"/>
       <c r="D772" s="7"/>
       <c r="E772" s="7"/>
       <c r="F772" s="7"/>
@@ -25095,7 +25108,7 @@
     <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="7"/>
       <c r="B773" s="7"/>
-      <c r="C773" s="82"/>
+      <c r="C773" s="81"/>
       <c r="D773" s="7"/>
       <c r="E773" s="7"/>
       <c r="F773" s="7"/>
@@ -25125,7 +25138,7 @@
     <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="7"/>
       <c r="B774" s="7"/>
-      <c r="C774" s="82"/>
+      <c r="C774" s="81"/>
       <c r="D774" s="7"/>
       <c r="E774" s="7"/>
       <c r="F774" s="7"/>
@@ -25155,7 +25168,7 @@
     <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="7"/>
       <c r="B775" s="7"/>
-      <c r="C775" s="82"/>
+      <c r="C775" s="81"/>
       <c r="D775" s="7"/>
       <c r="E775" s="7"/>
       <c r="F775" s="7"/>
@@ -25185,7 +25198,7 @@
     <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="7"/>
       <c r="B776" s="7"/>
-      <c r="C776" s="82"/>
+      <c r="C776" s="81"/>
       <c r="D776" s="7"/>
       <c r="E776" s="7"/>
       <c r="F776" s="7"/>
@@ -25215,7 +25228,7 @@
     <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="7"/>
       <c r="B777" s="7"/>
-      <c r="C777" s="82"/>
+      <c r="C777" s="81"/>
       <c r="D777" s="7"/>
       <c r="E777" s="7"/>
       <c r="F777" s="7"/>
@@ -25245,7 +25258,7 @@
     <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="7"/>
       <c r="B778" s="7"/>
-      <c r="C778" s="82"/>
+      <c r="C778" s="81"/>
       <c r="D778" s="7"/>
       <c r="E778" s="7"/>
       <c r="F778" s="7"/>
@@ -25275,7 +25288,7 @@
     <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="7"/>
       <c r="B779" s="7"/>
-      <c r="C779" s="82"/>
+      <c r="C779" s="81"/>
       <c r="D779" s="7"/>
       <c r="E779" s="7"/>
       <c r="F779" s="7"/>
@@ -25305,7 +25318,7 @@
     <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="7"/>
       <c r="B780" s="7"/>
-      <c r="C780" s="82"/>
+      <c r="C780" s="81"/>
       <c r="D780" s="7"/>
       <c r="E780" s="7"/>
       <c r="F780" s="7"/>
@@ -25335,7 +25348,7 @@
     <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="7"/>
       <c r="B781" s="7"/>
-      <c r="C781" s="82"/>
+      <c r="C781" s="81"/>
       <c r="D781" s="7"/>
       <c r="E781" s="7"/>
       <c r="F781" s="7"/>
@@ -25365,7 +25378,7 @@
     <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="7"/>
       <c r="B782" s="7"/>
-      <c r="C782" s="82"/>
+      <c r="C782" s="81"/>
       <c r="D782" s="7"/>
       <c r="E782" s="7"/>
       <c r="F782" s="7"/>
@@ -25395,7 +25408,7 @@
     <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="7"/>
       <c r="B783" s="7"/>
-      <c r="C783" s="82"/>
+      <c r="C783" s="81"/>
       <c r="D783" s="7"/>
       <c r="E783" s="7"/>
       <c r="F783" s="7"/>
@@ -25425,7 +25438,7 @@
     <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="7"/>
       <c r="B784" s="7"/>
-      <c r="C784" s="82"/>
+      <c r="C784" s="81"/>
       <c r="D784" s="7"/>
       <c r="E784" s="7"/>
       <c r="F784" s="7"/>
@@ -25455,7 +25468,7 @@
     <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="7"/>
       <c r="B785" s="7"/>
-      <c r="C785" s="82"/>
+      <c r="C785" s="81"/>
       <c r="D785" s="7"/>
       <c r="E785" s="7"/>
       <c r="F785" s="7"/>
@@ -25485,7 +25498,7 @@
     <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="7"/>
       <c r="B786" s="7"/>
-      <c r="C786" s="82"/>
+      <c r="C786" s="81"/>
       <c r="D786" s="7"/>
       <c r="E786" s="7"/>
       <c r="F786" s="7"/>
@@ -25515,7 +25528,7 @@
     <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="7"/>
       <c r="B787" s="7"/>
-      <c r="C787" s="82"/>
+      <c r="C787" s="81"/>
       <c r="D787" s="7"/>
       <c r="E787" s="7"/>
       <c r="F787" s="7"/>
@@ -25545,7 +25558,7 @@
     <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="7"/>
       <c r="B788" s="7"/>
-      <c r="C788" s="82"/>
+      <c r="C788" s="81"/>
       <c r="D788" s="7"/>
       <c r="E788" s="7"/>
       <c r="F788" s="7"/>
@@ -25575,7 +25588,7 @@
     <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="7"/>
       <c r="B789" s="7"/>
-      <c r="C789" s="82"/>
+      <c r="C789" s="81"/>
       <c r="D789" s="7"/>
       <c r="E789" s="7"/>
       <c r="F789" s="7"/>
@@ -25605,7 +25618,7 @@
     <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="7"/>
       <c r="B790" s="7"/>
-      <c r="C790" s="82"/>
+      <c r="C790" s="81"/>
       <c r="D790" s="7"/>
       <c r="E790" s="7"/>
       <c r="F790" s="7"/>
@@ -25635,7 +25648,7 @@
     <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="7"/>
       <c r="B791" s="7"/>
-      <c r="C791" s="82"/>
+      <c r="C791" s="81"/>
       <c r="D791" s="7"/>
       <c r="E791" s="7"/>
       <c r="F791" s="7"/>
@@ -25665,7 +25678,7 @@
     <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="7"/>
       <c r="B792" s="7"/>
-      <c r="C792" s="82"/>
+      <c r="C792" s="81"/>
       <c r="D792" s="7"/>
       <c r="E792" s="7"/>
       <c r="F792" s="7"/>
@@ -25695,7 +25708,7 @@
     <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="7"/>
       <c r="B793" s="7"/>
-      <c r="C793" s="82"/>
+      <c r="C793" s="81"/>
       <c r="D793" s="7"/>
       <c r="E793" s="7"/>
       <c r="F793" s="7"/>
@@ -25725,7 +25738,7 @@
     <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="7"/>
       <c r="B794" s="7"/>
-      <c r="C794" s="82"/>
+      <c r="C794" s="81"/>
       <c r="D794" s="7"/>
       <c r="E794" s="7"/>
       <c r="F794" s="7"/>
@@ -25755,7 +25768,7 @@
     <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="7"/>
       <c r="B795" s="7"/>
-      <c r="C795" s="82"/>
+      <c r="C795" s="81"/>
       <c r="D795" s="7"/>
       <c r="E795" s="7"/>
       <c r="F795" s="7"/>
@@ -25785,7 +25798,7 @@
     <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="7"/>
       <c r="B796" s="7"/>
-      <c r="C796" s="82"/>
+      <c r="C796" s="81"/>
       <c r="D796" s="7"/>
       <c r="E796" s="7"/>
       <c r="F796" s="7"/>
@@ -25815,7 +25828,7 @@
     <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="7"/>
       <c r="B797" s="7"/>
-      <c r="C797" s="82"/>
+      <c r="C797" s="81"/>
       <c r="D797" s="7"/>
       <c r="E797" s="7"/>
       <c r="F797" s="7"/>
@@ -25845,7 +25858,7 @@
     <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="7"/>
       <c r="B798" s="7"/>
-      <c r="C798" s="82"/>
+      <c r="C798" s="81"/>
       <c r="D798" s="7"/>
       <c r="E798" s="7"/>
       <c r="F798" s="7"/>
@@ -25875,7 +25888,7 @@
     <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="7"/>
       <c r="B799" s="7"/>
-      <c r="C799" s="82"/>
+      <c r="C799" s="81"/>
       <c r="D799" s="7"/>
       <c r="E799" s="7"/>
       <c r="F799" s="7"/>
@@ -25905,7 +25918,7 @@
     <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="7"/>
       <c r="B800" s="7"/>
-      <c r="C800" s="82"/>
+      <c r="C800" s="81"/>
       <c r="D800" s="7"/>
       <c r="E800" s="7"/>
       <c r="F800" s="7"/>
@@ -25935,7 +25948,7 @@
     <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="7"/>
       <c r="B801" s="7"/>
-      <c r="C801" s="82"/>
+      <c r="C801" s="81"/>
       <c r="D801" s="7"/>
       <c r="E801" s="7"/>
       <c r="F801" s="7"/>
@@ -25965,7 +25978,7 @@
     <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="7"/>
       <c r="B802" s="7"/>
-      <c r="C802" s="82"/>
+      <c r="C802" s="81"/>
       <c r="D802" s="7"/>
       <c r="E802" s="7"/>
       <c r="F802" s="7"/>
@@ -25995,7 +26008,7 @@
     <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="7"/>
       <c r="B803" s="7"/>
-      <c r="C803" s="82"/>
+      <c r="C803" s="81"/>
       <c r="D803" s="7"/>
       <c r="E803" s="7"/>
       <c r="F803" s="7"/>
@@ -26025,7 +26038,7 @@
     <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="7"/>
       <c r="B804" s="7"/>
-      <c r="C804" s="82"/>
+      <c r="C804" s="81"/>
       <c r="D804" s="7"/>
       <c r="E804" s="7"/>
       <c r="F804" s="7"/>
@@ -26055,7 +26068,7 @@
     <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="7"/>
       <c r="B805" s="7"/>
-      <c r="C805" s="82"/>
+      <c r="C805" s="81"/>
       <c r="D805" s="7"/>
       <c r="E805" s="7"/>
       <c r="F805" s="7"/>
@@ -26085,7 +26098,7 @@
     <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="7"/>
       <c r="B806" s="7"/>
-      <c r="C806" s="82"/>
+      <c r="C806" s="81"/>
       <c r="D806" s="7"/>
       <c r="E806" s="7"/>
       <c r="F806" s="7"/>
@@ -26115,7 +26128,7 @@
     <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="7"/>
       <c r="B807" s="7"/>
-      <c r="C807" s="82"/>
+      <c r="C807" s="81"/>
       <c r="D807" s="7"/>
       <c r="E807" s="7"/>
       <c r="F807" s="7"/>
@@ -26145,7 +26158,7 @@
     <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="7"/>
       <c r="B808" s="7"/>
-      <c r="C808" s="82"/>
+      <c r="C808" s="81"/>
       <c r="D808" s="7"/>
       <c r="E808" s="7"/>
       <c r="F808" s="7"/>
@@ -26175,7 +26188,7 @@
     <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="7"/>
       <c r="B809" s="7"/>
-      <c r="C809" s="82"/>
+      <c r="C809" s="81"/>
       <c r="D809" s="7"/>
       <c r="E809" s="7"/>
       <c r="F809" s="7"/>
@@ -26205,7 +26218,7 @@
     <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="7"/>
       <c r="B810" s="7"/>
-      <c r="C810" s="82"/>
+      <c r="C810" s="81"/>
       <c r="D810" s="7"/>
       <c r="E810" s="7"/>
       <c r="F810" s="7"/>
@@ -26235,7 +26248,7 @@
     <row r="811" ht="15.75" customHeight="1">
       <c r="A811" s="7"/>
       <c r="B811" s="7"/>
-      <c r="C811" s="82"/>
+      <c r="C811" s="81"/>
       <c r="D811" s="7"/>
       <c r="E811" s="7"/>
       <c r="F811" s="7"/>
@@ -26265,7 +26278,7 @@
     <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="7"/>
       <c r="B812" s="7"/>
-      <c r="C812" s="82"/>
+      <c r="C812" s="81"/>
       <c r="D812" s="7"/>
       <c r="E812" s="7"/>
       <c r="F812" s="7"/>
@@ -26295,7 +26308,7 @@
     <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="7"/>
       <c r="B813" s="7"/>
-      <c r="C813" s="82"/>
+      <c r="C813" s="81"/>
       <c r="D813" s="7"/>
       <c r="E813" s="7"/>
       <c r="F813" s="7"/>
@@ -26325,7 +26338,7 @@
     <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="7"/>
       <c r="B814" s="7"/>
-      <c r="C814" s="82"/>
+      <c r="C814" s="81"/>
       <c r="D814" s="7"/>
       <c r="E814" s="7"/>
       <c r="F814" s="7"/>
@@ -26355,7 +26368,7 @@
     <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="7"/>
       <c r="B815" s="7"/>
-      <c r="C815" s="82"/>
+      <c r="C815" s="81"/>
       <c r="D815" s="7"/>
       <c r="E815" s="7"/>
       <c r="F815" s="7"/>
@@ -26385,7 +26398,7 @@
     <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="7"/>
       <c r="B816" s="7"/>
-      <c r="C816" s="82"/>
+      <c r="C816" s="81"/>
       <c r="D816" s="7"/>
       <c r="E816" s="7"/>
       <c r="F816" s="7"/>
@@ -26415,7 +26428,7 @@
     <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="7"/>
       <c r="B817" s="7"/>
-      <c r="C817" s="82"/>
+      <c r="C817" s="81"/>
       <c r="D817" s="7"/>
       <c r="E817" s="7"/>
       <c r="F817" s="7"/>
@@ -26445,7 +26458,7 @@
     <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="7"/>
       <c r="B818" s="7"/>
-      <c r="C818" s="82"/>
+      <c r="C818" s="81"/>
       <c r="D818" s="7"/>
       <c r="E818" s="7"/>
       <c r="F818" s="7"/>
@@ -26475,7 +26488,7 @@
     <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="7"/>
       <c r="B819" s="7"/>
-      <c r="C819" s="82"/>
+      <c r="C819" s="81"/>
       <c r="D819" s="7"/>
       <c r="E819" s="7"/>
       <c r="F819" s="7"/>
@@ -26505,7 +26518,7 @@
     <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="7"/>
       <c r="B820" s="7"/>
-      <c r="C820" s="82"/>
+      <c r="C820" s="81"/>
       <c r="D820" s="7"/>
       <c r="E820" s="7"/>
       <c r="F820" s="7"/>
@@ -26535,7 +26548,7 @@
     <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="7"/>
       <c r="B821" s="7"/>
-      <c r="C821" s="82"/>
+      <c r="C821" s="81"/>
       <c r="D821" s="7"/>
       <c r="E821" s="7"/>
       <c r="F821" s="7"/>
@@ -26565,7 +26578,7 @@
     <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="7"/>
       <c r="B822" s="7"/>
-      <c r="C822" s="82"/>
+      <c r="C822" s="81"/>
       <c r="D822" s="7"/>
       <c r="E822" s="7"/>
       <c r="F822" s="7"/>
@@ -26595,7 +26608,7 @@
     <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="7"/>
       <c r="B823" s="7"/>
-      <c r="C823" s="82"/>
+      <c r="C823" s="81"/>
       <c r="D823" s="7"/>
       <c r="E823" s="7"/>
       <c r="F823" s="7"/>
@@ -26625,7 +26638,7 @@
     <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="7"/>
       <c r="B824" s="7"/>
-      <c r="C824" s="82"/>
+      <c r="C824" s="81"/>
       <c r="D824" s="7"/>
       <c r="E824" s="7"/>
       <c r="F824" s="7"/>
@@ -26655,7 +26668,7 @@
     <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="7"/>
       <c r="B825" s="7"/>
-      <c r="C825" s="82"/>
+      <c r="C825" s="81"/>
       <c r="D825" s="7"/>
       <c r="E825" s="7"/>
       <c r="F825" s="7"/>
@@ -26685,7 +26698,7 @@
     <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="7"/>
       <c r="B826" s="7"/>
-      <c r="C826" s="82"/>
+      <c r="C826" s="81"/>
       <c r="D826" s="7"/>
       <c r="E826" s="7"/>
       <c r="F826" s="7"/>
@@ -26715,7 +26728,7 @@
     <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="7"/>
       <c r="B827" s="7"/>
-      <c r="C827" s="82"/>
+      <c r="C827" s="81"/>
       <c r="D827" s="7"/>
       <c r="E827" s="7"/>
       <c r="F827" s="7"/>
@@ -26745,7 +26758,7 @@
     <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="7"/>
       <c r="B828" s="7"/>
-      <c r="C828" s="82"/>
+      <c r="C828" s="81"/>
       <c r="D828" s="7"/>
       <c r="E828" s="7"/>
       <c r="F828" s="7"/>
@@ -26775,7 +26788,7 @@
     <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="7"/>
       <c r="B829" s="7"/>
-      <c r="C829" s="82"/>
+      <c r="C829" s="81"/>
       <c r="D829" s="7"/>
       <c r="E829" s="7"/>
       <c r="F829" s="7"/>
@@ -26805,7 +26818,7 @@
     <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="7"/>
       <c r="B830" s="7"/>
-      <c r="C830" s="82"/>
+      <c r="C830" s="81"/>
       <c r="D830" s="7"/>
       <c r="E830" s="7"/>
       <c r="F830" s="7"/>
@@ -26835,7 +26848,7 @@
     <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="7"/>
       <c r="B831" s="7"/>
-      <c r="C831" s="82"/>
+      <c r="C831" s="81"/>
       <c r="D831" s="7"/>
       <c r="E831" s="7"/>
       <c r="F831" s="7"/>
@@ -26865,7 +26878,7 @@
     <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="7"/>
       <c r="B832" s="7"/>
-      <c r="C832" s="82"/>
+      <c r="C832" s="81"/>
       <c r="D832" s="7"/>
       <c r="E832" s="7"/>
       <c r="F832" s="7"/>
@@ -26895,7 +26908,7 @@
     <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="7"/>
       <c r="B833" s="7"/>
-      <c r="C833" s="82"/>
+      <c r="C833" s="81"/>
       <c r="D833" s="7"/>
       <c r="E833" s="7"/>
       <c r="F833" s="7"/>
@@ -26925,7 +26938,7 @@
     <row r="834" ht="15.75" customHeight="1">
       <c r="A834" s="7"/>
       <c r="B834" s="7"/>
-      <c r="C834" s="82"/>
+      <c r="C834" s="81"/>
       <c r="D834" s="7"/>
       <c r="E834" s="7"/>
       <c r="F834" s="7"/>
@@ -26955,7 +26968,7 @@
     <row r="835" ht="15.75" customHeight="1">
       <c r="A835" s="7"/>
       <c r="B835" s="7"/>
-      <c r="C835" s="82"/>
+      <c r="C835" s="81"/>
       <c r="D835" s="7"/>
       <c r="E835" s="7"/>
       <c r="F835" s="7"/>
@@ -26985,7 +26998,7 @@
     <row r="836" ht="15.75" customHeight="1">
       <c r="A836" s="7"/>
       <c r="B836" s="7"/>
-      <c r="C836" s="82"/>
+      <c r="C836" s="81"/>
       <c r="D836" s="7"/>
       <c r="E836" s="7"/>
       <c r="F836" s="7"/>
@@ -27015,7 +27028,7 @@
     <row r="837" ht="15.75" customHeight="1">
       <c r="A837" s="7"/>
       <c r="B837" s="7"/>
-      <c r="C837" s="82"/>
+      <c r="C837" s="81"/>
       <c r="D837" s="7"/>
       <c r="E837" s="7"/>
       <c r="F837" s="7"/>
@@ -27045,7 +27058,7 @@
     <row r="838" ht="15.75" customHeight="1">
       <c r="A838" s="7"/>
       <c r="B838" s="7"/>
-      <c r="C838" s="82"/>
+      <c r="C838" s="81"/>
       <c r="D838" s="7"/>
       <c r="E838" s="7"/>
       <c r="F838" s="7"/>
@@ -27075,7 +27088,7 @@
     <row r="839" ht="15.75" customHeight="1">
       <c r="A839" s="7"/>
       <c r="B839" s="7"/>
-      <c r="C839" s="82"/>
+      <c r="C839" s="81"/>
       <c r="D839" s="7"/>
       <c r="E839" s="7"/>
       <c r="F839" s="7"/>
@@ -27105,7 +27118,7 @@
     <row r="840" ht="15.75" customHeight="1">
       <c r="A840" s="7"/>
       <c r="B840" s="7"/>
-      <c r="C840" s="82"/>
+      <c r="C840" s="81"/>
       <c r="D840" s="7"/>
       <c r="E840" s="7"/>
       <c r="F840" s="7"/>
@@ -27135,7 +27148,7 @@
     <row r="841" ht="15.75" customHeight="1">
       <c r="A841" s="7"/>
       <c r="B841" s="7"/>
-      <c r="C841" s="82"/>
+      <c r="C841" s="81"/>
       <c r="D841" s="7"/>
       <c r="E841" s="7"/>
       <c r="F841" s="7"/>
@@ -27165,7 +27178,7 @@
     <row r="842" ht="15.75" customHeight="1">
       <c r="A842" s="7"/>
       <c r="B842" s="7"/>
-      <c r="C842" s="82"/>
+      <c r="C842" s="81"/>
       <c r="D842" s="7"/>
       <c r="E842" s="7"/>
       <c r="F842" s="7"/>
@@ -27195,7 +27208,7 @@
     <row r="843" ht="15.75" customHeight="1">
       <c r="A843" s="7"/>
       <c r="B843" s="7"/>
-      <c r="C843" s="82"/>
+      <c r="C843" s="81"/>
       <c r="D843" s="7"/>
       <c r="E843" s="7"/>
       <c r="F843" s="7"/>
@@ -27225,7 +27238,7 @@
     <row r="844" ht="15.75" customHeight="1">
       <c r="A844" s="7"/>
       <c r="B844" s="7"/>
-      <c r="C844" s="82"/>
+      <c r="C844" s="81"/>
       <c r="D844" s="7"/>
       <c r="E844" s="7"/>
       <c r="F844" s="7"/>
@@ -27255,7 +27268,7 @@
     <row r="845" ht="15.75" customHeight="1">
       <c r="A845" s="7"/>
       <c r="B845" s="7"/>
-      <c r="C845" s="82"/>
+      <c r="C845" s="81"/>
       <c r="D845" s="7"/>
       <c r="E845" s="7"/>
       <c r="F845" s="7"/>
@@ -27285,7 +27298,7 @@
     <row r="846" ht="15.75" customHeight="1">
       <c r="A846" s="7"/>
       <c r="B846" s="7"/>
-      <c r="C846" s="82"/>
+      <c r="C846" s="81"/>
       <c r="D846" s="7"/>
       <c r="E846" s="7"/>
       <c r="F846" s="7"/>
@@ -27315,7 +27328,7 @@
     <row r="847" ht="15.75" customHeight="1">
       <c r="A847" s="7"/>
       <c r="B847" s="7"/>
-      <c r="C847" s="82"/>
+      <c r="C847" s="81"/>
       <c r="D847" s="7"/>
       <c r="E847" s="7"/>
       <c r="F847" s="7"/>
@@ -27345,7 +27358,7 @@
     <row r="848" ht="15.75" customHeight="1">
       <c r="A848" s="7"/>
       <c r="B848" s="7"/>
-      <c r="C848" s="82"/>
+      <c r="C848" s="81"/>
       <c r="D848" s="7"/>
       <c r="E848" s="7"/>
       <c r="F848" s="7"/>
@@ -27375,7 +27388,7 @@
     <row r="849" ht="15.75" customHeight="1">
       <c r="A849" s="7"/>
       <c r="B849" s="7"/>
-      <c r="C849" s="82"/>
+      <c r="C849" s="81"/>
       <c r="D849" s="7"/>
       <c r="E849" s="7"/>
       <c r="F849" s="7"/>
@@ -27405,7 +27418,7 @@
     <row r="850" ht="15.75" customHeight="1">
       <c r="A850" s="7"/>
       <c r="B850" s="7"/>
-      <c r="C850" s="82"/>
+      <c r="C850" s="81"/>
       <c r="D850" s="7"/>
       <c r="E850" s="7"/>
       <c r="F850" s="7"/>
@@ -27435,7 +27448,7 @@
     <row r="851" ht="15.75" customHeight="1">
       <c r="A851" s="7"/>
       <c r="B851" s="7"/>
-      <c r="C851" s="82"/>
+      <c r="C851" s="81"/>
       <c r="D851" s="7"/>
       <c r="E851" s="7"/>
       <c r="F851" s="7"/>
@@ -27465,7 +27478,7 @@
     <row r="852" ht="15.75" customHeight="1">
       <c r="A852" s="7"/>
       <c r="B852" s="7"/>
-      <c r="C852" s="82"/>
+      <c r="C852" s="81"/>
       <c r="D852" s="7"/>
       <c r="E852" s="7"/>
       <c r="F852" s="7"/>
@@ -27495,7 +27508,7 @@
     <row r="853" ht="15.75" customHeight="1">
       <c r="A853" s="7"/>
       <c r="B853" s="7"/>
-      <c r="C853" s="82"/>
+      <c r="C853" s="81"/>
       <c r="D853" s="7"/>
       <c r="E853" s="7"/>
       <c r="F853" s="7"/>
@@ -27525,7 +27538,7 @@
     <row r="854" ht="15.75" customHeight="1">
       <c r="A854" s="7"/>
       <c r="B854" s="7"/>
-      <c r="C854" s="82"/>
+      <c r="C854" s="81"/>
       <c r="D854" s="7"/>
       <c r="E854" s="7"/>
       <c r="F854" s="7"/>
@@ -27555,7 +27568,7 @@
     <row r="855" ht="15.75" customHeight="1">
       <c r="A855" s="7"/>
       <c r="B855" s="7"/>
-      <c r="C855" s="82"/>
+      <c r="C855" s="81"/>
       <c r="D855" s="7"/>
       <c r="E855" s="7"/>
       <c r="F855" s="7"/>
@@ -27585,7 +27598,7 @@
     <row r="856" ht="15.75" customHeight="1">
       <c r="A856" s="7"/>
       <c r="B856" s="7"/>
-      <c r="C856" s="82"/>
+      <c r="C856" s="81"/>
       <c r="D856" s="7"/>
       <c r="E856" s="7"/>
       <c r="F856" s="7"/>
@@ -27615,7 +27628,7 @@
     <row r="857" ht="15.75" customHeight="1">
       <c r="A857" s="7"/>
       <c r="B857" s="7"/>
-      <c r="C857" s="82"/>
+      <c r="C857" s="81"/>
       <c r="D857" s="7"/>
       <c r="E857" s="7"/>
       <c r="F857" s="7"/>
@@ -27645,7 +27658,7 @@
     <row r="858" ht="15.75" customHeight="1">
       <c r="A858" s="7"/>
       <c r="B858" s="7"/>
-      <c r="C858" s="82"/>
+      <c r="C858" s="81"/>
       <c r="D858" s="7"/>
       <c r="E858" s="7"/>
       <c r="F858" s="7"/>
@@ -27675,7 +27688,7 @@
     <row r="859" ht="15.75" customHeight="1">
       <c r="A859" s="7"/>
       <c r="B859" s="7"/>
-      <c r="C859" s="82"/>
+      <c r="C859" s="81"/>
       <c r="D859" s="7"/>
       <c r="E859" s="7"/>
       <c r="F859" s="7"/>
@@ -27705,7 +27718,7 @@
     <row r="860" ht="15.75" customHeight="1">
       <c r="A860" s="7"/>
       <c r="B860" s="7"/>
-      <c r="C860" s="82"/>
+      <c r="C860" s="81"/>
       <c r="D860" s="7"/>
       <c r="E860" s="7"/>
       <c r="F860" s="7"/>
@@ -27735,7 +27748,7 @@
     <row r="861" ht="15.75" customHeight="1">
       <c r="A861" s="7"/>
       <c r="B861" s="7"/>
-      <c r="C861" s="82"/>
+      <c r="C861" s="81"/>
       <c r="D861" s="7"/>
       <c r="E861" s="7"/>
       <c r="F861" s="7"/>
@@ -27765,7 +27778,7 @@
     <row r="862" ht="15.75" customHeight="1">
       <c r="A862" s="7"/>
       <c r="B862" s="7"/>
-      <c r="C862" s="82"/>
+      <c r="C862" s="81"/>
       <c r="D862" s="7"/>
       <c r="E862" s="7"/>
       <c r="F862" s="7"/>
@@ -27795,7 +27808,7 @@
     <row r="863" ht="15.75" customHeight="1">
       <c r="A863" s="7"/>
       <c r="B863" s="7"/>
-      <c r="C863" s="82"/>
+      <c r="C863" s="81"/>
       <c r="D863" s="7"/>
       <c r="E863" s="7"/>
       <c r="F863" s="7"/>
@@ -27825,7 +27838,7 @@
     <row r="864" ht="15.75" customHeight="1">
       <c r="A864" s="7"/>
       <c r="B864" s="7"/>
-      <c r="C864" s="82"/>
+      <c r="C864" s="81"/>
       <c r="D864" s="7"/>
       <c r="E864" s="7"/>
       <c r="F864" s="7"/>
@@ -27855,7 +27868,7 @@
     <row r="865" ht="15.75" customHeight="1">
       <c r="A865" s="7"/>
       <c r="B865" s="7"/>
-      <c r="C865" s="82"/>
+      <c r="C865" s="81"/>
       <c r="D865" s="7"/>
       <c r="E865" s="7"/>
       <c r="F865" s="7"/>
@@ -27885,7 +27898,7 @@
     <row r="866" ht="15.75" customHeight="1">
       <c r="A866" s="7"/>
       <c r="B866" s="7"/>
-      <c r="C866" s="82"/>
+      <c r="C866" s="81"/>
       <c r="D866" s="7"/>
       <c r="E866" s="7"/>
       <c r="F866" s="7"/>
@@ -27915,7 +27928,7 @@
     <row r="867" ht="15.75" customHeight="1">
       <c r="A867" s="7"/>
       <c r="B867" s="7"/>
-      <c r="C867" s="82"/>
+      <c r="C867" s="81"/>
       <c r="D867" s="7"/>
       <c r="E867" s="7"/>
       <c r="F867" s="7"/>
@@ -27945,7 +27958,7 @@
     <row r="868" ht="15.75" customHeight="1">
       <c r="A868" s="7"/>
       <c r="B868" s="7"/>
-      <c r="C868" s="82"/>
+      <c r="C868" s="81"/>
       <c r="D868" s="7"/>
       <c r="E868" s="7"/>
       <c r="F868" s="7"/>
@@ -27975,7 +27988,7 @@
     <row r="869" ht="15.75" customHeight="1">
       <c r="A869" s="7"/>
       <c r="B869" s="7"/>
-      <c r="C869" s="82"/>
+      <c r="C869" s="81"/>
       <c r="D869" s="7"/>
       <c r="E869" s="7"/>
       <c r="F869" s="7"/>
@@ -28005,7 +28018,7 @@
     <row r="870" ht="15.75" customHeight="1">
       <c r="A870" s="7"/>
       <c r="B870" s="7"/>
-      <c r="C870" s="82"/>
+      <c r="C870" s="81"/>
       <c r="D870" s="7"/>
       <c r="E870" s="7"/>
       <c r="F870" s="7"/>
@@ -28035,7 +28048,7 @@
     <row r="871" ht="15.75" customHeight="1">
       <c r="A871" s="7"/>
       <c r="B871" s="7"/>
-      <c r="C871" s="82"/>
+      <c r="C871" s="81"/>
       <c r="D871" s="7"/>
       <c r="E871" s="7"/>
       <c r="F871" s="7"/>
@@ -28065,7 +28078,7 @@
     <row r="872" ht="15.75" customHeight="1">
       <c r="A872" s="7"/>
       <c r="B872" s="7"/>
-      <c r="C872" s="82"/>
+      <c r="C872" s="81"/>
       <c r="D872" s="7"/>
       <c r="E872" s="7"/>
       <c r="F872" s="7"/>
@@ -28095,7 +28108,7 @@
     <row r="873" ht="15.75" customHeight="1">
       <c r="A873" s="7"/>
       <c r="B873" s="7"/>
-      <c r="C873" s="82"/>
+      <c r="C873" s="81"/>
       <c r="D873" s="7"/>
       <c r="E873" s="7"/>
       <c r="F873" s="7"/>
@@ -28125,7 +28138,7 @@
     <row r="874" ht="15.75" customHeight="1">
       <c r="A874" s="7"/>
       <c r="B874" s="7"/>
-      <c r="C874" s="82"/>
+      <c r="C874" s="81"/>
       <c r="D874" s="7"/>
       <c r="E874" s="7"/>
       <c r="F874" s="7"/>
@@ -28155,7 +28168,7 @@
     <row r="875" ht="15.75" customHeight="1">
       <c r="A875" s="7"/>
       <c r="B875" s="7"/>
-      <c r="C875" s="82"/>
+      <c r="C875" s="81"/>
       <c r="D875" s="7"/>
       <c r="E875" s="7"/>
       <c r="F875" s="7"/>
@@ -28185,7 +28198,7 @@
     <row r="876" ht="15.75" customHeight="1">
       <c r="A876" s="7"/>
       <c r="B876" s="7"/>
-      <c r="C876" s="82"/>
+      <c r="C876" s="81"/>
       <c r="D876" s="7"/>
       <c r="E876" s="7"/>
       <c r="F876" s="7"/>
@@ -28215,7 +28228,7 @@
     <row r="877" ht="15.75" customHeight="1">
       <c r="A877" s="7"/>
       <c r="B877" s="7"/>
-      <c r="C877" s="82"/>
+      <c r="C877" s="81"/>
       <c r="D877" s="7"/>
       <c r="E877" s="7"/>
       <c r="F877" s="7"/>
@@ -28245,7 +28258,7 @@
     <row r="878" ht="15.75" customHeight="1">
       <c r="A878" s="7"/>
       <c r="B878" s="7"/>
-      <c r="C878" s="82"/>
+      <c r="C878" s="81"/>
       <c r="D878" s="7"/>
       <c r="E878" s="7"/>
       <c r="F878" s="7"/>
@@ -28275,7 +28288,7 @@
     <row r="879" ht="15.75" customHeight="1">
       <c r="A879" s="7"/>
       <c r="B879" s="7"/>
-      <c r="C879" s="82"/>
+      <c r="C879" s="81"/>
       <c r="D879" s="7"/>
       <c r="E879" s="7"/>
       <c r="F879" s="7"/>
@@ -28305,7 +28318,7 @@
     <row r="880" ht="15.75" customHeight="1">
       <c r="A880" s="7"/>
       <c r="B880" s="7"/>
-      <c r="C880" s="82"/>
+      <c r="C880" s="81"/>
       <c r="D880" s="7"/>
       <c r="E880" s="7"/>
       <c r="F880" s="7"/>
@@ -28335,7 +28348,7 @@
     <row r="881" ht="15.75" customHeight="1">
       <c r="A881" s="7"/>
       <c r="B881" s="7"/>
-      <c r="C881" s="82"/>
+      <c r="C881" s="81"/>
       <c r="D881" s="7"/>
       <c r="E881" s="7"/>
       <c r="F881" s="7"/>
@@ -28365,7 +28378,7 @@
     <row r="882" ht="15.75" customHeight="1">
       <c r="A882" s="7"/>
       <c r="B882" s="7"/>
-      <c r="C882" s="82"/>
+      <c r="C882" s="81"/>
       <c r="D882" s="7"/>
       <c r="E882" s="7"/>
       <c r="F882" s="7"/>
@@ -28395,7 +28408,7 @@
     <row r="883" ht="15.75" customHeight="1">
       <c r="A883" s="7"/>
       <c r="B883" s="7"/>
-      <c r="C883" s="82"/>
+      <c r="C883" s="81"/>
       <c r="D883" s="7"/>
       <c r="E883" s="7"/>
       <c r="F883" s="7"/>
@@ -28425,7 +28438,7 @@
     <row r="884" ht="15.75" customHeight="1">
       <c r="A884" s="7"/>
       <c r="B884" s="7"/>
-      <c r="C884" s="82"/>
+      <c r="C884" s="81"/>
       <c r="D884" s="7"/>
       <c r="E884" s="7"/>
       <c r="F884" s="7"/>
@@ -28455,7 +28468,7 @@
     <row r="885" ht="15.75" customHeight="1">
       <c r="A885" s="7"/>
       <c r="B885" s="7"/>
-      <c r="C885" s="82"/>
+      <c r="C885" s="81"/>
       <c r="D885" s="7"/>
       <c r="E885" s="7"/>
       <c r="F885" s="7"/>
@@ -28485,7 +28498,7 @@
     <row r="886" ht="15.75" customHeight="1">
       <c r="A886" s="7"/>
       <c r="B886" s="7"/>
-      <c r="C886" s="82"/>
+      <c r="C886" s="81"/>
       <c r="D886" s="7"/>
       <c r="E886" s="7"/>
       <c r="F886" s="7"/>
@@ -28515,7 +28528,7 @@
     <row r="887" ht="15.75" customHeight="1">
       <c r="A887" s="7"/>
       <c r="B887" s="7"/>
-      <c r="C887" s="82"/>
+      <c r="C887" s="81"/>
       <c r="D887" s="7"/>
       <c r="E887" s="7"/>
       <c r="F887" s="7"/>
@@ -28545,7 +28558,7 @@
     <row r="888" ht="15.75" customHeight="1">
       <c r="A888" s="7"/>
       <c r="B888" s="7"/>
-      <c r="C888" s="82"/>
+      <c r="C888" s="81"/>
       <c r="D888" s="7"/>
       <c r="E888" s="7"/>
       <c r="F888" s="7"/>
@@ -28575,7 +28588,7 @@
     <row r="889" ht="15.75" customHeight="1">
       <c r="A889" s="7"/>
       <c r="B889" s="7"/>
-      <c r="C889" s="82"/>
+      <c r="C889" s="81"/>
       <c r="D889" s="7"/>
       <c r="E889" s="7"/>
       <c r="F889" s="7"/>
@@ -28605,7 +28618,7 @@
     <row r="890" ht="15.75" customHeight="1">
       <c r="A890" s="7"/>
       <c r="B890" s="7"/>
-      <c r="C890" s="82"/>
+      <c r="C890" s="81"/>
       <c r="D890" s="7"/>
       <c r="E890" s="7"/>
       <c r="F890" s="7"/>
@@ -28635,7 +28648,7 @@
     <row r="891" ht="15.75" customHeight="1">
       <c r="A891" s="7"/>
       <c r="B891" s="7"/>
-      <c r="C891" s="82"/>
+      <c r="C891" s="81"/>
       <c r="D891" s="7"/>
       <c r="E891" s="7"/>
       <c r="F891" s="7"/>
@@ -28665,7 +28678,7 @@
     <row r="892" ht="15.75" customHeight="1">
       <c r="A892" s="7"/>
       <c r="B892" s="7"/>
-      <c r="C892" s="82"/>
+      <c r="C892" s="81"/>
       <c r="D892" s="7"/>
       <c r="E892" s="7"/>
       <c r="F892" s="7"/>
@@ -28695,7 +28708,7 @@
     <row r="893" ht="15.75" customHeight="1">
       <c r="A893" s="7"/>
       <c r="B893" s="7"/>
-      <c r="C893" s="82"/>
+      <c r="C893" s="81"/>
       <c r="D893" s="7"/>
       <c r="E893" s="7"/>
       <c r="F893" s="7"/>
@@ -28725,7 +28738,7 @@
     <row r="894" ht="15.75" customHeight="1">
       <c r="A894" s="7"/>
       <c r="B894" s="7"/>
-      <c r="C894" s="82"/>
+      <c r="C894" s="81"/>
       <c r="D894" s="7"/>
       <c r="E894" s="7"/>
       <c r="F894" s="7"/>
@@ -28755,7 +28768,7 @@
     <row r="895" ht="15.75" customHeight="1">
       <c r="A895" s="7"/>
       <c r="B895" s="7"/>
-      <c r="C895" s="82"/>
+      <c r="C895" s="81"/>
       <c r="D895" s="7"/>
       <c r="E895" s="7"/>
       <c r="F895" s="7"/>
@@ -28785,7 +28798,7 @@
     <row r="896" ht="15.75" customHeight="1">
       <c r="A896" s="7"/>
       <c r="B896" s="7"/>
-      <c r="C896" s="82"/>
+      <c r="C896" s="81"/>
       <c r="D896" s="7"/>
       <c r="E896" s="7"/>
       <c r="F896" s="7"/>
@@ -28815,7 +28828,7 @@
     <row r="897" ht="15.75" customHeight="1">
       <c r="A897" s="7"/>
       <c r="B897" s="7"/>
-      <c r="C897" s="82"/>
+      <c r="C897" s="81"/>
       <c r="D897" s="7"/>
       <c r="E897" s="7"/>
       <c r="F897" s="7"/>
@@ -28845,7 +28858,7 @@
     <row r="898" ht="15.75" customHeight="1">
       <c r="A898" s="7"/>
       <c r="B898" s="7"/>
-      <c r="C898" s="82"/>
+      <c r="C898" s="81"/>
       <c r="D898" s="7"/>
       <c r="E898" s="7"/>
       <c r="F898" s="7"/>
@@ -28875,7 +28888,7 @@
     <row r="899" ht="15.75" customHeight="1">
       <c r="A899" s="7"/>
       <c r="B899" s="7"/>
-      <c r="C899" s="82"/>
+      <c r="C899" s="81"/>
       <c r="D899" s="7"/>
       <c r="E899" s="7"/>
       <c r="F899" s="7"/>
@@ -28905,7 +28918,7 @@
     <row r="900" ht="15.75" customHeight="1">
       <c r="A900" s="7"/>
       <c r="B900" s="7"/>
-      <c r="C900" s="82"/>
+      <c r="C900" s="81"/>
       <c r="D900" s="7"/>
       <c r="E900" s="7"/>
       <c r="F900" s="7"/>
@@ -28935,7 +28948,7 @@
     <row r="901" ht="15.75" customHeight="1">
       <c r="A901" s="7"/>
       <c r="B901" s="7"/>
-      <c r="C901" s="82"/>
+      <c r="C901" s="81"/>
       <c r="D901" s="7"/>
       <c r="E901" s="7"/>
       <c r="F901" s="7"/>
@@ -28965,7 +28978,7 @@
     <row r="902" ht="15.75" customHeight="1">
       <c r="A902" s="7"/>
       <c r="B902" s="7"/>
-      <c r="C902" s="82"/>
+      <c r="C902" s="81"/>
       <c r="D902" s="7"/>
       <c r="E902" s="7"/>
       <c r="F902" s="7"/>
@@ -28995,7 +29008,7 @@
     <row r="903" ht="15.75" customHeight="1">
       <c r="A903" s="7"/>
       <c r="B903" s="7"/>
-      <c r="C903" s="82"/>
+      <c r="C903" s="81"/>
       <c r="D903" s="7"/>
       <c r="E903" s="7"/>
       <c r="F903" s="7"/>
@@ -29025,7 +29038,7 @@
     <row r="904" ht="15.75" customHeight="1">
       <c r="A904" s="7"/>
       <c r="B904" s="7"/>
-      <c r="C904" s="82"/>
+      <c r="C904" s="81"/>
       <c r="D904" s="7"/>
       <c r="E904" s="7"/>
       <c r="F904" s="7"/>
@@ -29055,7 +29068,7 @@
     <row r="905" ht="15.75" customHeight="1">
       <c r="A905" s="7"/>
       <c r="B905" s="7"/>
-      <c r="C905" s="82"/>
+      <c r="C905" s="81"/>
       <c r="D905" s="7"/>
       <c r="E905" s="7"/>
       <c r="F905" s="7"/>
@@ -29085,7 +29098,7 @@
     <row r="906" ht="15.75" customHeight="1">
       <c r="A906" s="7"/>
       <c r="B906" s="7"/>
-      <c r="C906" s="82"/>
+      <c r="C906" s="81"/>
       <c r="D906" s="7"/>
       <c r="E906" s="7"/>
       <c r="F906" s="7"/>
@@ -29115,7 +29128,7 @@
     <row r="907" ht="15.75" customHeight="1">
       <c r="A907" s="7"/>
       <c r="B907" s="7"/>
-      <c r="C907" s="82"/>
+      <c r="C907" s="81"/>
       <c r="D907" s="7"/>
       <c r="E907" s="7"/>
       <c r="F907" s="7"/>
@@ -29145,7 +29158,7 @@
     <row r="908" ht="15.75" customHeight="1">
       <c r="A908" s="7"/>
       <c r="B908" s="7"/>
-      <c r="C908" s="82"/>
+      <c r="C908" s="81"/>
       <c r="D908" s="7"/>
       <c r="E908" s="7"/>
       <c r="F908" s="7"/>
@@ -29175,7 +29188,7 @@
     <row r="909" ht="15.75" customHeight="1">
       <c r="A909" s="7"/>
       <c r="B909" s="7"/>
-      <c r="C909" s="82"/>
+      <c r="C909" s="81"/>
       <c r="D909" s="7"/>
       <c r="E909" s="7"/>
       <c r="F909" s="7"/>
@@ -29205,7 +29218,7 @@
     <row r="910" ht="15.75" customHeight="1">
       <c r="A910" s="7"/>
       <c r="B910" s="7"/>
-      <c r="C910" s="82"/>
+      <c r="C910" s="81"/>
       <c r="D910" s="7"/>
       <c r="E910" s="7"/>
       <c r="F910" s="7"/>
@@ -29235,7 +29248,7 @@
     <row r="911" ht="15.75" customHeight="1">
       <c r="A911" s="7"/>
       <c r="B911" s="7"/>
-      <c r="C911" s="82"/>
+      <c r="C911" s="81"/>
       <c r="D911" s="7"/>
       <c r="E911" s="7"/>
       <c r="F911" s="7"/>
@@ -29265,7 +29278,7 @@
     <row r="912" ht="15.75" customHeight="1">
       <c r="A912" s="7"/>
       <c r="B912" s="7"/>
-      <c r="C912" s="82"/>
+      <c r="C912" s="81"/>
       <c r="D912" s="7"/>
       <c r="E912" s="7"/>
       <c r="F912" s="7"/>
@@ -29295,7 +29308,7 @@
     <row r="913" ht="15.75" customHeight="1">
       <c r="A913" s="7"/>
       <c r="B913" s="7"/>
-      <c r="C913" s="82"/>
+      <c r="C913" s="81"/>
       <c r="D913" s="7"/>
       <c r="E913" s="7"/>
       <c r="F913" s="7"/>
@@ -29325,7 +29338,7 @@
     <row r="914" ht="15.75" customHeight="1">
       <c r="A914" s="7"/>
       <c r="B914" s="7"/>
-      <c r="C914" s="82"/>
+      <c r="C914" s="81"/>
       <c r="D914" s="7"/>
       <c r="E914" s="7"/>
       <c r="F914" s="7"/>
@@ -29355,7 +29368,7 @@
     <row r="915" ht="15.75" customHeight="1">
       <c r="A915" s="7"/>
       <c r="B915" s="7"/>
-      <c r="C915" s="82"/>
+      <c r="C915" s="81"/>
       <c r="D915" s="7"/>
       <c r="E915" s="7"/>
       <c r="F915" s="7"/>
@@ -29385,7 +29398,7 @@
     <row r="916" ht="15.75" customHeight="1">
       <c r="A916" s="7"/>
       <c r="B916" s="7"/>
-      <c r="C916" s="82"/>
+      <c r="C916" s="81"/>
       <c r="D916" s="7"/>
       <c r="E916" s="7"/>
       <c r="F916" s="7"/>
@@ -29415,7 +29428,7 @@
     <row r="917" ht="15.75" customHeight="1">
       <c r="A917" s="7"/>
       <c r="B917" s="7"/>
-      <c r="C917" s="82"/>
+      <c r="C917" s="81"/>
       <c r="D917" s="7"/>
       <c r="E917" s="7"/>
       <c r="F917" s="7"/>
@@ -29445,7 +29458,7 @@
     <row r="918" ht="15.75" customHeight="1">
       <c r="A918" s="7"/>
       <c r="B918" s="7"/>
-      <c r="C918" s="82"/>
+      <c r="C918" s="81"/>
       <c r="D918" s="7"/>
       <c r="E918" s="7"/>
       <c r="F918" s="7"/>
@@ -29475,7 +29488,7 @@
     <row r="919" ht="15.75" customHeight="1">
       <c r="A919" s="7"/>
       <c r="B919" s="7"/>
-      <c r="C919" s="82"/>
+      <c r="C919" s="81"/>
       <c r="D919" s="7"/>
       <c r="E919" s="7"/>
       <c r="F919" s="7"/>
@@ -29505,7 +29518,7 @@
     <row r="920" ht="15.75" customHeight="1">
       <c r="A920" s="7"/>
       <c r="B920" s="7"/>
-      <c r="C920" s="82"/>
+      <c r="C920" s="81"/>
       <c r="D920" s="7"/>
       <c r="E920" s="7"/>
       <c r="F920" s="7"/>
@@ -29535,7 +29548,7 @@
     <row r="921" ht="15.75" customHeight="1">
       <c r="A921" s="7"/>
       <c r="B921" s="7"/>
-      <c r="C921" s="82"/>
+      <c r="C921" s="81"/>
       <c r="D921" s="7"/>
       <c r="E921" s="7"/>
       <c r="F921" s="7"/>
@@ -29565,7 +29578,7 @@
     <row r="922" ht="15.75" customHeight="1">
       <c r="A922" s="7"/>
       <c r="B922" s="7"/>
-      <c r="C922" s="82"/>
+      <c r="C922" s="81"/>
       <c r="D922" s="7"/>
       <c r="E922" s="7"/>
       <c r="F922" s="7"/>
@@ -29595,7 +29608,7 @@
     <row r="923" ht="15.75" customHeight="1">
       <c r="A923" s="7"/>
       <c r="B923" s="7"/>
-      <c r="C923" s="82"/>
+      <c r="C923" s="81"/>
       <c r="D923" s="7"/>
       <c r="E923" s="7"/>
       <c r="F923" s="7"/>
@@ -29625,7 +29638,7 @@
     <row r="924" ht="15.75" customHeight="1">
       <c r="A924" s="7"/>
       <c r="B924" s="7"/>
-      <c r="C924" s="82"/>
+      <c r="C924" s="81"/>
       <c r="D924" s="7"/>
       <c r="E924" s="7"/>
       <c r="F924" s="7"/>
@@ -29655,7 +29668,7 @@
     <row r="925" ht="15.75" customHeight="1">
       <c r="A925" s="7"/>
       <c r="B925" s="7"/>
-      <c r="C925" s="82"/>
+      <c r="C925" s="81"/>
       <c r="D925" s="7"/>
       <c r="E925" s="7"/>
       <c r="F925" s="7"/>
@@ -29685,7 +29698,7 @@
     <row r="926" ht="15.75" customHeight="1">
       <c r="A926" s="7"/>
       <c r="B926" s="7"/>
-      <c r="C926" s="82"/>
+      <c r="C926" s="81"/>
       <c r="D926" s="7"/>
       <c r="E926" s="7"/>
       <c r="F926" s="7"/>
@@ -29715,7 +29728,7 @@
     <row r="927" ht="15.75" customHeight="1">
       <c r="A927" s="7"/>
       <c r="B927" s="7"/>
-      <c r="C927" s="82"/>
+      <c r="C927" s="81"/>
       <c r="D927" s="7"/>
       <c r="E927" s="7"/>
       <c r="F927" s="7"/>
@@ -29745,7 +29758,7 @@
     <row r="928" ht="15.75" customHeight="1">
       <c r="A928" s="7"/>
       <c r="B928" s="7"/>
-      <c r="C928" s="82"/>
+      <c r="C928" s="81"/>
       <c r="D928" s="7"/>
       <c r="E928" s="7"/>
       <c r="F928" s="7"/>
@@ -29775,7 +29788,7 @@
     <row r="929" ht="15.75" customHeight="1">
       <c r="A929" s="7"/>
       <c r="B929" s="7"/>
-      <c r="C929" s="82"/>
+      <c r="C929" s="81"/>
       <c r="D929" s="7"/>
       <c r="E929" s="7"/>
       <c r="F929" s="7"/>
@@ -29805,7 +29818,7 @@
     <row r="930" ht="15.75" customHeight="1">
       <c r="A930" s="7"/>
       <c r="B930" s="7"/>
-      <c r="C930" s="82"/>
+      <c r="C930" s="81"/>
       <c r="D930" s="7"/>
       <c r="E930" s="7"/>
       <c r="F930" s="7"/>
@@ -29835,7 +29848,7 @@
     <row r="931" ht="15.75" customHeight="1">
       <c r="A931" s="7"/>
       <c r="B931" s="7"/>
-      <c r="C931" s="82"/>
+      <c r="C931" s="81"/>
       <c r="D931" s="7"/>
       <c r="E931" s="7"/>
       <c r="F931" s="7"/>
@@ -29865,7 +29878,7 @@
     <row r="932" ht="15.75" customHeight="1">
       <c r="A932" s="7"/>
       <c r="B932" s="7"/>
-      <c r="C932" s="82"/>
+      <c r="C932" s="81"/>
       <c r="D932" s="7"/>
       <c r="E932" s="7"/>
       <c r="F932" s="7"/>
@@ -29895,7 +29908,7 @@
     <row r="933" ht="15.75" customHeight="1">
       <c r="A933" s="7"/>
       <c r="B933" s="7"/>
-      <c r="C933" s="82"/>
+      <c r="C933" s="81"/>
       <c r="D933" s="7"/>
       <c r="E933" s="7"/>
       <c r="F933" s="7"/>
@@ -29925,7 +29938,7 @@
     <row r="934" ht="15.75" customHeight="1">
       <c r="A934" s="7"/>
       <c r="B934" s="7"/>
-      <c r="C934" s="82"/>
+      <c r="C934" s="81"/>
       <c r="D934" s="7"/>
       <c r="E934" s="7"/>
       <c r="F934" s="7"/>
@@ -29955,7 +29968,7 @@
     <row r="935" ht="15.75" customHeight="1">
       <c r="A935" s="7"/>
       <c r="B935" s="7"/>
-      <c r="C935" s="82"/>
+      <c r="C935" s="81"/>
       <c r="D935" s="7"/>
       <c r="E935" s="7"/>
       <c r="F935" s="7"/>
@@ -29985,7 +29998,7 @@
     <row r="936" ht="15.75" customHeight="1">
       <c r="A936" s="7"/>
       <c r="B936" s="7"/>
-      <c r="C936" s="82"/>
+      <c r="C936" s="81"/>
       <c r="D936" s="7"/>
       <c r="E936" s="7"/>
       <c r="F936" s="7"/>
@@ -30015,7 +30028,7 @@
     <row r="937" ht="15.75" customHeight="1">
       <c r="A937" s="7"/>
       <c r="B937" s="7"/>
-      <c r="C937" s="82"/>
+      <c r="C937" s="81"/>
       <c r="D937" s="7"/>
       <c r="E937" s="7"/>
       <c r="F937" s="7"/>
@@ -30045,7 +30058,7 @@
     <row r="938" ht="15.75" customHeight="1">
       <c r="A938" s="7"/>
       <c r="B938" s="7"/>
-      <c r="C938" s="82"/>
+      <c r="C938" s="81"/>
       <c r="D938" s="7"/>
       <c r="E938" s="7"/>
       <c r="F938" s="7"/>
@@ -30075,7 +30088,7 @@
     <row r="939" ht="15.75" customHeight="1">
       <c r="A939" s="7"/>
       <c r="B939" s="7"/>
-      <c r="C939" s="82"/>
+      <c r="C939" s="81"/>
       <c r="D939" s="7"/>
       <c r="E939" s="7"/>
       <c r="F939" s="7"/>
@@ -30105,7 +30118,7 @@
     <row r="940" ht="15.75" customHeight="1">
       <c r="A940" s="7"/>
       <c r="B940" s="7"/>
-      <c r="C940" s="82"/>
+      <c r="C940" s="81"/>
       <c r="D940" s="7"/>
       <c r="E940" s="7"/>
       <c r="F940" s="7"/>
@@ -30135,7 +30148,7 @@
     <row r="941" ht="15.75" customHeight="1">
       <c r="A941" s="7"/>
       <c r="B941" s="7"/>
-      <c r="C941" s="82"/>
+      <c r="C941" s="81"/>
       <c r="D941" s="7"/>
       <c r="E941" s="7"/>
       <c r="F941" s="7"/>
@@ -30165,7 +30178,7 @@
     <row r="942" ht="15.75" customHeight="1">
       <c r="A942" s="7"/>
       <c r="B942" s="7"/>
-      <c r="C942" s="82"/>
+      <c r="C942" s="81"/>
       <c r="D942" s="7"/>
       <c r="E942" s="7"/>
       <c r="F942" s="7"/>
@@ -30195,7 +30208,7 @@
     <row r="943" ht="15.75" customHeight="1">
       <c r="A943" s="7"/>
       <c r="B943" s="7"/>
-      <c r="C943" s="82"/>
+      <c r="C943" s="81"/>
       <c r="D943" s="7"/>
       <c r="E943" s="7"/>
       <c r="F943" s="7"/>
@@ -30225,7 +30238,7 @@
     <row r="944" ht="15.75" customHeight="1">
       <c r="A944" s="7"/>
       <c r="B944" s="7"/>
-      <c r="C944" s="82"/>
+      <c r="C944" s="81"/>
       <c r="D944" s="7"/>
       <c r="E944" s="7"/>
       <c r="F944" s="7"/>
@@ -30255,7 +30268,7 @@
     <row r="945" ht="15.75" customHeight="1">
       <c r="A945" s="7"/>
       <c r="B945" s="7"/>
-      <c r="C945" s="82"/>
+      <c r="C945" s="81"/>
       <c r="D945" s="7"/>
       <c r="E945" s="7"/>
       <c r="F945" s="7"/>
@@ -30285,7 +30298,7 @@
     <row r="946" ht="15.75" customHeight="1">
       <c r="A946" s="7"/>
       <c r="B946" s="7"/>
-      <c r="C946" s="82"/>
+      <c r="C946" s="81"/>
       <c r="D946" s="7"/>
       <c r="E946" s="7"/>
       <c r="F946" s="7"/>
@@ -30315,7 +30328,7 @@
     <row r="947" ht="15.75" customHeight="1">
       <c r="A947" s="7"/>
       <c r="B947" s="7"/>
-      <c r="C947" s="82"/>
+      <c r="C947" s="81"/>
       <c r="D947" s="7"/>
       <c r="E947" s="7"/>
       <c r="F947" s="7"/>
@@ -30345,7 +30358,7 @@
     <row r="948" ht="15.75" customHeight="1">
       <c r="A948" s="7"/>
       <c r="B948" s="7"/>
-      <c r="C948" s="82"/>
+      <c r="C948" s="81"/>
       <c r="D948" s="7"/>
       <c r="E948" s="7"/>
       <c r="F948" s="7"/>
@@ -30375,7 +30388,7 @@
     <row r="949" ht="15.75" customHeight="1">
       <c r="A949" s="7"/>
       <c r="B949" s="7"/>
-      <c r="C949" s="82"/>
+      <c r="C949" s="81"/>
       <c r="D949" s="7"/>
       <c r="E949" s="7"/>
       <c r="F949" s="7"/>
@@ -30405,7 +30418,7 @@
     <row r="950" ht="15.75" customHeight="1">
       <c r="A950" s="7"/>
       <c r="B950" s="7"/>
-      <c r="C950" s="82"/>
+      <c r="C950" s="81"/>
       <c r="D950" s="7"/>
       <c r="E950" s="7"/>
       <c r="F950" s="7"/>
@@ -30435,7 +30448,7 @@
     <row r="951" ht="15.75" customHeight="1">
       <c r="A951" s="7"/>
       <c r="B951" s="7"/>
-      <c r="C951" s="82"/>
+      <c r="C951" s="81"/>
       <c r="D951" s="7"/>
       <c r="E951" s="7"/>
       <c r="F951" s="7"/>
@@ -30465,7 +30478,7 @@
     <row r="952" ht="15.75" customHeight="1">
       <c r="A952" s="7"/>
       <c r="B952" s="7"/>
-      <c r="C952" s="82"/>
+      <c r="C952" s="81"/>
       <c r="D952" s="7"/>
       <c r="E952" s="7"/>
       <c r="F952" s="7"/>
@@ -30495,7 +30508,7 @@
     <row r="953" ht="15.75" customHeight="1">
       <c r="A953" s="7"/>
       <c r="B953" s="7"/>
-      <c r="C953" s="82"/>
+      <c r="C953" s="81"/>
       <c r="D953" s="7"/>
       <c r="E953" s="7"/>
       <c r="F953" s="7"/>
@@ -30525,7 +30538,7 @@
     <row r="954" ht="15.75" customHeight="1">
       <c r="A954" s="7"/>
       <c r="B954" s="7"/>
-      <c r="C954" s="82"/>
+      <c r="C954" s="81"/>
       <c r="D954" s="7"/>
       <c r="E954" s="7"/>
       <c r="F954" s="7"/>
@@ -30555,7 +30568,7 @@
     <row r="955" ht="15.75" customHeight="1">
       <c r="A955" s="7"/>
       <c r="B955" s="7"/>
-      <c r="C955" s="82"/>
+      <c r="C955" s="81"/>
       <c r="D955" s="7"/>
       <c r="E955" s="7"/>
       <c r="F955" s="7"/>
@@ -30585,7 +30598,7 @@
     <row r="956" ht="15.75" customHeight="1">
       <c r="A956" s="7"/>
       <c r="B956" s="7"/>
-      <c r="C956" s="82"/>
+      <c r="C956" s="81"/>
       <c r="D956" s="7"/>
       <c r="E956" s="7"/>
       <c r="F956" s="7"/>
@@ -30615,7 +30628,7 @@
     <row r="957" ht="15.75" customHeight="1">
       <c r="A957" s="7"/>
       <c r="B957" s="7"/>
-      <c r="C957" s="82"/>
+      <c r="C957" s="81"/>
       <c r="D957" s="7"/>
       <c r="E957" s="7"/>
       <c r="F957" s="7"/>
@@ -30645,7 +30658,7 @@
     <row r="958" ht="15.75" customHeight="1">
       <c r="A958" s="7"/>
       <c r="B958" s="7"/>
-      <c r="C958" s="82"/>
+      <c r="C958" s="81"/>
       <c r="D958" s="7"/>
       <c r="E958" s="7"/>
       <c r="F958" s="7"/>
@@ -30675,7 +30688,7 @@
     <row r="959" ht="15.75" customHeight="1">
       <c r="A959" s="7"/>
       <c r="B959" s="7"/>
-      <c r="C959" s="82"/>
+      <c r="C959" s="81"/>
       <c r="D959" s="7"/>
       <c r="E959" s="7"/>
       <c r="F959" s="7"/>
@@ -30705,7 +30718,7 @@
     <row r="960" ht="15.75" customHeight="1">
       <c r="A960" s="7"/>
       <c r="B960" s="7"/>
-      <c r="C960" s="82"/>
+      <c r="C960" s="81"/>
       <c r="D960" s="7"/>
       <c r="E960" s="7"/>
       <c r="F960" s="7"/>
@@ -30735,7 +30748,7 @@
     <row r="961" ht="15.75" customHeight="1">
       <c r="A961" s="7"/>
       <c r="B961" s="7"/>
-      <c r="C961" s="82"/>
+      <c r="C961" s="81"/>
       <c r="D961" s="7"/>
       <c r="E961" s="7"/>
       <c r="F961" s="7"/>
@@ -30765,7 +30778,7 @@
     <row r="962" ht="15.75" customHeight="1">
       <c r="A962" s="7"/>
       <c r="B962" s="7"/>
-      <c r="C962" s="82"/>
+      <c r="C962" s="81"/>
       <c r="D962" s="7"/>
       <c r="E962" s="7"/>
       <c r="F962" s="7"/>
@@ -30795,7 +30808,7 @@
     <row r="963" ht="15.75" customHeight="1">
       <c r="A963" s="7"/>
       <c r="B963" s="7"/>
-      <c r="C963" s="82"/>
+      <c r="C963" s="81"/>
       <c r="D963" s="7"/>
       <c r="E963" s="7"/>
       <c r="F963" s="7"/>
@@ -30825,7 +30838,7 @@
     <row r="964" ht="15.75" customHeight="1">
       <c r="A964" s="7"/>
       <c r="B964" s="7"/>
-      <c r="C964" s="82"/>
+      <c r="C964" s="81"/>
       <c r="D964" s="7"/>
       <c r="E964" s="7"/>
       <c r="F964" s="7"/>
@@ -30855,7 +30868,7 @@
     <row r="965" ht="15.75" customHeight="1">
       <c r="A965" s="7"/>
       <c r="B965" s="7"/>
-      <c r="C965" s="82"/>
+      <c r="C965" s="81"/>
       <c r="D965" s="7"/>
       <c r="E965" s="7"/>
       <c r="F965" s="7"/>
@@ -30885,7 +30898,7 @@
     <row r="966" ht="15.75" customHeight="1">
       <c r="A966" s="7"/>
       <c r="B966" s="7"/>
-      <c r="C966" s="82"/>
+      <c r="C966" s="81"/>
       <c r="D966" s="7"/>
       <c r="E966" s="7"/>
       <c r="F966" s="7"/>
@@ -30915,7 +30928,7 @@
     <row r="967" ht="15.75" customHeight="1">
       <c r="A967" s="7"/>
       <c r="B967" s="7"/>
-      <c r="C967" s="82"/>
+      <c r="C967" s="81"/>
       <c r="D967" s="7"/>
       <c r="E967" s="7"/>
       <c r="F967" s="7"/>
@@ -30945,7 +30958,7 @@
     <row r="968" ht="15.75" customHeight="1">
       <c r="A968" s="7"/>
       <c r="B968" s="7"/>
-      <c r="C968" s="82"/>
+      <c r="C968" s="81"/>
       <c r="D968" s="7"/>
       <c r="E968" s="7"/>
       <c r="F968" s="7"/>
@@ -30975,7 +30988,7 @@
     <row r="969" ht="15.75" customHeight="1">
       <c r="A969" s="7"/>
       <c r="B969" s="7"/>
-      <c r="C969" s="82"/>
+      <c r="C969" s="81"/>
       <c r="D969" s="7"/>
       <c r="E969" s="7"/>
       <c r="F969" s="7"/>
@@ -31005,7 +31018,7 @@
     <row r="970" ht="15.75" customHeight="1">
       <c r="A970" s="7"/>
       <c r="B970" s="7"/>
-      <c r="C970" s="82"/>
+      <c r="C970" s="81"/>
       <c r="D970" s="7"/>
       <c r="E970" s="7"/>
       <c r="F970" s="7"/>
@@ -31035,7 +31048,7 @@
     <row r="971" ht="15.75" customHeight="1">
       <c r="A971" s="7"/>
       <c r="B971" s="7"/>
-      <c r="C971" s="82"/>
+      <c r="C971" s="81"/>
       <c r="D971" s="7"/>
       <c r="E971" s="7"/>
       <c r="F971" s="7"/>
@@ -31065,7 +31078,7 @@
     <row r="972" ht="15.75" customHeight="1">
       <c r="A972" s="7"/>
       <c r="B972" s="7"/>
-      <c r="C972" s="82"/>
+      <c r="C972" s="81"/>
       <c r="D972" s="7"/>
       <c r="E972" s="7"/>
       <c r="F972" s="7"/>
@@ -31095,7 +31108,7 @@
     <row r="973" ht="15.75" customHeight="1">
       <c r="A973" s="7"/>
       <c r="B973" s="7"/>
-      <c r="C973" s="82"/>
+      <c r="C973" s="81"/>
       <c r="D973" s="7"/>
       <c r="E973" s="7"/>
       <c r="F973" s="7"/>
@@ -31125,7 +31138,7 @@
     <row r="974" ht="15.75" customHeight="1">
       <c r="A974" s="7"/>
       <c r="B974" s="7"/>
-      <c r="C974" s="82"/>
+      <c r="C974" s="81"/>
       <c r="D974" s="7"/>
       <c r="E974" s="7"/>
       <c r="F974" s="7"/>
@@ -31155,7 +31168,7 @@
     <row r="975" ht="15.75" customHeight="1">
       <c r="A975" s="7"/>
       <c r="B975" s="7"/>
-      <c r="C975" s="82"/>
+      <c r="C975" s="81"/>
       <c r="D975" s="7"/>
       <c r="E975" s="7"/>
       <c r="F975" s="7"/>
@@ -31185,7 +31198,7 @@
     <row r="976" ht="15.75" customHeight="1">
       <c r="A976" s="7"/>
       <c r="B976" s="7"/>
-      <c r="C976" s="82"/>
+      <c r="C976" s="81"/>
       <c r="D976" s="7"/>
       <c r="E976" s="7"/>
       <c r="F976" s="7"/>
@@ -31215,7 +31228,7 @@
     <row r="977" ht="15.75" customHeight="1">
       <c r="A977" s="7"/>
       <c r="B977" s="7"/>
-      <c r="C977" s="82"/>
+      <c r="C977" s="81"/>
       <c r="D977" s="7"/>
       <c r="E977" s="7"/>
       <c r="F977" s="7"/>
@@ -31245,7 +31258,7 @@
     <row r="978" ht="15.75" customHeight="1">
       <c r="A978" s="7"/>
       <c r="B978" s="7"/>
-      <c r="C978" s="82"/>
+      <c r="C978" s="81"/>
       <c r="D978" s="7"/>
       <c r="E978" s="7"/>
       <c r="F978" s="7"/>
@@ -31275,7 +31288,7 @@
     <row r="979" ht="15.75" customHeight="1">
       <c r="A979" s="7"/>
       <c r="B979" s="7"/>
-      <c r="C979" s="82"/>
+      <c r="C979" s="81"/>
       <c r="D979" s="7"/>
       <c r="E979" s="7"/>
       <c r="F979" s="7"/>
@@ -31305,7 +31318,7 @@
     <row r="980" ht="15.75" customHeight="1">
       <c r="A980" s="7"/>
       <c r="B980" s="7"/>
-      <c r="C980" s="82"/>
+      <c r="C980" s="81"/>
       <c r="D980" s="7"/>
       <c r="E980" s="7"/>
       <c r="F980" s="7"/>
@@ -31335,7 +31348,7 @@
     <row r="981" ht="15.75" customHeight="1">
       <c r="A981" s="7"/>
       <c r="B981" s="7"/>
-      <c r="C981" s="82"/>
+      <c r="C981" s="81"/>
       <c r="D981" s="7"/>
       <c r="E981" s="7"/>
       <c r="F981" s="7"/>
@@ -31365,7 +31378,7 @@
     <row r="982" ht="15.75" customHeight="1">
       <c r="A982" s="7"/>
       <c r="B982" s="7"/>
-      <c r="C982" s="82"/>
+      <c r="C982" s="81"/>
       <c r="D982" s="7"/>
       <c r="E982" s="7"/>
       <c r="F982" s="7"/>
@@ -31395,7 +31408,7 @@
     <row r="983" ht="15.75" customHeight="1">
       <c r="A983" s="7"/>
       <c r="B983" s="7"/>
-      <c r="C983" s="82"/>
+      <c r="C983" s="81"/>
       <c r="D983" s="7"/>
       <c r="E983" s="7"/>
       <c r="F983" s="7"/>
@@ -31425,7 +31438,7 @@
     <row r="984" ht="15.75" customHeight="1">
       <c r="A984" s="7"/>
       <c r="B984" s="7"/>
-      <c r="C984" s="82"/>
+      <c r="C984" s="81"/>
       <c r="D984" s="7"/>
       <c r="E984" s="7"/>
       <c r="F984" s="7"/>
@@ -31455,7 +31468,7 @@
     <row r="985" ht="15.75" customHeight="1">
       <c r="A985" s="7"/>
       <c r="B985" s="7"/>
-      <c r="C985" s="82"/>
+      <c r="C985" s="81"/>
       <c r="D985" s="7"/>
       <c r="E985" s="7"/>
       <c r="F985" s="7"/>
@@ -31485,7 +31498,7 @@
     <row r="986" ht="15.75" customHeight="1">
       <c r="A986" s="7"/>
       <c r="B986" s="7"/>
-      <c r="C986" s="82"/>
+      <c r="C986" s="81"/>
       <c r="D986" s="7"/>
       <c r="E986" s="7"/>
       <c r="F986" s="7"/>
@@ -31515,7 +31528,7 @@
     <row r="987" ht="15.75" customHeight="1">
       <c r="A987" s="7"/>
       <c r="B987" s="7"/>
-      <c r="C987" s="82"/>
+      <c r="C987" s="81"/>
       <c r="D987" s="7"/>
       <c r="E987" s="7"/>
       <c r="F987" s="7"/>
@@ -31545,7 +31558,7 @@
     <row r="988" ht="15.75" customHeight="1">
       <c r="A988" s="7"/>
       <c r="B988" s="7"/>
-      <c r="C988" s="82"/>
+      <c r="C988" s="81"/>
       <c r="D988" s="7"/>
       <c r="E988" s="7"/>
       <c r="F988" s="7"/>
@@ -31575,7 +31588,7 @@
     <row r="989" ht="15.75" customHeight="1">
       <c r="A989" s="7"/>
       <c r="B989" s="7"/>
-      <c r="C989" s="82"/>
+      <c r="C989" s="81"/>
       <c r="D989" s="7"/>
       <c r="E989" s="7"/>
       <c r="F989" s="7"/>
@@ -31605,7 +31618,7 @@
     <row r="990" ht="15.75" customHeight="1">
       <c r="A990" s="7"/>
       <c r="B990" s="7"/>
-      <c r="C990" s="82"/>
+      <c r="C990" s="81"/>
       <c r="D990" s="7"/>
       <c r="E990" s="7"/>
       <c r="F990" s="7"/>
@@ -31635,7 +31648,7 @@
     <row r="991" ht="15.75" customHeight="1">
       <c r="A991" s="7"/>
       <c r="B991" s="7"/>
-      <c r="C991" s="82"/>
+      <c r="C991" s="81"/>
       <c r="D991" s="7"/>
       <c r="E991" s="7"/>
       <c r="F991" s="7"/>
@@ -31665,7 +31678,7 @@
     <row r="992" ht="15.75" customHeight="1">
       <c r="A992" s="7"/>
       <c r="B992" s="7"/>
-      <c r="C992" s="82"/>
+      <c r="C992" s="81"/>
       <c r="D992" s="7"/>
       <c r="E992" s="7"/>
       <c r="F992" s="7"/>
@@ -31695,7 +31708,7 @@
     <row r="993" ht="15.75" customHeight="1">
       <c r="A993" s="7"/>
       <c r="B993" s="7"/>
-      <c r="C993" s="82"/>
+      <c r="C993" s="81"/>
       <c r="D993" s="7"/>
       <c r="E993" s="7"/>
       <c r="F993" s="7"/>
@@ -31725,7 +31738,7 @@
     <row r="994" ht="15.75" customHeight="1">
       <c r="A994" s="7"/>
       <c r="B994" s="7"/>
-      <c r="C994" s="82"/>
+      <c r="C994" s="81"/>
       <c r="D994" s="7"/>
       <c r="E994" s="7"/>
       <c r="F994" s="7"/>
@@ -31755,7 +31768,7 @@
     <row r="995" ht="15.75" customHeight="1">
       <c r="A995" s="7"/>
       <c r="B995" s="7"/>
-      <c r="C995" s="82"/>
+      <c r="C995" s="81"/>
       <c r="D995" s="7"/>
       <c r="E995" s="7"/>
       <c r="F995" s="7"/>
@@ -31785,7 +31798,7 @@
     <row r="996" ht="15.75" customHeight="1">
       <c r="A996" s="7"/>
       <c r="B996" s="7"/>
-      <c r="C996" s="82"/>
+      <c r="C996" s="81"/>
       <c r="D996" s="7"/>
       <c r="E996" s="7"/>
       <c r="F996" s="7"/>
@@ -31815,7 +31828,7 @@
     <row r="997" ht="15.75" customHeight="1">
       <c r="A997" s="7"/>
       <c r="B997" s="7"/>
-      <c r="C997" s="82"/>
+      <c r="C997" s="81"/>
       <c r="D997" s="7"/>
       <c r="E997" s="7"/>
       <c r="F997" s="7"/>
@@ -31845,7 +31858,7 @@
     <row r="998" ht="15.75" customHeight="1">
       <c r="A998" s="7"/>
       <c r="B998" s="7"/>
-      <c r="C998" s="82"/>
+      <c r="C998" s="81"/>
       <c r="D998" s="7"/>
       <c r="E998" s="7"/>
       <c r="F998" s="7"/>
@@ -31875,7 +31888,7 @@
     <row r="999" ht="15.75" customHeight="1">
       <c r="A999" s="7"/>
       <c r="B999" s="7"/>
-      <c r="C999" s="82"/>
+      <c r="C999" s="81"/>
       <c r="D999" s="7"/>
       <c r="E999" s="7"/>
       <c r="F999" s="7"/>
@@ -31905,7 +31918,7 @@
     <row r="1000" ht="15.75" customHeight="1">
       <c r="A1000" s="7"/>
       <c r="B1000" s="7"/>
-      <c r="C1000" s="82"/>
+      <c r="C1000" s="81"/>
       <c r="D1000" s="7"/>
       <c r="E1000" s="7"/>
       <c r="F1000" s="7"/>
@@ -31935,7 +31948,7 @@
     <row r="1001" ht="15.75" customHeight="1">
       <c r="A1001" s="7"/>
       <c r="B1001" s="7"/>
-      <c r="C1001" s="82"/>
+      <c r="C1001" s="81"/>
       <c r="D1001" s="7"/>
       <c r="E1001" s="7"/>
       <c r="F1001" s="7"/>
@@ -31965,7 +31978,7 @@
     <row r="1002" ht="15.75" customHeight="1">
       <c r="A1002" s="7"/>
       <c r="B1002" s="7"/>
-      <c r="C1002" s="82"/>
+      <c r="C1002" s="81"/>
       <c r="D1002" s="7"/>
       <c r="E1002" s="7"/>
       <c r="F1002" s="7"/>
@@ -31995,7 +32008,7 @@
     <row r="1003" ht="15.75" customHeight="1">
       <c r="A1003" s="7"/>
       <c r="B1003" s="7"/>
-      <c r="C1003" s="82"/>
+      <c r="C1003" s="81"/>
       <c r="D1003" s="7"/>
       <c r="E1003" s="7"/>
       <c r="F1003" s="7"/>
@@ -32025,7 +32038,7 @@
     <row r="1004" ht="15.75" customHeight="1">
       <c r="A1004" s="7"/>
       <c r="B1004" s="7"/>
-      <c r="C1004" s="82"/>
+      <c r="C1004" s="81"/>
       <c r="D1004" s="7"/>
       <c r="E1004" s="7"/>
       <c r="F1004" s="7"/>
@@ -32055,7 +32068,7 @@
     <row r="1005" ht="15.75" customHeight="1">
       <c r="A1005" s="7"/>
       <c r="B1005" s="7"/>
-      <c r="C1005" s="82"/>
+      <c r="C1005" s="81"/>
       <c r="D1005" s="7"/>
       <c r="E1005" s="7"/>
       <c r="F1005" s="7"/>
@@ -32085,7 +32098,7 @@
     <row r="1006" ht="15.75" customHeight="1">
       <c r="A1006" s="7"/>
       <c r="B1006" s="7"/>
-      <c r="C1006" s="82"/>
+      <c r="C1006" s="81"/>
       <c r="D1006" s="7"/>
       <c r="E1006" s="7"/>
       <c r="F1006" s="7"/>
@@ -32115,7 +32128,7 @@
     <row r="1007" ht="15.75" customHeight="1">
       <c r="A1007" s="7"/>
       <c r="B1007" s="7"/>
-      <c r="C1007" s="82"/>
+      <c r="C1007" s="81"/>
       <c r="D1007" s="7"/>
       <c r="E1007" s="7"/>
       <c r="F1007" s="7"/>
@@ -32145,7 +32158,7 @@
     <row r="1008" ht="15.75" customHeight="1">
       <c r="A1008" s="7"/>
       <c r="B1008" s="7"/>
-      <c r="C1008" s="82"/>
+      <c r="C1008" s="81"/>
       <c r="D1008" s="7"/>
       <c r="E1008" s="7"/>
       <c r="F1008" s="7"/>
@@ -32175,7 +32188,7 @@
     <row r="1009" ht="15.75" customHeight="1">
       <c r="A1009" s="7"/>
       <c r="B1009" s="7"/>
-      <c r="C1009" s="82"/>
+      <c r="C1009" s="81"/>
       <c r="D1009" s="7"/>
       <c r="E1009" s="7"/>
       <c r="F1009" s="7"/>
@@ -32205,7 +32218,7 @@
     <row r="1010" ht="15.75" customHeight="1">
       <c r="A1010" s="7"/>
       <c r="B1010" s="7"/>
-      <c r="C1010" s="82"/>
+      <c r="C1010" s="81"/>
       <c r="D1010" s="7"/>
       <c r="E1010" s="7"/>
       <c r="F1010" s="7"/>
@@ -32235,7 +32248,7 @@
     <row r="1011" ht="15.75" customHeight="1">
       <c r="A1011" s="7"/>
       <c r="B1011" s="7"/>
-      <c r="C1011" s="82"/>
+      <c r="C1011" s="81"/>
       <c r="D1011" s="7"/>
       <c r="E1011" s="7"/>
       <c r="F1011" s="7"/>
@@ -32265,7 +32278,7 @@
     <row r="1012" ht="15.75" customHeight="1">
       <c r="A1012" s="7"/>
       <c r="B1012" s="7"/>
-      <c r="C1012" s="82"/>
+      <c r="C1012" s="81"/>
       <c r="D1012" s="7"/>
       <c r="E1012" s="7"/>
       <c r="F1012" s="7"/>
@@ -32295,7 +32308,7 @@
     <row r="1013" ht="15.75" customHeight="1">
       <c r="A1013" s="7"/>
       <c r="B1013" s="7"/>
-      <c r="C1013" s="82"/>
+      <c r="C1013" s="81"/>
       <c r="D1013" s="7"/>
       <c r="E1013" s="7"/>
       <c r="F1013" s="7"/>
@@ -32325,7 +32338,7 @@
     <row r="1014" ht="15.75" customHeight="1">
       <c r="A1014" s="7"/>
       <c r="B1014" s="7"/>
-      <c r="C1014" s="82"/>
+      <c r="C1014" s="81"/>
       <c r="D1014" s="7"/>
       <c r="E1014" s="7"/>
       <c r="F1014" s="7"/>
@@ -32355,7 +32368,7 @@
     <row r="1015" ht="15.75" customHeight="1">
       <c r="A1015" s="7"/>
       <c r="B1015" s="7"/>
-      <c r="C1015" s="82"/>
+      <c r="C1015" s="81"/>
       <c r="D1015" s="7"/>
       <c r="E1015" s="7"/>
       <c r="F1015" s="7"/>
@@ -32385,7 +32398,7 @@
     <row r="1016" ht="15.75" customHeight="1">
       <c r="A1016" s="7"/>
       <c r="B1016" s="7"/>
-      <c r="C1016" s="82"/>
+      <c r="C1016" s="81"/>
       <c r="D1016" s="7"/>
       <c r="E1016" s="7"/>
       <c r="F1016" s="7"/>
@@ -32415,7 +32428,7 @@
     <row r="1017" ht="15.75" customHeight="1">
       <c r="A1017" s="7"/>
       <c r="B1017" s="7"/>
-      <c r="C1017" s="82"/>
+      <c r="C1017" s="81"/>
       <c r="D1017" s="7"/>
       <c r="E1017" s="7"/>
       <c r="F1017" s="7"/>
